--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1) الأصناف (فينكا – زينيا – امرانتس – بيتونيا – سيلوزيا – فضية) موحدة 0.50 للطرفين في كل العقود والمسحوبات.</t>
+          <t>1) الأصناف (فينكا – زينيا – امرانتس – بيتونيا – سيلوزيا – فضية – ماري جولد – سالفيا – هيبوستس – الزهور الموسمية) موحدة 0.50 للطرفين في كل العقود والمسحوبات.</t>
         </is>
       </c>
     </row>
@@ -883,17 +883,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>سيلوزيا</t>
+          <t>سالفيا مركن 9</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>زهور سيلوزيا</t>
+          <t>زهور سالفيا مركن 9 / زهور سالفيا مركن9 سم</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5 / 0.6 / 0.75</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
@@ -906,11 +906,11 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3000</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="7">
@@ -919,12 +919,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>فضيه</t>
+          <t>سيلوزيا</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>زهور فضية</t>
+          <t>زهور سيلوزيا</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -942,11 +942,11 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="8">
@@ -955,17 +955,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>فينكا ابيض</t>
+          <t>فضيه</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>فينكا أبيض</t>
+          <t>زهور فضية</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
@@ -978,11 +978,11 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات قبل الفترة</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -991,12 +991,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>فينكا ابيض نقطه حمراء</t>
+          <t>فينكا ابيض</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>فينكا أبيض نقطة حمراء</t>
+          <t>فينكا أبيض</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3875</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="10">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>فينكا احمر</t>
+          <t>فينكا ابيض نقطه حمراء</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>فينكا أحمر</t>
+          <t>فينكا أبيض نقطة حمراء</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11000</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="11">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>فينكا احمر بنقطه</t>
+          <t>فينكا احمر</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>فينكا أحمر بنقطة</t>
+          <t>فينكا أحمر</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="12">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>فينكا ازرق</t>
+          <t>فينكا احمر بنقطه</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>فينكا أزرق</t>
+          <t>فينكا أحمر بنقطة</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>فينكا روزا</t>
+          <t>فينكا ازرق</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>فينكا أزرق</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.5 / 0.55</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات قبل الفترة</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>190390</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>فينكا مشمشي</t>
+          <t>فينكا روزا</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>فينكا مشمشي</t>
+          <t>زهور فينكا روزا</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5 / 0.55</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات قبل الفترة</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5000</v>
+        <v>190390</v>
       </c>
     </row>
     <row r="15">
@@ -1207,32 +1207,34 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>اشجار تيسبيسيا 2- 3 متر</t>
+          <t>فينكا مشمشي</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>أشجار تيسبيسيا 2-3 متر</t>
+          <t>فينكا مشمشي</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>موحد 0.50 (قرارك)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد</t>
+          <t>مسحوبات قبل الفترة</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="16">
@@ -1241,23 +1243,25 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقي مركن 12</t>
+          <t>ماري جولد</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقى مركن 12 / زهور اقحوان افريقى مركن12 سم / زهور اقحوان افريقي مركن 12</t>
+          <t>زهور مارى جولد / زهور ماري جولد / مارى جولد</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
+          <t>0.5 / 0.7</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>موحد 0.50 (قرارك)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1266,7 +1270,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7010</v>
+        <v>15425</v>
       </c>
     </row>
     <row r="17">
@@ -1275,32 +1279,34 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقي مركن 9</t>
+          <t>ماري جولد فرنسي</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>زهور اقحوان افريقي مركن 9 / زهور اقحوان افريقي مركن9 سم</t>
+          <t>زهور ماري جولد فرنسى</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1.5 / 2</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>موحد 0.50 (قرارك)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5975</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18">
@@ -1309,32 +1315,34 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقي هولندي مركن 12</t>
+          <t>موسميه</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>زهور اقحوان افريقي هولندي مركن 12</t>
+          <t>زهور موسمية (SEASONAL FLOWERS) / زهور موسمية – غير شامل التوصيل</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>موحد 0.50 (قرارك)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات قبل الفترة</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1875</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="19">
@@ -1343,32 +1351,34 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>اكاسيا جلوكا من 1 - 2 متر</t>
+          <t>هيبوستس</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>اكاسيا جلوكا من 1 - 2 متر</t>
+          <t>زهور هيبوستس / زهور هيبوستس مركن9 سم / هيبوستس</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n"/>
+          <t>0.55 / 0.7 / 2.5</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>موحد 0.50 (قرارك)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>172</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="20">
@@ -1377,17 +1387,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>اكاليفا</t>
+          <t>اشجار تيسبيسيا 2- 3 متر</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>اكاليفا / اكاليفيا</t>
+          <t>أشجار تيسبيسيا 2-3 متر</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -1398,11 +1408,11 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1411,17 +1421,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>اليسوم</t>
+          <t>اقحوان افريقي مركن 12</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>زهور اليسوم / زهور اليسوم مركن9 سم</t>
+          <t>اقحوان افريقى مركن 12 / زهور اقحوان افريقى مركن12 سم / زهور اقحوان افريقي مركن 12</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E21" s="7" t="n"/>
@@ -1432,11 +1442,11 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5275</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="22">
@@ -1445,17 +1455,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>بانستيم اخضر</t>
+          <t>اقحوان افريقي مركن 9</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>بانستيم اخضر</t>
+          <t>زهور اقحوان افريقي مركن 9 / زهور اقحوان افريقي مركن9 سم</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5 / 2</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
@@ -1466,11 +1476,11 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>150</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="23">
@@ -1479,17 +1489,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>بوتنج سويل 70 لتر</t>
+          <t>اقحوان افريقي هولندي مركن 12</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>بوتنج سويل 70 لتر</t>
+          <t>زهور اقحوان افريقي هولندي مركن 12</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
@@ -1504,7 +1514,7 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>10</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="24">
@@ -1513,17 +1523,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>بيرلايت 100 لتر</t>
+          <t>اكاسيا جلوكا من 1 - 2 متر</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>بيرلايت 100 لتر</t>
+          <t>اكاسيا جلوكا من 1 - 2 متر</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E24" s="7" t="n"/>
@@ -1534,11 +1544,11 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>125</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25">
@@ -1547,17 +1557,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>تجيل كروي مركن 9</t>
+          <t>اكاليفا</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>تجيل كروي مركن 9 سم</t>
+          <t>اكاليفا / اكاليفيا</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
@@ -1568,11 +1578,11 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2400</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26">
@@ -1581,17 +1591,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>تراديسكانتيا مركن 19 علاقي</t>
+          <t>اليسوم</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>تراديسكانتيا مركن 19 علاقي</t>
+          <t>زهور اليسوم / زهور اليسوم مركن9 سم</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E26" s="7" t="n"/>
@@ -1602,11 +1612,11 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>515</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="27">
@@ -1615,17 +1625,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>تيكوماريا 50</t>
+          <t>بانستيم اخضر</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>تيكوماريا / تيكوماريا 50 سم / تيكوماريا50 سم</t>
+          <t>بانستيم اخضر</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2.5 / 4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -1636,11 +1646,11 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3530</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
@@ -1649,17 +1659,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>جازانيا</t>
+          <t>بوتنج سويل 70 لتر</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>زهور جازانيا</t>
+          <t>بوتنج سويل 70 لتر</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1670,11 +1680,11 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5525</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1683,17 +1693,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>جهنميه بلدي 1 متر</t>
+          <t>بيرلايت 100 لتر</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>جهنمية بلدي1 متر</t>
+          <t>بيرلايت 100 لتر</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1704,11 +1714,11 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
@@ -1717,17 +1727,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>جهنميه بلدي 50</t>
+          <t>تجيل كروي مركن 9</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>جهنمية بلدى واحد عود 50سم / جهنمية بلدي 50 سم</t>
+          <t>تجيل كروي مركن 9 سم</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2.5 / 5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1738,11 +1748,11 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="31">
@@ -1751,17 +1761,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>جهنميه تايلاندي مركن 25</t>
+          <t>تراديسكانتيا مركن 19 علاقي</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>جهنميه تايلاندى مركن 25</t>
+          <t>تراديسكانتيا مركن 19 علاقي</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1776,7 +1786,7 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32">
@@ -1785,17 +1795,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>جهنميه كرويه تايلندي صغير</t>
+          <t>تيكوماريا 50</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>جهنمية كروية تايلندي صغير</t>
+          <t>تيكوماريا / تيكوماريا 50 سم / تيكوماريا50 سم</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2.5 / 4</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
@@ -1806,11 +1816,11 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="33">
@@ -1819,17 +1829,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>جهنميه كرويه تايلندي كبير</t>
+          <t>جازانيا</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>جهنمية كروية تايلندي كبير</t>
+          <t>زهور جازانيا</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1840,11 +1850,11 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="34">
@@ -1853,17 +1863,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم مركن 12</t>
+          <t>جهنميه بلدي 1 متر</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم مركن 12 / زهور جيرانيوم مركن 12 / زهور جيرانيوم مركن12 سم</t>
+          <t>جهنمية بلدي1 متر</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3 / 3.75</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1874,11 +1884,11 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>20355</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1887,17 +1897,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم مركن 9</t>
+          <t>جهنميه بلدي 50</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>زهور جرانيوم مركن9 سم / زهور جيرانيوم مركن 9</t>
+          <t>جهنمية بلدى واحد عود 50سم / جهنمية بلدي 50 سم</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1.25 / 1.4 / 1.5</t>
+          <t>2.5 / 5</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1908,11 +1918,11 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>41825</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36">
@@ -1921,17 +1931,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم هولندي مركن 12</t>
+          <t>جهنميه تايلاندي مركن 25</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>زهور جيرانيوم  هولندي مركن12 / زهور جيرانيوم هولندى مركن12 سم</t>
+          <t>جهنميه تايلاندى مركن 25</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3.45 / 3.75</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1942,11 +1952,11 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1190</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1955,17 +1965,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري ابيض لامع 1: 3</t>
+          <t>جهنميه كرويه تايلندي صغير</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ابيض لامع / حجر ديكوري أبيض لامع 1:3 سم (10 كجم)</t>
+          <t>جهنمية كروية تايلندي صغير</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>18 / 25</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1976,11 +1986,11 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1989,17 +1999,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري ابيض مطفي 3: 5</t>
+          <t>جهنميه كرويه تايلندي كبير</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكورى ابيض مطفى 3:5سم-10كجم / حجر ديكوري أبيض مطفي 3:5 سم (10 كجم)</t>
+          <t>جهنمية كروية تايلندي كبير</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>10 / 13</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -2010,11 +2020,11 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1123</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2023,17 +2033,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري احمر لامع 1: 3</t>
+          <t>جيرانيوم مركن 12</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>احمر لامع / حجر ديكوري أحمر لامع 1:3 سم (10 كجم)</t>
+          <t>جيرانيوم مركن 12 / زهور جيرانيوم مركن 12 / زهور جيرانيوم مركن12 سم</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>18 / 25</t>
+          <t>3 / 3.75</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -2044,11 +2054,11 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>15</v>
+        <v>20355</v>
       </c>
     </row>
     <row r="40">
@@ -2057,17 +2067,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري احمر مطفي</t>
+          <t>جيرانيوم مركن 9</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>احمر مطفى</t>
+          <t>زهور جرانيوم مركن9 سم / زهور جيرانيوم مركن 9</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.25 / 1.4 / 1.5</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -2078,11 +2088,11 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>70</v>
+        <v>41825</v>
       </c>
     </row>
     <row r="41">
@@ -2091,17 +2101,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري اسود لامع 1: 3</t>
+          <t>جيرانيوم هولندي مركن 12</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>اسود لامع / حجر ديكوري أسود لامع 1:3 سم (10 كجم)</t>
+          <t>زهور جيرانيوم  هولندي مركن12 / زهور جيرانيوم هولندى مركن12 سم</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>18 / 25</t>
+          <t>3.45 / 3.75</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -2112,11 +2122,11 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>14</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="42">
@@ -2125,17 +2135,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري اصفر مطفي 1: 3</t>
+          <t>حجر ديكوري ابيض لامع 1: 3</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>اصفر مطفى / حجر اصفر مطفى / حجر ديكوري أصفر مطفي 1:3 سم (10 كجم)</t>
+          <t>ابيض لامع / حجر ديكوري أبيض لامع 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>10 / 10.5 / 13</t>
+          <t>18 / 25</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -2146,11 +2156,11 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>202</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -2159,17 +2169,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>دورانتا اخضر</t>
+          <t>حجر ديكوري ابيض مطفي 3: 5</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>دورانتا أخضر / دورانتا اخضر</t>
+          <t>حجر ديكورى ابيض مطفى 3:5سم-10كجم / حجر ديكوري أبيض مطفي 3:5 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10 / 13</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -2180,11 +2190,11 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>4000</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="44">
@@ -2193,17 +2203,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>رويليا</t>
+          <t>حجر ديكوري احمر لامع 1: 3</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>رويليا</t>
+          <t>احمر لامع / حجر ديكوري أحمر لامع 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>18 / 25</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -2214,11 +2224,11 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>600</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -2227,17 +2237,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>سالفيا مركن 9</t>
+          <t>حجر ديكوري احمر مطفي</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>زهور سالفيا مركن 9 / زهور سالفيا مركن9 سم</t>
+          <t>احمر مطفى</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.5 / 0.6 / 0.75</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -2248,11 +2258,11 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>6337</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
@@ -2261,17 +2271,17 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>سكندابسس مركن 19 علاقي</t>
+          <t>حجر ديكوري اسود لامع 1: 3</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>سكندابسس مركن 19 علاقي</t>
+          <t>اسود لامع / حجر ديكوري أسود لامع 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18 / 25</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -2282,11 +2292,11 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2300</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -2295,17 +2305,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>سيسبانيا 1 - 2 متر</t>
+          <t>حجر ديكوري اصفر مطفي 1: 3</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>سيسلبانيا 1 - 2 متر</t>
+          <t>اصفر مطفى / حجر اصفر مطفى / حجر ديكوري أصفر مطفي 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>10 / 10.5 / 13</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -2316,11 +2326,11 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>240</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48">
@@ -2329,17 +2339,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>سينيراريا مركن 12</t>
+          <t>دورانتا اخضر</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>زهور سينيراريا 12 / زهور سينيراريا مركن12 سم</t>
+          <t>دورانتا أخضر / دورانتا اخضر</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2.5 / 5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -2350,11 +2360,11 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>348</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="49">
@@ -2363,12 +2373,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>فل بلدي</t>
+          <t>رويليا</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>فل بلدى / فل بلدي</t>
+          <t>رويليا</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2388,7 +2398,7 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="50">
@@ -2397,12 +2407,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>فيكس بندا 50</t>
+          <t>سكندابسس مركن 19 علاقي</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>فيكس بندا 50 سم</t>
+          <t>سكندابسس مركن 19 علاقي</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2422,7 +2432,7 @@
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>10</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="51">
@@ -2431,17 +2441,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>قرنفل امريكي 12</t>
+          <t>سيسبانيا 1 - 2 متر</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>زهور قرنفل امريكي 12</t>
+          <t>سيسلبانيا 1 - 2 متر</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E51" s="7" t="n"/>
@@ -2456,7 +2466,7 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52">
@@ -2465,17 +2475,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>قرنفل صيني</t>
+          <t>سينيراريا مركن 12</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>زهور قرنفل صيني / زهور قرنفل صيني مركن9 سم</t>
+          <t>زهور سينيراريا 12 / زهور سينيراريا مركن12 سم</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.5 / 5</t>
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
@@ -2490,7 +2500,7 @@
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>3550</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53">
@@ -2499,17 +2509,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>كف مريم 1. 5 : 2 م</t>
+          <t>فل بلدي</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>كف مريم 1.5 : 2 م</t>
+          <t>فل بلدى / فل بلدي</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -2520,11 +2530,11 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="54">
@@ -2533,17 +2543,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>كلانشو هولندي مركن 12</t>
+          <t>فيكس بندا 50</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>كالنشو هولندى مركن12 سم / كلانشو هولندي مركن 12</t>
+          <t>فيكس بندا 50 سم</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>4 / 5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -2554,11 +2564,11 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>2420</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -2567,17 +2577,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>قرنفل امريكي 12</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>زهور قرنفل امريكي 12</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E55" s="7" t="n"/>
@@ -2592,7 +2602,7 @@
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56">
@@ -2601,17 +2611,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>كيليوس</t>
+          <t>قرنفل صيني</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>زهور كيليوس</t>
+          <t>زهور قرنفل صيني / زهور قرنفل صيني مركن9 سم</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E56" s="7" t="n"/>
@@ -2622,11 +2632,11 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>2200</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="57">
@@ -2635,17 +2645,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>لانتانا لبناني صغير</t>
+          <t>كف مريم 1. 5 : 2 م</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>لانتانا لبناني صغير</t>
+          <t>كف مريم 1.5 : 2 م</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="E57" s="7" t="n"/>
@@ -2656,11 +2666,11 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -2669,17 +2679,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>ماري جولد</t>
+          <t>كلانشو هولندي مركن 12</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>زهور مارى جولد / زهور ماري جولد / مارى جولد</t>
+          <t>كالنشو هولندى مركن12 سم / كلانشو هولندي مركن 12</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0.5 / 0.7</t>
+          <t>4 / 5</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
@@ -2694,7 +2704,7 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>15425</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="59">
@@ -2703,17 +2713,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ماري جولد فرنسي</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>زهور ماري جولد فرنسى</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
@@ -2728,7 +2738,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>250</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
@@ -2737,17 +2747,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>ملفوف مركن 9</t>
+          <t>كيليوس</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>زهور ملفوف براسيكا مركن9 سم / زهور ملفوف مركن 9</t>
+          <t>زهور كيليوس</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -2758,11 +2768,11 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>2362</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="61">
@@ -2771,17 +2781,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>منثور مركن 9</t>
+          <t>لانتانا لبناني صغير</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>زهور منثور مركن 9</t>
+          <t>لانتانا لبناني صغير</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E61" s="7" t="n"/>
@@ -2792,11 +2802,11 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>462</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62">
@@ -2805,17 +2815,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>موسميه</t>
+          <t>ملفوف مركن 9</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>زهور موسمية (SEASONAL FLOWERS) / زهور موسمية – غير شامل التوصيل</t>
+          <t>زهور ملفوف براسيكا مركن9 سم / زهور ملفوف مركن 9</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -2826,11 +2836,11 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات قبل الفترة</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>66000</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="63">
@@ -2839,17 +2849,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 30</t>
+          <t>منثور مركن 9</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 30 سم</t>
+          <t>زهور منثور مركن 9</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>262.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -2864,7 +2874,7 @@
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>4</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64">
@@ -2873,17 +2883,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 40</t>
+          <t>نخيل سايكس 30</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 40 سم</t>
+          <t>نخيل سايكس 30 سم</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>262.5</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -2898,7 +2908,7 @@
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -2907,17 +2917,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>هيبوستس</t>
+          <t>نخيل سايكس 40</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>زهور هيبوستس / زهور هيبوستس مركن9 سم / هيبوستس</t>
+          <t>نخيل سايكس 40 سم</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>0.55 / 0.7 / 2.5</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E65" s="7" t="n"/>
@@ -2928,11 +2938,11 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>4575</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -3387,7 +3397,7 @@
         <f>IF(G7="","",F7*G7)</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="4">
         <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G7,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G7)</f>
         <v/>
       </c>
@@ -3709,7 +3719,7 @@
         <f>IF(G14="","",F14*G14)</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="4">
         <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G14,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G14)</f>
         <v/>
       </c>
@@ -4215,7 +4225,7 @@
         <f>IF(G25="","",F25*G25)</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G25,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G25)</f>
         <v/>
       </c>
@@ -4629,7 +4639,7 @@
         <f>IF(G34="","",F34*G34)</f>
         <v/>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="4">
         <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G34,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G34)</f>
         <v/>
       </c>
@@ -4767,7 +4777,7 @@
         <f>IF(G37="","",F37*G37)</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="4">
         <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G37,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G37)</f>
         <v/>
       </c>
@@ -5987,7 +5997,7 @@
         <f>IF(F3="","",E3*F3)</f>
         <v/>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F3,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F3)</f>
         <v/>
       </c>
@@ -6110,7 +6120,7 @@
         <f>IF(F6="","",E6*F6)</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F6,VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F6)</f>
         <v/>
       </c>
@@ -6315,7 +6325,7 @@
         <f>IF(F11="","",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="4">
         <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F11,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F11)</f>
         <v/>
       </c>
@@ -6520,7 +6530,7 @@
         <f>IF(F16="","",E16*F16)</f>
         <v/>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F16,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F16)</f>
         <v/>
       </c>
@@ -6930,7 +6940,7 @@
         <f>IF(F26="","",E26*F26)</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="4">
         <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F26,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F26)</f>
         <v/>
       </c>
@@ -7053,7 +7063,7 @@
         <f>IF(F29="","",E29*F29)</f>
         <v/>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F29,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F29)</f>
         <v/>
       </c>
@@ -7340,7 +7350,7 @@
         <f>IF(F36="","",E36*F36)</f>
         <v/>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F36,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F36)</f>
         <v/>
       </c>
@@ -7422,7 +7432,7 @@
         <f>IF(F38="","",E38*F38)</f>
         <v/>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="4">
         <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F38,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F38)</f>
         <v/>
       </c>
@@ -8324,7 +8334,7 @@
         <f>IF(F60="","",E60*F60)</f>
         <v/>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="4">
         <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F60,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F60)</f>
         <v/>
       </c>
@@ -8447,7 +8457,7 @@
         <f>IF(F63="","",E63*F63)</f>
         <v/>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="4">
         <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F63,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F63)</f>
         <v/>
       </c>
@@ -12629,7 +12639,7 @@
         <f>IF(F11="","",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="4">
         <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F11,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F11)</f>
         <v/>
       </c>
@@ -12671,7 +12681,7 @@
         <f>IF(F12="","",E12*F12)</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="4">
         <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F12,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F12)</f>
         <v/>
       </c>
@@ -12713,7 +12723,7 @@
         <f>IF(F13="","",E13*F13)</f>
         <v/>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="4">
         <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F13,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F13)</f>
         <v/>
       </c>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -1808,10 +1808,12 @@
           <t>2.5 / 4</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n"/>
+      <c r="E32" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -1910,10 +1912,12 @@
           <t>2.5 / 5</t>
         </is>
       </c>
-      <c r="E35" s="7" t="n"/>
+      <c r="E35" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2148,10 +2152,12 @@
           <t>18 / 25</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n"/>
+      <c r="E42" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2182,10 +2188,12 @@
           <t>10 / 13</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n"/>
+      <c r="E43" s="6" t="n">
+        <v>11</v>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2216,10 +2224,12 @@
           <t>18 / 25</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n"/>
+      <c r="E44" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2250,10 +2260,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
+      <c r="E45" s="6" t="n">
+        <v>11</v>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2284,10 +2296,12 @@
           <t>18 / 25</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n"/>
+      <c r="E46" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2318,10 +2332,12 @@
           <t>10 / 10.5 / 13</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n"/>
+      <c r="E47" s="6" t="n">
+        <v>11</v>
+      </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -1468,10 +1468,12 @@
           <t>1.5 / 2</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2050,10 +2052,12 @@
           <t>3 / 3.75</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n"/>
+      <c r="E39" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2084,10 +2088,12 @@
           <t>1.25 / 1.4 / 1.5</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n"/>
+      <c r="E40" s="6" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2118,10 +2124,12 @@
           <t>3.45 / 3.75</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n"/>
+      <c r="E41" s="6" t="n">
+        <v>3.45</v>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2504,10 +2512,12 @@
           <t>2.5 / 5</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n"/>
+      <c r="E52" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -2708,10 +2718,12 @@
           <t>4 / 5</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n"/>
+      <c r="E58" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -718,6 +718,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -768,6 +769,11 @@
           <t>إجمالي الكمية</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>أقل سعر باع به لأبو خالد</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -804,6 +810,9 @@
       <c r="H3" s="4" t="n">
         <v>8700</v>
       </c>
+      <c r="I3" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -840,6 +849,9 @@
       <c r="H4" s="4" t="n">
         <v>259147</v>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -876,6 +888,9 @@
       <c r="H5" s="4" t="n">
         <v>69275</v>
       </c>
+      <c r="I5" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -912,6 +927,9 @@
       <c r="H6" s="4" t="n">
         <v>6337</v>
       </c>
+      <c r="I6" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -948,6 +966,9 @@
       <c r="H7" s="4" t="n">
         <v>3000</v>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -984,6 +1005,11 @@
       <c r="H8" s="4" t="n">
         <v>300</v>
       </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1020,6 +1046,11 @@
       <c r="H9" s="4" t="n">
         <v>9000</v>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1056,6 +1087,11 @@
       <c r="H10" s="4" t="n">
         <v>3875</v>
       </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1092,6 +1128,11 @@
       <c r="H11" s="4" t="n">
         <v>11000</v>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1128,6 +1169,11 @@
       <c r="H12" s="4" t="n">
         <v>3000</v>
       </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1164,6 +1210,11 @@
       <c r="H13" s="4" t="n">
         <v>5000</v>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1200,6 +1251,9 @@
       <c r="H14" s="4" t="n">
         <v>190390</v>
       </c>
+      <c r="I14" s="4" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1236,6 +1290,11 @@
       <c r="H15" s="4" t="n">
         <v>5000</v>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1272,6 +1331,9 @@
       <c r="H16" s="4" t="n">
         <v>15425</v>
       </c>
+      <c r="I16" s="4" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1308,6 +1370,11 @@
       <c r="H17" s="4" t="n">
         <v>250</v>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1344,6 +1411,11 @@
       <c r="H18" s="4" t="n">
         <v>66000</v>
       </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1380,6 +1452,9 @@
       <c r="H19" s="4" t="n">
         <v>4575</v>
       </c>
+      <c r="I19" s="4" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1414,6 +1489,9 @@
       <c r="H20" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="I20" s="4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1448,6 +1526,9 @@
       <c r="H21" s="4" t="n">
         <v>7010</v>
       </c>
+      <c r="I21" s="4" t="n">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1484,6 +1565,9 @@
       <c r="H22" s="4" t="n">
         <v>5975</v>
       </c>
+      <c r="I22" s="4" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1518,6 +1602,11 @@
       <c r="H23" s="4" t="n">
         <v>1875</v>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1552,6 +1641,11 @@
       <c r="H24" s="4" t="n">
         <v>172</v>
       </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1586,6 +1680,11 @@
       <c r="H25" s="4" t="n">
         <v>120</v>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1620,6 +1719,9 @@
       <c r="H26" s="4" t="n">
         <v>5275</v>
       </c>
+      <c r="I26" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1654,6 +1756,11 @@
       <c r="H27" s="4" t="n">
         <v>150</v>
       </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1688,6 +1795,11 @@
       <c r="H28" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1722,6 +1834,11 @@
       <c r="H29" s="4" t="n">
         <v>125</v>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1756,6 +1873,11 @@
       <c r="H30" s="4" t="n">
         <v>2400</v>
       </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1790,6 +1912,11 @@
       <c r="H31" s="4" t="n">
         <v>515</v>
       </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1826,6 +1953,9 @@
       <c r="H32" s="4" t="n">
         <v>3530</v>
       </c>
+      <c r="I32" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1860,6 +1990,9 @@
       <c r="H33" s="4" t="n">
         <v>5525</v>
       </c>
+      <c r="I33" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1894,6 +2027,11 @@
       <c r="H34" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1930,6 +2068,11 @@
       <c r="H35" s="4" t="n">
         <v>600</v>
       </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -1964,6 +2107,11 @@
       <c r="H36" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -1998,6 +2146,11 @@
       <c r="H37" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2032,6 +2185,11 @@
       <c r="H38" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2068,6 +2226,9 @@
       <c r="H39" s="4" t="n">
         <v>20355</v>
       </c>
+      <c r="I39" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2104,6 +2265,9 @@
       <c r="H40" s="4" t="n">
         <v>41825</v>
       </c>
+      <c r="I40" s="4" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2140,6 +2304,9 @@
       <c r="H41" s="4" t="n">
         <v>1190</v>
       </c>
+      <c r="I41" s="4" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2176,6 +2343,9 @@
       <c r="H42" s="4" t="n">
         <v>16</v>
       </c>
+      <c r="I42" s="4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2212,6 +2382,9 @@
       <c r="H43" s="4" t="n">
         <v>1123</v>
       </c>
+      <c r="I43" s="4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2248,6 +2421,9 @@
       <c r="H44" s="4" t="n">
         <v>15</v>
       </c>
+      <c r="I44" s="4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2284,6 +2460,11 @@
       <c r="H45" s="4" t="n">
         <v>70</v>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2320,6 +2501,9 @@
       <c r="H46" s="4" t="n">
         <v>14</v>
       </c>
+      <c r="I46" s="4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2356,6 +2540,9 @@
       <c r="H47" s="4" t="n">
         <v>202</v>
       </c>
+      <c r="I47" s="4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -2390,6 +2577,11 @@
       <c r="H48" s="4" t="n">
         <v>4000</v>
       </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2424,6 +2616,11 @@
       <c r="H49" s="4" t="n">
         <v>600</v>
       </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -2458,6 +2655,11 @@
       <c r="H50" s="4" t="n">
         <v>2300</v>
       </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2492,6 +2694,11 @@
       <c r="H51" s="4" t="n">
         <v>240</v>
       </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -2528,6 +2735,9 @@
       <c r="H52" s="4" t="n">
         <v>348</v>
       </c>
+      <c r="I52" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2562,6 +2772,11 @@
       <c r="H53" s="4" t="n">
         <v>500</v>
       </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2596,6 +2811,11 @@
       <c r="H54" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2630,6 +2850,11 @@
       <c r="H55" s="4" t="n">
         <v>90</v>
       </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -2664,6 +2889,9 @@
       <c r="H56" s="4" t="n">
         <v>3550</v>
       </c>
+      <c r="I56" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2698,6 +2926,11 @@
       <c r="H57" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -2734,6 +2967,9 @@
       <c r="H58" s="4" t="n">
         <v>2420</v>
       </c>
+      <c r="I58" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -2768,6 +3004,11 @@
       <c r="H59" s="4" t="n">
         <v>19</v>
       </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -2788,10 +3029,12 @@
           <t>0.55</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n"/>
+      <c r="E60" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -2801,6 +3044,9 @@
       </c>
       <c r="H60" s="4" t="n">
         <v>2200</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="61">
@@ -2836,6 +3082,11 @@
       <c r="H61" s="4" t="n">
         <v>200</v>
       </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -2870,6 +3121,9 @@
       <c r="H62" s="4" t="n">
         <v>2362</v>
       </c>
+      <c r="I62" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -2904,6 +3158,11 @@
       <c r="H63" s="4" t="n">
         <v>462</v>
       </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -2938,6 +3197,11 @@
       <c r="H64" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -2972,6 +3236,11 @@
       <c r="H65" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -3006,6 +3275,11 @@
       <c r="H66" s="4" t="n">
         <v>288</v>
       </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -3040,6 +3314,11 @@
       <c r="H67" s="4" t="n">
         <v>400</v>
       </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -3074,6 +3353,11 @@
       <c r="H68" s="4" t="n">
         <v>730</v>
       </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -3107,6 +3391,11 @@
       </c>
       <c r="H69" s="4" t="n">
         <v>20</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -1475,10 +1475,12 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n"/>
+      <c r="E20" s="6" t="n">
+        <v>60</v>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1512,10 +1514,12 @@
           <t>3.25</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
+      <c r="E21" s="6" t="n">
+        <v>3.25</v>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1666,10 +1670,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n"/>
+      <c r="E25" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1705,10 +1711,12 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n"/>
+      <c r="E26" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1742,10 +1750,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1859,10 +1869,12 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n"/>
+      <c r="E30" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -1976,10 +1988,12 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n"/>
+      <c r="E33" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2013,10 +2027,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n"/>
+      <c r="E34" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2563,10 +2579,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n"/>
+      <c r="E48" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2758,10 +2776,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
+      <c r="E53" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -2797,10 +2817,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n"/>
+      <c r="E54" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -2875,10 +2897,12 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n"/>
+      <c r="E56" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -2912,10 +2936,12 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n"/>
+      <c r="E57" s="6" t="n">
+        <v>5.5</v>
+      </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3068,10 +3094,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E61" s="7" t="n"/>
+      <c r="E61" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3107,10 +3135,12 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n"/>
+      <c r="E62" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -3144,10 +3174,12 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n"/>
+      <c r="E63" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3300,10 +3332,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n"/>
+      <c r="E67" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -3339,10 +3373,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n"/>
+      <c r="E68" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -1592,10 +1592,12 @@
           <t>3.25</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
+      <c r="E23" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1631,10 +1633,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n"/>
+      <c r="E24" s="6" t="n">
+        <v>12</v>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1791,10 +1795,12 @@
           <t>46</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
+      <c r="E28" s="6" t="n">
+        <v>64</v>
+      </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1830,10 +1836,12 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
+      <c r="E29" s="6" t="n">
+        <v>25</v>
+      </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2109,10 +2117,12 @@
           <t>250</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n"/>
+      <c r="E36" s="6" t="n">
+        <v>200</v>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2148,10 +2158,12 @@
           <t>250</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
+      <c r="E37" s="6" t="n">
+        <v>200</v>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2187,10 +2199,12 @@
           <t>300</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n"/>
+      <c r="E38" s="6" t="n">
+        <v>230</v>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2620,10 +2634,12 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="E49" s="7" t="n"/>
+      <c r="E49" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2698,10 +2714,12 @@
           <t>25.5</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n"/>
+      <c r="E51" s="6" t="n">
+        <v>4.5</v>
+      </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2858,10 +2876,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n"/>
+      <c r="E55" s="6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -2978,7 +2998,7 @@
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -3016,10 +3036,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n"/>
+      <c r="E59" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3215,10 +3237,12 @@
           <t>262.5</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n"/>
+      <c r="E64" s="6" t="n">
+        <v>300</v>
+      </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3254,10 +3278,12 @@
           <t>400</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n"/>
+      <c r="E65" s="6" t="n">
+        <v>350</v>
+      </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3414,10 +3440,12 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n"/>
+      <c r="E69" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -114,12 +114,12 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1918,10 +1918,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
+      <c r="E31" s="6" t="n">
+        <v>9.5</v>
+      </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2675,10 +2677,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n"/>
+      <c r="E50" s="6" t="n">
+        <v>9.5</v>
+      </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3319,10 +3323,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n"/>
+      <c r="E66" s="6" t="n">
+        <v>7</v>
+      </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>يحتاج تسعير</t>
+          <t>معتمد (قرارك)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -3563,7 +3569,7 @@
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <v>45957</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3612,7 +3618,7 @@
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <v>45963</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3658,7 +3664,7 @@
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>45966</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3704,7 +3710,7 @@
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>45967</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3750,7 +3756,7 @@
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3796,7 +3802,7 @@
       <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3842,7 +3848,7 @@
       <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3870,7 +3876,7 @@
         <f>IF(G9="","",F9*G9)</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G9,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G9)</f>
         <v/>
       </c>
@@ -3888,7 +3894,7 @@
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>45971</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3934,7 +3940,7 @@
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>45971</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3962,7 +3968,7 @@
         <f>IF(G11="","",F11*G11)</f>
         <v/>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G11,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G11)</f>
         <v/>
       </c>
@@ -3980,7 +3986,7 @@
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>45971</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -4008,7 +4014,7 @@
         <f>IF(G12="","",F12*G12)</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G12)</f>
         <v/>
       </c>
@@ -4026,7 +4032,7 @@
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>45971</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -4054,7 +4060,7 @@
         <f>IF(G13="","",F13*G13)</f>
         <v/>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G13,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G13)</f>
         <v/>
       </c>
@@ -4072,7 +4078,7 @@
       <c r="A14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="7" t="n">
         <v>45971</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -4118,7 +4124,7 @@
       <c r="A15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="7" t="n">
         <v>45971</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -4146,7 +4152,7 @@
         <f>IF(G15="","",F15*G15)</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G15,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G15)</f>
         <v/>
       </c>
@@ -4164,7 +4170,7 @@
       <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="7" t="n">
         <v>45972</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -4210,7 +4216,7 @@
       <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="7" t="n">
         <v>45973</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -4256,7 +4262,7 @@
       <c r="A18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="7" t="n">
         <v>45974</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -4284,7 +4290,7 @@
         <f>IF(G18="","",F18*G18)</f>
         <v/>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G18,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G18)</f>
         <v/>
       </c>
@@ -4302,7 +4308,7 @@
       <c r="A19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="7" t="n">
         <v>45978</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -4348,7 +4354,7 @@
       <c r="A20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>45978</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4376,7 +4382,7 @@
         <f>IF(G20="","",F20*G20)</f>
         <v/>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G20,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G20)</f>
         <v/>
       </c>
@@ -4394,7 +4400,7 @@
       <c r="A21" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="7" t="n">
         <v>45981</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4440,7 +4446,7 @@
       <c r="A22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="7" t="n">
         <v>45981</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4468,7 +4474,7 @@
         <f>IF(G22="","",F22*G22)</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G22,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G22)</f>
         <v/>
       </c>
@@ -4486,7 +4492,7 @@
       <c r="A23" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="7" t="n">
         <v>45984</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4532,7 +4538,7 @@
       <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="7" t="n">
         <v>45985</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4578,7 +4584,7 @@
       <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="7" t="n">
         <v>45988</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4624,7 +4630,7 @@
       <c r="A26" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="7" t="n">
         <v>45996</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4670,7 +4676,7 @@
       <c r="A27" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="7" t="n">
         <v>46006</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4698,7 +4704,7 @@
         <f>IF(G27="","",F27*G27)</f>
         <v/>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G27,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G27)</f>
         <v/>
       </c>
@@ -4716,7 +4722,7 @@
       <c r="A28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="7" t="n">
         <v>46021</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4744,7 +4750,7 @@
         <f>IF(G28="","",F28*G28)</f>
         <v/>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G28,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G28)</f>
         <v/>
       </c>
@@ -4762,7 +4768,7 @@
       <c r="A29" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="7" t="n">
         <v>46021</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4790,7 +4796,7 @@
         <f>IF(G29="","",F29*G29)</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G29,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G29)</f>
         <v/>
       </c>
@@ -4808,7 +4814,7 @@
       <c r="A30" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="7" t="n">
         <v>46021</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4836,7 +4842,7 @@
         <f>IF(G30="","",F30*G30)</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G30,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G30)</f>
         <v/>
       </c>
@@ -4854,7 +4860,7 @@
       <c r="A31" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="7" t="n">
         <v>46021</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -4882,7 +4888,7 @@
         <f>IF(G31="","",F31*G31)</f>
         <v/>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G31,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G31)</f>
         <v/>
       </c>
@@ -4900,7 +4906,7 @@
       <c r="A32" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="7" t="n">
         <v>46021</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -4928,7 +4934,7 @@
         <f>IF(G32="","",F32*G32)</f>
         <v/>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G32,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G32)</f>
         <v/>
       </c>
@@ -4946,7 +4952,7 @@
       <c r="A33" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4992,7 +4998,7 @@
       <c r="A34" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5038,7 +5044,7 @@
       <c r="A35" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -5066,7 +5072,7 @@
         <f>IF(G35="","",F35*G35)</f>
         <v/>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="8">
         <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G35,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G35)</f>
         <v/>
       </c>
@@ -5084,7 +5090,7 @@
       <c r="A36" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -5130,7 +5136,7 @@
       <c r="A37" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="8" t="n">
+      <c r="B37" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -5176,7 +5182,7 @@
       <c r="A38" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B38" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -5204,7 +5210,7 @@
         <f>IF(G38="","",F38*G38)</f>
         <v/>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="8">
         <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G38,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G38)</f>
         <v/>
       </c>
@@ -5222,7 +5228,7 @@
       <c r="A39" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B39" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -5250,7 +5256,7 @@
         <f>IF(G39="","",F39*G39)</f>
         <v/>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="8">
         <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G39,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G39)</f>
         <v/>
       </c>
@@ -5268,7 +5274,7 @@
       <c r="A40" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="8" t="n">
+      <c r="B40" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -5296,7 +5302,7 @@
         <f>IF(G40="","",F40*G40)</f>
         <v/>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="8">
         <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G40,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G40)</f>
         <v/>
       </c>
@@ -5314,7 +5320,7 @@
       <c r="A41" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5342,7 +5348,7 @@
         <f>IF(G41="","",F41*G41)</f>
         <v/>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="8">
         <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G41,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G41)</f>
         <v/>
       </c>
@@ -5360,7 +5366,7 @@
       <c r="A42" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="8" t="n">
+      <c r="B42" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5388,7 +5394,7 @@
         <f>IF(G42="","",F42*G42)</f>
         <v/>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G42,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G42)</f>
         <v/>
       </c>
@@ -5406,7 +5412,7 @@
       <c r="A43" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="8" t="n">
+      <c r="B43" s="7" t="n">
         <v>46058</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5434,7 +5440,7 @@
         <f>IF(G43="","",F43*G43)</f>
         <v/>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="8">
         <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G43,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G43)</f>
         <v/>
       </c>
@@ -5452,7 +5458,7 @@
       <c r="A44" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="8" t="n">
+      <c r="B44" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5480,7 +5486,7 @@
         <f>IF(G44="","",F44*G44)</f>
         <v/>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G44,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G44)</f>
         <v/>
       </c>
@@ -5498,7 +5504,7 @@
       <c r="A45" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B45" s="7" t="n">
         <v>46072</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5544,7 +5550,7 @@
       <c r="A46" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="8" t="n">
+      <c r="B46" s="7" t="n">
         <v>46084</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5572,7 +5578,7 @@
         <f>IF(G46="","",F46*G46)</f>
         <v/>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G46,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G46)</f>
         <v/>
       </c>
@@ -5590,7 +5596,7 @@
       <c r="A47" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="8" t="n">
+      <c r="B47" s="7" t="n">
         <v>46084</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -5618,7 +5624,7 @@
         <f>IF(G47="","",F47*G47)</f>
         <v/>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G47,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G47)</f>
         <v/>
       </c>
@@ -5636,7 +5642,7 @@
       <c r="A48" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="8" t="n">
+      <c r="B48" s="7" t="n">
         <v>46085</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5664,7 +5670,7 @@
         <f>IF(G48="","",F48*G48)</f>
         <v/>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G48,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G48)</f>
         <v/>
       </c>
@@ -5682,7 +5688,7 @@
       <c r="A49" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="8" t="n">
+      <c r="B49" s="7" t="n">
         <v>46085</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -5710,7 +5716,7 @@
         <f>IF(G49="","",F49*G49)</f>
         <v/>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="8">
         <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G49,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G49)</f>
         <v/>
       </c>
@@ -5728,7 +5734,7 @@
       <c r="A50" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="8" t="n">
+      <c r="B50" s="7" t="n">
         <v>46145</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5774,7 +5780,7 @@
       <c r="A51" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="8" t="n">
+      <c r="B51" s="7" t="n">
         <v>46145</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -5820,7 +5826,7 @@
       <c r="A52" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="8" t="n">
+      <c r="B52" s="7" t="n">
         <v>46145</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -5866,7 +5872,7 @@
       <c r="A53" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="8" t="n">
+      <c r="B53" s="7" t="n">
         <v>46145</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -5894,7 +5900,7 @@
         <f>IF(G53="","",F53*G53)</f>
         <v/>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="8">
         <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G53,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G53)</f>
         <v/>
       </c>
@@ -5912,7 +5918,7 @@
       <c r="A54" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="8" t="n">
+      <c r="B54" s="7" t="n">
         <v>46145</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -5940,7 +5946,7 @@
         <f>IF(G54="","",F54*G54)</f>
         <v/>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="8">
         <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G54,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G54)</f>
         <v/>
       </c>
@@ -5958,7 +5964,7 @@
       <c r="A55" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="8" t="n">
+      <c r="B55" s="7" t="n">
         <v>46145</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -5986,7 +5992,7 @@
         <f>IF(G55="","",F55*G55)</f>
         <v/>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="8">
         <f>IFERROR(IF(VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G55,VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G55)</f>
         <v/>
       </c>
@@ -6004,7 +6010,7 @@
       <c r="A56" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="8" t="n">
+      <c r="B56" s="7" t="n">
         <v>46147</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -6050,7 +6056,7 @@
       <c r="A57" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="8" t="n">
+      <c r="B57" s="7" t="n">
         <v>46147</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -6078,7 +6084,7 @@
         <f>IF(G57="","",F57*G57)</f>
         <v/>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="8">
         <f>IFERROR(IF(VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G57,VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G57)</f>
         <v/>
       </c>
@@ -6096,7 +6102,7 @@
       <c r="A58" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="8" t="n">
+      <c r="B58" s="7" t="n">
         <v>46152</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6142,7 +6148,7 @@
       <c r="A59" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="8" t="n">
+      <c r="B59" s="7" t="n">
         <v>46154</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6188,7 +6194,7 @@
       <c r="A60" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="8" t="n">
+      <c r="B60" s="7" t="n">
         <v>46160</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -6231,34 +6237,34 @@
       <c r="L60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n"/>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="11">
         <f>SUM(F3:F60)</f>
         <v/>
       </c>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="12">
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="11">
         <f>SUM(H3:H60)</f>
         <v/>
       </c>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="12">
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="11">
         <f>SUM(J3:J60)</f>
         <v/>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="11">
         <f>SUM(K3:K60)</f>
         <v/>
       </c>
-      <c r="L61" s="10" t="n"/>
+      <c r="L61" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6355,7 +6361,7 @@
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <v>45906</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6396,7 +6402,7 @@
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <v>45926</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6437,7 +6443,7 @@
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>45926</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6460,7 +6466,7 @@
         <f>IF(F5="","",E5*F5)</f>
         <v/>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F5,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F5)</f>
         <v/>
       </c>
@@ -6478,7 +6484,7 @@
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>45926</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6519,7 +6525,7 @@
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>45926</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6542,7 +6548,7 @@
         <f>IF(F7="","",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F7,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F7)</f>
         <v/>
       </c>
@@ -6560,7 +6566,7 @@
       <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -6583,7 +6589,7 @@
         <f>IF(F8="","",E8*F8)</f>
         <v/>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F8,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F8)</f>
         <v/>
       </c>
@@ -6601,7 +6607,7 @@
       <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6624,7 +6630,7 @@
         <f>IF(F9="","",E9*F9)</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F9,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F9)</f>
         <v/>
       </c>
@@ -6642,7 +6648,7 @@
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6665,7 +6671,7 @@
         <f>IF(F10="","",E10*F10)</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F10,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F10)</f>
         <v/>
       </c>
@@ -6683,7 +6689,7 @@
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6724,7 +6730,7 @@
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6747,7 +6753,7 @@
         <f>IF(F12="","",E12*F12)</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F12)</f>
         <v/>
       </c>
@@ -6765,7 +6771,7 @@
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6788,7 +6794,7 @@
         <f>IF(F13="","",E13*F13)</f>
         <v/>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F13,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F13)</f>
         <v/>
       </c>
@@ -6806,7 +6812,7 @@
       <c r="A14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -6829,7 +6835,7 @@
         <f>IF(F14="","",E14*F14)</f>
         <v/>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F14,VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F14)</f>
         <v/>
       </c>
@@ -6847,7 +6853,7 @@
       <c r="A15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="7" t="n">
         <v>45937</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -6870,7 +6876,7 @@
         <f>IF(F15="","",E15*F15)</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F15,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F15)</f>
         <v/>
       </c>
@@ -6888,7 +6894,7 @@
       <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="7" t="n">
         <v>45947</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -6929,7 +6935,7 @@
       <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="7" t="n">
         <v>45947</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6970,7 +6976,7 @@
       <c r="A18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="7" t="n">
         <v>45947</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -6993,7 +6999,7 @@
         <f>IF(F18="","",E18*F18)</f>
         <v/>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <f>IFERROR(IF(VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F18,VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F18)</f>
         <v/>
       </c>
@@ -7011,7 +7017,7 @@
       <c r="A19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="7" t="n">
         <v>45954</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -7052,7 +7058,7 @@
       <c r="A20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -7075,7 +7081,7 @@
         <f>IF(F20="","",E20*F20)</f>
         <v/>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F20,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F20)</f>
         <v/>
       </c>
@@ -7093,7 +7099,7 @@
       <c r="A21" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -7116,7 +7122,7 @@
         <f>IF(F21="","",E21*F21)</f>
         <v/>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F21,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F21)</f>
         <v/>
       </c>
@@ -7134,7 +7140,7 @@
       <c r="A22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -7157,7 +7163,7 @@
         <f>IF(F22="","",E22*F22)</f>
         <v/>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F22,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F22)</f>
         <v/>
       </c>
@@ -7175,7 +7181,7 @@
       <c r="A23" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7198,7 +7204,7 @@
         <f>IF(F23="","",E23*F23)</f>
         <v/>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <f>IFERROR(IF(VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F23,VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F23)</f>
         <v/>
       </c>
@@ -7216,7 +7222,7 @@
       <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="7" t="n">
         <v>45964</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7239,7 +7245,7 @@
         <f>IF(F24="","",E24*F24)</f>
         <v/>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F24,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F24)</f>
         <v/>
       </c>
@@ -7257,7 +7263,7 @@
       <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -7280,7 +7286,7 @@
         <f>IF(F25="","",E25*F25)</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F25,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F25)</f>
         <v/>
       </c>
@@ -7298,7 +7304,7 @@
       <c r="A26" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -7339,7 +7345,7 @@
       <c r="A27" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="7" t="n">
         <v>45999</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -7362,7 +7368,7 @@
         <f>IF(F27="","",E27*F27)</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F27,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F27)</f>
         <v/>
       </c>
@@ -7380,7 +7386,7 @@
       <c r="A28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="7" t="n">
         <v>45999</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -7403,7 +7409,7 @@
         <f>IF(F28="","",E28*F28)</f>
         <v/>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F28,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F28)</f>
         <v/>
       </c>
@@ -7421,7 +7427,7 @@
       <c r="A29" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="7" t="n">
         <v>46011</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -7462,7 +7468,7 @@
       <c r="A30" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="7" t="n">
         <v>46011</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -7503,7 +7509,7 @@
       <c r="A31" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="7" t="n">
         <v>46011</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -7526,7 +7532,7 @@
         <f>IF(F31="","",E31*F31)</f>
         <v/>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F31,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F31)</f>
         <v/>
       </c>
@@ -7544,7 +7550,7 @@
       <c r="A32" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -7567,7 +7573,7 @@
         <f>IF(F32="","",E32*F32)</f>
         <v/>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F32,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F32)</f>
         <v/>
       </c>
@@ -7585,7 +7591,7 @@
       <c r="A33" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -7608,7 +7614,7 @@
         <f>IF(F33="","",E33*F33)</f>
         <v/>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="8">
         <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F33,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F33)</f>
         <v/>
       </c>
@@ -7626,7 +7632,7 @@
       <c r="A34" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -7649,7 +7655,7 @@
         <f>IF(F34="","",E34*F34)</f>
         <v/>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F34,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F34)</f>
         <v/>
       </c>
@@ -7667,7 +7673,7 @@
       <c r="A35" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -7708,7 +7714,7 @@
       <c r="A36" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7749,7 +7755,7 @@
       <c r="A37" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="8" t="n">
+      <c r="B37" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -7772,7 +7778,7 @@
         <f>IF(F37="","",E37*F37)</f>
         <v/>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F37,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F37)</f>
         <v/>
       </c>
@@ -7790,7 +7796,7 @@
       <c r="A38" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B38" s="7" t="n">
         <v>46026</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7831,7 +7837,7 @@
       <c r="A39" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B39" s="7" t="n">
         <v>46029</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -7872,7 +7878,7 @@
       <c r="A40" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="8" t="n">
+      <c r="B40" s="7" t="n">
         <v>46029</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7895,7 +7901,7 @@
         <f>IF(F40="","",E40*F40)</f>
         <v/>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="8">
         <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F40,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F40)</f>
         <v/>
       </c>
@@ -7913,7 +7919,7 @@
       <c r="A41" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" s="7" t="n">
         <v>46029</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -7936,7 +7942,7 @@
         <f>IF(F41="","",E41*F41)</f>
         <v/>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="8">
         <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F41,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F41)</f>
         <v/>
       </c>
@@ -7954,7 +7960,7 @@
       <c r="A42" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="8" t="n">
+      <c r="B42" s="7" t="n">
         <v>46033</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7995,7 +8001,7 @@
       <c r="A43" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="8" t="n">
+      <c r="B43" s="7" t="n">
         <v>46040</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -8018,7 +8024,7 @@
         <f>IF(F43="","",E43*F43)</f>
         <v/>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="8">
         <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F43,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F43)</f>
         <v/>
       </c>
@@ -8036,7 +8042,7 @@
       <c r="A44" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="8" t="n">
+      <c r="B44" s="7" t="n">
         <v>46042</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8059,7 +8065,7 @@
         <f>IF(F44="","",E44*F44)</f>
         <v/>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="8">
         <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F44,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F44)</f>
         <v/>
       </c>
@@ -8077,7 +8083,7 @@
       <c r="A45" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B45" s="7" t="n">
         <v>46042</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -8100,7 +8106,7 @@
         <f>IF(F45="","",E45*F45)</f>
         <v/>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="8">
         <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F45,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F45)</f>
         <v/>
       </c>
@@ -8118,7 +8124,7 @@
       <c r="A46" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="8" t="n">
+      <c r="B46" s="7" t="n">
         <v>46042</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8141,7 +8147,7 @@
         <f>IF(F46="","",E46*F46)</f>
         <v/>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="8">
         <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F46,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F46)</f>
         <v/>
       </c>
@@ -8159,7 +8165,7 @@
       <c r="A47" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="8" t="n">
+      <c r="B47" s="7" t="n">
         <v>46042</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -8182,7 +8188,7 @@
         <f>IF(F47="","",E47*F47)</f>
         <v/>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F47,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F47)</f>
         <v/>
       </c>
@@ -8200,7 +8206,7 @@
       <c r="A48" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="8" t="n">
+      <c r="B48" s="7" t="n">
         <v>46042</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -8223,7 +8229,7 @@
         <f>IF(F48="","",E48*F48)</f>
         <v/>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="8">
         <f>IFERROR(IF(VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F48,VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F48)</f>
         <v/>
       </c>
@@ -8241,7 +8247,7 @@
       <c r="A49" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="8" t="n">
+      <c r="B49" s="7" t="n">
         <v>46042</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -8264,7 +8270,7 @@
         <f>IF(F49="","",E49*F49)</f>
         <v/>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F49,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F49)</f>
         <v/>
       </c>
@@ -8282,7 +8288,7 @@
       <c r="A50" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="8" t="n">
+      <c r="B50" s="7" t="n">
         <v>46060</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -8305,7 +8311,7 @@
         <f>IF(F50="","",E50*F50)</f>
         <v/>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F50,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F50)</f>
         <v/>
       </c>
@@ -8323,7 +8329,7 @@
       <c r="A51" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="8" t="n">
+      <c r="B51" s="7" t="n">
         <v>46060</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8346,7 +8352,7 @@
         <f>IF(F51="","",E51*F51)</f>
         <v/>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="8">
         <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F51,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F51)</f>
         <v/>
       </c>
@@ -8364,7 +8370,7 @@
       <c r="A52" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="8" t="n">
+      <c r="B52" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8387,7 +8393,7 @@
         <f>IF(F52="","",E52*F52)</f>
         <v/>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F52,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F52)</f>
         <v/>
       </c>
@@ -8405,7 +8411,7 @@
       <c r="A53" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="8" t="n">
+      <c r="B53" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8428,7 +8434,7 @@
         <f>IF(F53="","",E53*F53)</f>
         <v/>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F53,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F53)</f>
         <v/>
       </c>
@@ -8446,7 +8452,7 @@
       <c r="A54" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="8" t="n">
+      <c r="B54" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8469,7 +8475,7 @@
         <f>IF(F54="","",E54*F54)</f>
         <v/>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="8">
         <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F54,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F54)</f>
         <v/>
       </c>
@@ -8487,7 +8493,7 @@
       <c r="A55" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="8" t="n">
+      <c r="B55" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8510,7 +8516,7 @@
         <f>IF(F55="","",E55*F55)</f>
         <v/>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="8">
         <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F55,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F55)</f>
         <v/>
       </c>
@@ -8528,7 +8534,7 @@
       <c r="A56" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="8" t="n">
+      <c r="B56" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8551,7 +8557,7 @@
         <f>IF(F56="","",E56*F56)</f>
         <v/>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="8">
         <f>IFERROR(IF(VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F56,VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F56)</f>
         <v/>
       </c>
@@ -8569,7 +8575,7 @@
       <c r="A57" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="8" t="n">
+      <c r="B57" s="7" t="n">
         <v>46064</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8592,7 +8598,7 @@
         <f>IF(F57="","",E57*F57)</f>
         <v/>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="8">
         <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F57,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F57)</f>
         <v/>
       </c>
@@ -8610,7 +8616,7 @@
       <c r="A58" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="8" t="n">
+      <c r="B58" s="7" t="n">
         <v>46068</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -8651,7 +8657,7 @@
       <c r="A59" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="8" t="n">
+      <c r="B59" s="7" t="n">
         <v>46068</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -8674,7 +8680,7 @@
         <f>IF(F59="","",E59*F59)</f>
         <v/>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="8">
         <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F59,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F59)</f>
         <v/>
       </c>
@@ -8692,7 +8698,7 @@
       <c r="A60" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="8" t="n">
+      <c r="B60" s="7" t="n">
         <v>46068</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -8733,7 +8739,7 @@
       <c r="A61" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="8" t="n">
+      <c r="B61" s="7" t="n">
         <v>46068</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -8756,7 +8762,7 @@
         <f>IF(F61="","",E61*F61)</f>
         <v/>
       </c>
-      <c r="H61" s="9">
+      <c r="H61" s="8">
         <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F61,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F61)</f>
         <v/>
       </c>
@@ -8774,7 +8780,7 @@
       <c r="A62" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="8" t="n">
+      <c r="B62" s="7" t="n">
         <v>46104</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -8797,7 +8803,7 @@
         <f>IF(F62="","",E62*F62)</f>
         <v/>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="8">
         <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F62,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F62)</f>
         <v/>
       </c>
@@ -8815,7 +8821,7 @@
       <c r="A63" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="8" t="n">
+      <c r="B63" s="7" t="n">
         <v>46104</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -8856,7 +8862,7 @@
       <c r="A64" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="8" t="n">
+      <c r="B64" s="7" t="n">
         <v>46104</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -8879,7 +8885,7 @@
         <f>IF(F64="","",E64*F64)</f>
         <v/>
       </c>
-      <c r="H64" s="9">
+      <c r="H64" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F64,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F64)</f>
         <v/>
       </c>
@@ -8897,7 +8903,7 @@
       <c r="A65" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="8" t="n">
+      <c r="B65" s="7" t="n">
         <v>46120</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -8938,7 +8944,7 @@
       <c r="A66" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="8" t="n">
+      <c r="B66" s="7" t="n">
         <v>46121</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -8979,7 +8985,7 @@
       <c r="A67" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="8" t="n">
+      <c r="B67" s="7" t="n">
         <v>46121</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -9020,7 +9026,7 @@
       <c r="A68" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="8" t="n">
+      <c r="B68" s="7" t="n">
         <v>46121</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -9043,7 +9049,7 @@
         <f>IF(F68="","",E68*F68)</f>
         <v/>
       </c>
-      <c r="H68" s="9">
+      <c r="H68" s="8">
         <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F68,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F68)</f>
         <v/>
       </c>
@@ -9061,7 +9067,7 @@
       <c r="A69" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="8" t="n">
+      <c r="B69" s="7" t="n">
         <v>46121</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -9102,7 +9108,7 @@
       <c r="A70" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B70" s="7" t="n">
         <v>46123</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -9125,7 +9131,7 @@
         <f>IF(F70="","",E70*F70)</f>
         <v/>
       </c>
-      <c r="H70" s="9">
+      <c r="H70" s="8">
         <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F70,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F70)</f>
         <v/>
       </c>
@@ -9143,7 +9149,7 @@
       <c r="A71" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="8" t="n">
+      <c r="B71" s="7" t="n">
         <v>46123</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -9184,7 +9190,7 @@
       <c r="A72" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="8" t="n">
+      <c r="B72" s="7" t="n">
         <v>46127</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -9225,7 +9231,7 @@
       <c r="A73" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="8" t="n">
+      <c r="B73" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -9266,7 +9272,7 @@
       <c r="A74" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="8" t="n">
+      <c r="B74" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -9307,7 +9313,7 @@
       <c r="A75" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="8" t="n">
+      <c r="B75" s="7" t="n">
         <v>46144</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -9348,7 +9354,7 @@
       <c r="A76" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="8" t="n">
+      <c r="B76" s="7" t="n">
         <v>46144</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -9389,7 +9395,7 @@
       <c r="A77" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="8" t="n">
+      <c r="B77" s="7" t="n">
         <v>46147</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -9430,7 +9436,7 @@
       <c r="A78" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="8" t="n">
+      <c r="B78" s="7" t="n">
         <v>46147</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -9453,7 +9459,7 @@
         <f>IF(F78="","",E78*F78)</f>
         <v/>
       </c>
-      <c r="H78" s="9">
+      <c r="H78" s="8">
         <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F78,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F78)</f>
         <v/>
       </c>
@@ -9471,7 +9477,7 @@
       <c r="A79" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="8" t="n">
+      <c r="B79" s="7" t="n">
         <v>46160</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -9512,7 +9518,7 @@
       <c r="A80" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="8" t="n">
+      <c r="B80" s="7" t="n">
         <v>46163</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -9553,7 +9559,7 @@
       <c r="A81" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="8" t="n">
+      <c r="B81" s="7" t="n">
         <v>46163</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -9594,7 +9600,7 @@
       <c r="A82" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="8" t="n">
+      <c r="B82" s="7" t="n">
         <v>46184</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -9635,7 +9641,7 @@
       <c r="A83" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="8" t="n">
+      <c r="B83" s="7" t="n">
         <v>46184</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -9676,7 +9682,7 @@
       <c r="A84" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="8" t="n">
+      <c r="B84" s="7" t="n">
         <v>46184</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -9717,7 +9723,7 @@
       <c r="A85" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="8" t="n">
+      <c r="B85" s="7" t="n">
         <v>46184</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -9758,7 +9764,7 @@
       <c r="A86" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="8" t="n">
+      <c r="B86" s="7" t="n">
         <v>46184</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -9799,7 +9805,7 @@
       <c r="A87" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="8" t="n">
+      <c r="B87" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -9840,7 +9846,7 @@
       <c r="A88" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="8" t="n">
+      <c r="B88" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -9881,7 +9887,7 @@
       <c r="A89" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="8" t="n">
+      <c r="B89" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -9904,7 +9910,7 @@
         <f>IF(F89="","",E89*F89)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
+      <c r="H89" s="8">
         <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F89,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F89)</f>
         <v/>
       </c>
@@ -9922,7 +9928,7 @@
       <c r="A90" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="8" t="n">
+      <c r="B90" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -9945,7 +9951,7 @@
         <f>IF(F90="","",E90*F90)</f>
         <v/>
       </c>
-      <c r="H90" s="9">
+      <c r="H90" s="8">
         <f>IFERROR(IF(VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F90,VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F90)</f>
         <v/>
       </c>
@@ -9963,7 +9969,7 @@
       <c r="A91" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="8" t="n">
+      <c r="B91" s="7" t="n">
         <v>46197</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -9986,7 +9992,7 @@
         <f>IF(F91="","",E91*F91)</f>
         <v/>
       </c>
-      <c r="H91" s="9">
+      <c r="H91" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F91,VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F91)</f>
         <v/>
       </c>
@@ -10004,7 +10010,7 @@
       <c r="A92" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="8" t="n">
+      <c r="B92" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -10045,7 +10051,7 @@
       <c r="A93" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="8" t="n">
+      <c r="B93" s="7" t="n">
         <v>46190</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -10068,7 +10074,7 @@
         <f>IF(F93="","",E93*F93)</f>
         <v/>
       </c>
-      <c r="H93" s="9">
+      <c r="H93" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F93,VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F93)</f>
         <v/>
       </c>
@@ -10086,7 +10092,7 @@
       <c r="A94" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="8" t="n">
+      <c r="B94" s="7" t="n">
         <v>46195</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10109,7 +10115,7 @@
         <f>IF(F94="","",E94*F94)</f>
         <v/>
       </c>
-      <c r="H94" s="9">
+      <c r="H94" s="8">
         <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F94,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F94)</f>
         <v/>
       </c>
@@ -10127,7 +10133,7 @@
       <c r="A95" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="8" t="n">
+      <c r="B95" s="7" t="n">
         <v>46200</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10168,7 +10174,7 @@
       <c r="A96" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="8" t="n">
+      <c r="B96" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10209,7 +10215,7 @@
       <c r="A97" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="8" t="n">
+      <c r="B97" s="7" t="n">
         <v>46205</v>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10250,7 +10256,7 @@
       <c r="A98" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="8" t="n">
+      <c r="B98" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -10291,7 +10297,7 @@
       <c r="A99" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="8" t="n">
+      <c r="B99" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -10314,7 +10320,7 @@
         <f>IF(F99="","",E99*F99)</f>
         <v/>
       </c>
-      <c r="H99" s="9">
+      <c r="H99" s="8">
         <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F99,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F99)</f>
         <v/>
       </c>
@@ -10332,7 +10338,7 @@
       <c r="A100" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="8" t="n">
+      <c r="B100" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -10355,7 +10361,7 @@
         <f>IF(F100="","",E100*F100)</f>
         <v/>
       </c>
-      <c r="H100" s="9">
+      <c r="H100" s="8">
         <f>IFERROR(IF(VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F100,VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F100)</f>
         <v/>
       </c>
@@ -10373,7 +10379,7 @@
       <c r="A101" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="8" t="n">
+      <c r="B101" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -10414,7 +10420,7 @@
       <c r="A102" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="8" t="n">
+      <c r="B102" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -10455,7 +10461,7 @@
       <c r="A103" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="B103" s="8" t="n">
+      <c r="B103" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -10496,7 +10502,7 @@
       <c r="A104" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="B104" s="8" t="n">
+      <c r="B104" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -10519,7 +10525,7 @@
         <f>IF(F104="","",E104*F104)</f>
         <v/>
       </c>
-      <c r="H104" s="9">
+      <c r="H104" s="8">
         <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F104,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F104)</f>
         <v/>
       </c>
@@ -10537,7 +10543,7 @@
       <c r="A105" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="B105" s="8" t="n">
+      <c r="B105" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -10560,7 +10566,7 @@
         <f>IF(F105="","",E105*F105)</f>
         <v/>
       </c>
-      <c r="H105" s="9">
+      <c r="H105" s="8">
         <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F105,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F105)</f>
         <v/>
       </c>
@@ -10578,7 +10584,7 @@
       <c r="A106" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="8" t="n">
+      <c r="B106" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -10601,7 +10607,7 @@
         <f>IF(F106="","",E106*F106)</f>
         <v/>
       </c>
-      <c r="H106" s="9">
+      <c r="H106" s="8">
         <f>IFERROR(IF(VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F106,VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F106)</f>
         <v/>
       </c>
@@ -10619,7 +10625,7 @@
       <c r="A107" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="8" t="n">
+      <c r="B107" s="7" t="n">
         <v>46229</v>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -10660,7 +10666,7 @@
       <c r="A108" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="8" t="n">
+      <c r="B108" s="7" t="n">
         <v>46229</v>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -10701,7 +10707,7 @@
       <c r="A109" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="8" t="n">
+      <c r="B109" s="7" t="n">
         <v>46229</v>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -10724,7 +10730,7 @@
         <f>IF(F109="","",E109*F109)</f>
         <v/>
       </c>
-      <c r="H109" s="9">
+      <c r="H109" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F109,VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F109)</f>
         <v/>
       </c>
@@ -10742,7 +10748,7 @@
       <c r="A110" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="B110" s="8" t="n">
+      <c r="B110" s="7" t="n">
         <v>46229</v>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -10765,7 +10771,7 @@
         <f>IF(F110="","",E110*F110)</f>
         <v/>
       </c>
-      <c r="H110" s="9">
+      <c r="H110" s="8">
         <f>IFERROR(IF(VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F110,VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F110)</f>
         <v/>
       </c>
@@ -10783,7 +10789,7 @@
       <c r="A111" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="8" t="n">
+      <c r="B111" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -10806,7 +10812,7 @@
         <f>IF(F111="","",E111*F111)</f>
         <v/>
       </c>
-      <c r="H111" s="9">
+      <c r="H111" s="8">
         <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F111,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F111)</f>
         <v/>
       </c>
@@ -10828,7 +10834,7 @@
       <c r="A112" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="B112" s="8" t="n">
+      <c r="B112" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -10851,7 +10857,7 @@
         <f>IF(F112="","",E112*F112)</f>
         <v/>
       </c>
-      <c r="H112" s="9">
+      <c r="H112" s="8">
         <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F112,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F112)</f>
         <v/>
       </c>
@@ -10873,7 +10879,7 @@
       <c r="A113" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="8" t="n">
+      <c r="B113" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -10896,7 +10902,7 @@
         <f>IF(F113="","",E113*F113)</f>
         <v/>
       </c>
-      <c r="H113" s="9">
+      <c r="H113" s="8">
         <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F113,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F113)</f>
         <v/>
       </c>
@@ -10918,7 +10924,7 @@
       <c r="A114" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="8" t="n">
+      <c r="B114" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -10941,7 +10947,7 @@
         <f>IF(F114="","",E114*F114)</f>
         <v/>
       </c>
-      <c r="H114" s="9">
+      <c r="H114" s="8">
         <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F114,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F114)</f>
         <v/>
       </c>
@@ -10963,7 +10969,7 @@
       <c r="A115" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="B115" s="8" t="n">
+      <c r="B115" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -10986,7 +10992,7 @@
         <f>IF(F115="","",E115*F115)</f>
         <v/>
       </c>
-      <c r="H115" s="9">
+      <c r="H115" s="8">
         <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F115,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F115)</f>
         <v/>
       </c>
@@ -11008,7 +11014,7 @@
       <c r="A116" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="8" t="n">
+      <c r="B116" s="7" t="n">
         <v>46214</v>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -11031,7 +11037,7 @@
         <f>IF(F116="","",E116*F116)</f>
         <v/>
       </c>
-      <c r="H116" s="9">
+      <c r="H116" s="8">
         <f>IFERROR(IF(VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F116,VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F116)</f>
         <v/>
       </c>
@@ -11053,7 +11059,7 @@
       <c r="A117" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="B117" s="8" t="n">
+      <c r="B117" s="7" t="n">
         <v>46104</v>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -11076,7 +11082,7 @@
         <f>IF(F117="","",E117*F117)</f>
         <v/>
       </c>
-      <c r="H117" s="9">
+      <c r="H117" s="8">
         <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F117,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F117)</f>
         <v/>
       </c>
@@ -11098,7 +11104,7 @@
       <c r="A118" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="8" t="n">
+      <c r="B118" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -11121,7 +11127,7 @@
         <f>IF(F118="","",E118*F118)</f>
         <v/>
       </c>
-      <c r="H118" s="9">
+      <c r="H118" s="8">
         <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F118,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F118)</f>
         <v/>
       </c>
@@ -11143,7 +11149,7 @@
       <c r="A119" s="4" t="n">
         <v>117</v>
       </c>
-      <c r="B119" s="8" t="n">
+      <c r="B119" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -11166,7 +11172,7 @@
         <f>IF(F119="","",E119*F119)</f>
         <v/>
       </c>
-      <c r="H119" s="9">
+      <c r="H119" s="8">
         <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F119,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F119)</f>
         <v/>
       </c>
@@ -11188,7 +11194,7 @@
       <c r="A120" s="4" t="n">
         <v>118</v>
       </c>
-      <c r="B120" s="8" t="n">
+      <c r="B120" s="7" t="n">
         <v>46057</v>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -11211,7 +11217,7 @@
         <f>IF(F120="","",E120*F120)</f>
         <v/>
       </c>
-      <c r="H120" s="9">
+      <c r="H120" s="8">
         <f>IFERROR(IF(VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F120,VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F120)</f>
         <v/>
       </c>
@@ -11233,7 +11239,7 @@
       <c r="A121" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="B121" s="8" t="n">
+      <c r="B121" s="7" t="n">
         <v>46163</v>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -11275,33 +11281,33 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="n"/>
-      <c r="B122" s="10" t="n"/>
-      <c r="C122" s="10" t="n"/>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E122" s="12">
+      <c r="E122" s="11">
         <f>SUM(E3:E121)</f>
         <v/>
       </c>
-      <c r="F122" s="10" t="n"/>
-      <c r="G122" s="12">
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="11">
         <f>SUM(G3:G121)</f>
         <v/>
       </c>
-      <c r="H122" s="10" t="n"/>
-      <c r="I122" s="12">
+      <c r="H122" s="9" t="n"/>
+      <c r="I122" s="11">
         <f>SUM(I3:I121)</f>
         <v/>
       </c>
-      <c r="J122" s="12">
+      <c r="J122" s="11">
         <f>SUM(J3:J121)</f>
         <v/>
       </c>
-      <c r="K122" s="10" t="n"/>
+      <c r="K122" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11398,7 +11404,7 @@
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <v>45874</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11421,7 +11427,7 @@
         <f>IF(F3="","",E3*F3)</f>
         <v/>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F3,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F3)</f>
         <v/>
       </c>
@@ -11443,7 +11449,7 @@
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <v>45874</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11466,7 +11472,7 @@
         <f>IF(F4="","",E4*F4)</f>
         <v/>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F4,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F4)</f>
         <v/>
       </c>
@@ -11488,7 +11494,7 @@
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>45874</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11511,7 +11517,7 @@
         <f>IF(F5="","",E5*F5)</f>
         <v/>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F5,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F5)</f>
         <v/>
       </c>
@@ -11533,7 +11539,7 @@
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>45874</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11556,7 +11562,7 @@
         <f>IF(F6="","",E6*F6)</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F6,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F6)</f>
         <v/>
       </c>
@@ -11578,7 +11584,7 @@
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>45874</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11601,7 +11607,7 @@
         <f>IF(F7="","",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F7,VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F7)</f>
         <v/>
       </c>
@@ -11623,7 +11629,7 @@
       <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>45874</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -11646,7 +11652,7 @@
         <f>IF(F8="","",E8*F8)</f>
         <v/>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F8,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F8)</f>
         <v/>
       </c>
@@ -11668,7 +11674,7 @@
       <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11691,7 +11697,7 @@
         <f>IF(F9="","",E9*F9)</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F9,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F9)</f>
         <v/>
       </c>
@@ -11709,7 +11715,7 @@
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11732,7 +11738,7 @@
         <f>IF(F10="","",E10*F10)</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <f>IFERROR(IF(VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F10,VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F10)</f>
         <v/>
       </c>
@@ -11750,7 +11756,7 @@
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11773,7 +11779,7 @@
         <f>IF(F11="","",E11*F11)</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F11,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F11)</f>
         <v/>
       </c>
@@ -11791,7 +11797,7 @@
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11814,7 +11820,7 @@
         <f>IF(F12="","",E12*F12)</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F12,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F12)</f>
         <v/>
       </c>
@@ -11832,7 +11838,7 @@
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>45969</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11855,7 +11861,7 @@
         <f>IF(F13="","",E13*F13)</f>
         <v/>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F13,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F13)</f>
         <v/>
       </c>
@@ -11873,7 +11879,7 @@
       <c r="A14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="7" t="n">
         <v>45981</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11914,7 +11920,7 @@
       <c r="A15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="7" t="n">
         <v>45981</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11937,7 +11943,7 @@
         <f>IF(F15="","",E15*F15)</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F15,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F15)</f>
         <v/>
       </c>
@@ -11955,7 +11961,7 @@
       <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="7" t="n">
         <v>46002</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11978,7 +11984,7 @@
         <f>IF(F16="","",E16*F16)</f>
         <v/>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F16,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F16)</f>
         <v/>
       </c>
@@ -11996,7 +12002,7 @@
       <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="7" t="n">
         <v>46025</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -12019,7 +12025,7 @@
         <f>IF(F17="","",E17*F17)</f>
         <v/>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F17,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F17)</f>
         <v/>
       </c>
@@ -12037,7 +12043,7 @@
       <c r="A18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="7" t="n">
         <v>46025</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -12060,7 +12066,7 @@
         <f>IF(F18="","",E18*F18)</f>
         <v/>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F18,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F18)</f>
         <v/>
       </c>
@@ -12078,7 +12084,7 @@
       <c r="A19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="7" t="n">
         <v>46025</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -12101,7 +12107,7 @@
         <f>IF(F19="","",E19*F19)</f>
         <v/>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F19,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F19)</f>
         <v/>
       </c>
@@ -12119,7 +12125,7 @@
       <c r="A20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>46025</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -12142,7 +12148,7 @@
         <f>IF(F20="","",E20*F20)</f>
         <v/>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F20,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F20)</f>
         <v/>
       </c>
@@ -12180,7 +12186,7 @@
         <f>IF(F21="","",E21*F21)</f>
         <v/>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F21,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F21)</f>
         <v/>
       </c>
@@ -12222,7 +12228,7 @@
         <f>IF(F22="","",E22*F22)</f>
         <v/>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F22,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F22)</f>
         <v/>
       </c>
@@ -12264,7 +12270,7 @@
         <f>IF(F23="","",E23*F23)</f>
         <v/>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F23,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F23)</f>
         <v/>
       </c>
@@ -12306,7 +12312,7 @@
         <f>IF(F24="","",E24*F24)</f>
         <v/>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F24,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F24)</f>
         <v/>
       </c>
@@ -12348,7 +12354,7 @@
         <f>IF(F25="","",E25*F25)</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F25,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F25)</f>
         <v/>
       </c>
@@ -12390,7 +12396,7 @@
         <f>IF(F26="","",E26*F26)</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="8">
         <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F26,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F26)</f>
         <v/>
       </c>
@@ -12432,7 +12438,7 @@
         <f>IF(F27="","",E27*F27)</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F27,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F27)</f>
         <v/>
       </c>
@@ -12454,7 +12460,7 @@
       <c r="A28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="7" t="n">
         <v>46231</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12477,7 +12483,7 @@
         <f>IF(F28="","",E28*F28)</f>
         <v/>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F28,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F28)</f>
         <v/>
       </c>
@@ -12499,7 +12505,7 @@
       <c r="A29" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="7" t="n">
         <v>45976</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12541,33 +12547,33 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="11">
         <f>SUM(E3:E29)</f>
         <v/>
       </c>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="12">
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="11">
         <f>SUM(G3:G29)</f>
         <v/>
       </c>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="12">
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="11">
         <f>SUM(I3:I29)</f>
         <v/>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="11">
         <f>SUM(J3:J29)</f>
         <v/>
       </c>
-      <c r="K30" s="10" t="n"/>
+      <c r="K30" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12664,7 +12670,7 @@
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <v>45845</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -12706,7 +12712,7 @@
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <v>45845</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -12748,7 +12754,7 @@
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>45845</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -12790,7 +12796,7 @@
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>45845</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -12832,7 +12838,7 @@
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>45845</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -12874,7 +12880,7 @@
       <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>45845</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -12916,7 +12922,7 @@
       <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>45854</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -12958,7 +12964,7 @@
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>45854</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -13000,7 +13006,7 @@
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>45856</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -13042,7 +13048,7 @@
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>45856</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -13084,7 +13090,7 @@
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>45856</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -13123,33 +13129,33 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="11">
         <f>SUM(E3:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="12">
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="11">
         <f>SUM(G3:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="12">
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="11">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <f>SUM(J3:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="10" t="n"/>
+      <c r="K14" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13238,7 +13244,7 @@
           <t>RNT-2166</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="7" t="n">
         <v>45887</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -13249,7 +13255,7 @@
       <c r="F3" s="4" t="n">
         <v>7475</v>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="12" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
@@ -13270,7 +13276,7 @@
           <t>RNT-2141</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="7" t="n">
         <v>45909</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -13281,7 +13287,7 @@
       <c r="F4" s="4" t="n">
         <v>8855</v>
       </c>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="12" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
@@ -13302,7 +13308,7 @@
           <t>RNT-3077</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -13313,7 +13319,7 @@
       <c r="F5" s="4" t="n">
         <v>4305.03</v>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="12" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
@@ -13334,7 +13340,7 @@
           <t>RNT-3346</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7" t="n">
         <v>46016</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -13345,7 +13351,7 @@
       <c r="F6" s="4" t="n">
         <v>1765.25</v>
       </c>
-      <c r="G6" s="7" t="n"/>
+      <c r="G6" s="12" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
@@ -13366,7 +13372,7 @@
           <t>RNP-2297</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>45926</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -13377,7 +13383,7 @@
       <c r="F7" s="4" t="n">
         <v>5433.75</v>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="12" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
@@ -13398,7 +13404,7 @@
           <t>RNP-2427</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>45938</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -13409,7 +13415,7 @@
       <c r="F8" s="4" t="n">
         <v>7078.25</v>
       </c>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="12" t="n"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
@@ -13430,7 +13436,7 @@
           <t>RNP-1787</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>45873</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -13441,7 +13447,7 @@
       <c r="F9" s="4" t="n">
         <v>20872.5</v>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="12" t="n"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,7 +119,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -561,15 +560,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'مسحوبات نسما من الرياض'!G122</f>
+        <f>'مسحوبات نسما من الرياض'!G128</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'مسحوبات نسما من الرياض'!I122</f>
+        <f>'مسحوبات نسما من الرياض'!I128</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'مسحوبات نسما من الرياض'!J122</f>
+        <f>'مسحوبات نسما من الرياض'!J128</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -633,11 +632,11 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!F10</f>
+        <f>'سندات بدون تفصيل أصناف'!F8</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!G10</f>
+        <f>'سندات بدون تفصيل أصناف'!G8</f>
         <v/>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -678,19 +677,26 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>4) الترحيل من الرياض إلى تبوك = مديونية على أبو مازن، ومن تبوك إلى الرياض = دعم تشغيلي من أبو مازن.</t>
+          <t>7) لا تُطبق الضريبة على أي تحويل بين المزرعتين أو مسحوبات لأي من الشريكين – كل القيم قبل الضريبة (معاملات داخلية بدون فاتورة).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>5) أُلغي PO-213 (بيتونيا 6,000) وخُصمت 17,900 فينكا مفقودة من الطلب 58991، وسلفة رائد الخير (ISV-0075) مستبعدة.</t>
+          <t>4) الترحيل من الرياض إلى تبوك = مديونية على أبو مازن، ومن تبوك إلى الرياض = دعم تشغيلي من أبو مازن.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>5) أُلغي PO-213 (بيتونيا 6,000) وخُصمت 17,900 فينكا مفقودة من الطلب 58991، وسلفة رائد الخير (ISV-0075) مستبعدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>6) تكاليف الشحن الخارجي لأوامر ما قبل الفترة تحمّلتها نسما (11,300) ولا تُحمّل على أي طرف.</t>
         </is>
@@ -1329,7 +1335,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>15425</v>
+        <v>16025</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0.7</v>
@@ -1850,7 +1856,7 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -2312,7 +2318,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>زهور جيرانيوم  هولندي مركن12 / زهور جيرانيوم هولندى مركن12 سم</t>
+          <t>زهور جيرانيوم  هولندي مركن12 / زهور جيرانيوم هولندى مركن12 سم / زهور جيرانيوم هولندي مركن 12</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2334,7 +2340,7 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1190</v>
+        <v>1295</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>3.45</v>
@@ -3015,7 +3021,7 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2420</v>
+        <v>2720</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>4</v>
@@ -3054,7 +3060,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
@@ -3175,7 +3181,7 @@
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>2362</v>
+        <v>2862</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>0.5</v>
@@ -6277,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11240,30 +11246,30 @@
         <v>119</v>
       </c>
       <c r="B121" s="7" t="n">
-        <v>46163</v>
+        <v>45992</v>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>طلب 58991 (#299/#301)</t>
+          <t>RNT-3077</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>زهور جيرانيوم هولندي مركن 12</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>-17900</v>
+        <v>105</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0.5</v>
+        <v>3.45</v>
       </c>
       <c r="G121" s="4">
         <f>IF(F121="","",E121*F121)</f>
         <v/>
       </c>
-      <c r="H121" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F121,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F121)</f>
+      <c r="H121" s="8">
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F121,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F121)</f>
         <v/>
       </c>
       <c r="I121" s="4">
@@ -11276,38 +11282,308 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
+          <t>أصناف من إذن الصرف المرسل (RAW OUT#65/#90) – السعر المسجل = سعر النظام التقريبي</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="7" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>RNT-3077</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>كمبوست 10 ك</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="4">
+        <f>IF(F122="","",E122*F122)</f>
+        <v/>
+      </c>
+      <c r="H122" s="8">
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F122,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F122)</f>
+        <v/>
+      </c>
+      <c r="I122" s="4">
+        <f>IF(H122="","",E122*H122)</f>
+        <v/>
+      </c>
+      <c r="J122" s="4">
+        <f>IF(OR(G122="",I122=""),"",G122-I122)</f>
+        <v/>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>أصناف من إذن الصرف المرسل (RAW OUT#65/#90) – السعر المسجل = سعر النظام التقريبي</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>RNT-3077</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>بيرلايت 100 لتر</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G123" s="4">
+        <f>IF(F123="","",E123*F123)</f>
+        <v/>
+      </c>
+      <c r="H123" s="8">
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F123,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F123)</f>
+        <v/>
+      </c>
+      <c r="I123" s="4">
+        <f>IF(H123="","",E123*H123)</f>
+        <v/>
+      </c>
+      <c r="J123" s="4">
+        <f>IF(OR(G123="",I123=""),"",G123-I123)</f>
+        <v/>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>أصناف من إذن الصرف المرسل (RAW OUT#65/#90) – السعر المسجل = سعر النظام التقريبي</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="7" t="n">
+        <v>46016</v>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>RNT-3346</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>زهور ماري جولد</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G124" s="4">
+        <f>IF(F124="","",E124*F124)</f>
+        <v/>
+      </c>
+      <c r="H124" s="4">
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F124,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F124)</f>
+        <v/>
+      </c>
+      <c r="I124" s="4">
+        <f>IF(H124="","",E124*H124)</f>
+        <v/>
+      </c>
+      <c r="J124" s="4">
+        <f>IF(OR(G124="",I124=""),"",G124-I124)</f>
+        <v/>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>أصناف من إذن الصرف المرسل (RAW OUT#65/#90) – السعر المسجل = سعر النظام التقريبي</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>46016</v>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>RNT-3346</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>كلانشو هولندي مركن 12</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" s="4">
+        <f>IF(F125="","",E125*F125)</f>
+        <v/>
+      </c>
+      <c r="H125" s="8">
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F125,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F125)</f>
+        <v/>
+      </c>
+      <c r="I125" s="4">
+        <f>IF(H125="","",E125*H125)</f>
+        <v/>
+      </c>
+      <c r="J125" s="4">
+        <f>IF(OR(G125="",I125=""),"",G125-I125)</f>
+        <v/>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>أصناف من إذن الصرف المرسل (RAW OUT#65/#90) – السعر المسجل = سعر النظام التقريبي</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>46016</v>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>RNT-3346</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>زهور ملفوف مركن 9</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G126" s="4">
+        <f>IF(F126="","",E126*F126)</f>
+        <v/>
+      </c>
+      <c r="H126" s="8">
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F126,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F126)</f>
+        <v/>
+      </c>
+      <c r="I126" s="4">
+        <f>IF(H126="","",E126*H126)</f>
+        <v/>
+      </c>
+      <c r="J126" s="4">
+        <f>IF(OR(G126="",I126=""),"",G126-I126)</f>
+        <v/>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>أصناف من إذن الصرف المرسل (RAW OUT#65/#90) – السعر المسجل = سعر النظام التقريبي</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>طلب 58991 (#299/#301)</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>-17900</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G127" s="4">
+        <f>IF(F127="","",E127*F127)</f>
+        <v/>
+      </c>
+      <c r="H127" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F127,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F127)</f>
+        <v/>
+      </c>
+      <c r="I127" s="4">
+        <f>IF(H127="","",E127*H127)</f>
+        <v/>
+      </c>
+      <c r="J127" s="4">
+        <f>IF(OR(G127="",I127=""),"",G127-I127)</f>
+        <v/>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
           <t>خصم كمية مرفوضة/مفقودة مع المناديب (حسب قرارك)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="n"/>
-      <c r="B122" s="9" t="n"/>
-      <c r="C122" s="9" t="n"/>
-      <c r="D122" s="10" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E122" s="11">
-        <f>SUM(E3:E121)</f>
-        <v/>
-      </c>
-      <c r="F122" s="9" t="n"/>
-      <c r="G122" s="11">
-        <f>SUM(G3:G121)</f>
-        <v/>
-      </c>
-      <c r="H122" s="9" t="n"/>
-      <c r="I122" s="11">
-        <f>SUM(I3:I121)</f>
-        <v/>
-      </c>
-      <c r="J122" s="11">
-        <f>SUM(J3:J121)</f>
-        <v/>
-      </c>
-      <c r="K122" s="9" t="n"/>
+      <c r="E128" s="11">
+        <f>SUM(E3:E127)</f>
+        <v/>
+      </c>
+      <c r="F128" s="9" t="n"/>
+      <c r="G128" s="11">
+        <f>SUM(G3:G127)</f>
+        <v/>
+      </c>
+      <c r="H128" s="9" t="n"/>
+      <c r="I128" s="11">
+        <f>SUM(I3:I127)</f>
+        <v/>
+      </c>
+      <c r="J128" s="11">
+        <f>SUM(J3:J127)</f>
+        <v/>
+      </c>
+      <c r="K128" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13168,7 +13444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13221,7 +13497,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>القيمة المعتمدة (يدوي)</t>
+          <t>القيمة بدون ضريبة</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -13255,10 +13531,13 @@
       <c r="F3" s="4" t="n">
         <v>7475</v>
       </c>
-      <c r="G3" s="12" t="n"/>
+      <c r="G3" s="4">
+        <f>ROUND(F3/1.15,2)</f>
+        <v/>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
+          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
         </is>
       </c>
     </row>
@@ -13287,10 +13566,13 @@
       <c r="F4" s="4" t="n">
         <v>8855</v>
       </c>
-      <c r="G4" s="12" t="n"/>
+      <c r="G4" s="4">
+        <f>ROUND(F4/1.15,2)</f>
+        <v/>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
+          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
         </is>
       </c>
     </row>
@@ -13305,24 +13587,27 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>RNT-3077</t>
+          <t>RNP-2297</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>45992</v>
+        <v>45926</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>TRANSACTIONS BETWEEN RIYADH-TABUK</t>
+          <t>NESMA ELSHARQ-PROJECTS</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4305.03</v>
-      </c>
-      <c r="G5" s="12" t="n"/>
+        <v>5433.75</v>
+      </c>
+      <c r="G5" s="4">
+        <f>ROUND(F5/1.15,2)</f>
+        <v/>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
+          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
         </is>
       </c>
     </row>
@@ -13337,24 +13622,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>RNT-3346</t>
+          <t>RNP-2427</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>46016</v>
+        <v>45938</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>TRANSACTIONS BETWEEN RIYADH-TABUK</t>
+          <t>NESMA ELSHARQ-PROJECTS</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1765.25</v>
-      </c>
-      <c r="G6" s="12" t="n"/>
+        <v>7078.25</v>
+      </c>
+      <c r="G6" s="4">
+        <f>ROUND(F6/1.15,2)</f>
+        <v/>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
+          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
         </is>
       </c>
     </row>
@@ -13369,103 +13657,42 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>RNP-2297</t>
+          <t>RNP-1787</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>45926</v>
+        <v>45873</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>NESMA ELSHARQ-PROJECTS</t>
+          <t>WHOLESALE DEPARTMENT RIYADH</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5433.75</v>
-      </c>
-      <c r="G7" s="12" t="n"/>
+        <v>20872.5</v>
+      </c>
+      <c r="G7" s="4">
+        <f>ROUND(F7/1.15,2)</f>
+        <v/>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
+          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>RNP-2427</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>45938</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>NESMA ELSHARQ-PROJECTS</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>7078.25</v>
-      </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>RNP-1787</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>WHOLESALE DEPARTMENT RIYADH</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>20872.5</v>
-      </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف أو اعتمد القيمة</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="F10" s="4">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="4">
-        <f>SUM(G3:G9)</f>
+      <c r="F8" s="4">
+        <f>SUM(F3:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>SUM(G3:G7)</f>
         <v/>
       </c>
     </row>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -560,15 +560,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'مسحوبات نسما من الرياض'!G128</f>
+        <f>'مسحوبات نسما من الرياض'!G129</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'مسحوبات نسما من الرياض'!I128</f>
+        <f>'مسحوبات نسما من الرياض'!I129</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'مسحوبات نسما من الرياض'!J128</f>
+        <f>'مسحوبات نسما من الرياض'!J129</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!F8</f>
+        <f>'سندات بدون تفصيل أصناف'!F7</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!G8</f>
+        <f>'سندات بدون تفصيل أصناف'!G7</f>
         <v/>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1023,17 +1023,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>فينكا ابيض</t>
+          <t>فينكا</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>فينكا أبيض</t>
+          <t>زهور فينكا</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
@@ -1046,11 +1046,11 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات قبل الفترة</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9000</v>
+        <v>33000</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>فينكا ابيض نقطه حمراء</t>
+          <t>فينكا ابيض</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>فينكا أبيض نقطة حمراء</t>
+          <t>فينكا أبيض</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3875</v>
+        <v>9000</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>فينكا احمر</t>
+          <t>فينكا ابيض نقطه حمراء</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>فينكا أحمر</t>
+          <t>فينكا أبيض نقطة حمراء</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>11000</v>
+        <v>3875</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>فينكا احمر بنقطه</t>
+          <t>فينكا احمر</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>فينكا أحمر بنقطة</t>
+          <t>فينكا أحمر</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>فينكا ازرق</t>
+          <t>فينكا احمر بنقطه</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>فينكا أزرق</t>
+          <t>فينكا أحمر بنقطة</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>فينكا روزا</t>
+          <t>فينكا ازرق</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>فينكا أزرق</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.5 / 0.55</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -1251,14 +1251,16 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات قبل الفترة</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>190390</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0.55</v>
+        <v>5000</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1267,17 +1269,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>فينكا مشمشي</t>
+          <t>فينكا روزا</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>فينكا مشمشي</t>
+          <t>زهور فينكا روزا</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5 / 0.55</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -1290,16 +1292,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات قبل الفترة</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>190390</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="16">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ماري جولد</t>
+          <t>فينكا مشمشي</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>زهور مارى جولد / زهور ماري جولد / مارى جولد</t>
+          <t>فينكا مشمشي</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.5 / 0.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -1331,14 +1331,16 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات قبل الفترة</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>16025</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0.7</v>
+        <v>5000</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1347,17 +1349,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ماري جولد فرنسي</t>
+          <t>ماري جولد</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>زهور ماري جولد فرنسى</t>
+          <t>زهور مارى جولد / زهور ماري جولد / مارى جولد</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5 / 0.7</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -1370,16 +1372,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>16025</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="18">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>موسميه</t>
+          <t>ماري جولد فرنسي</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>زهور موسمية (SEASONAL FLOWERS) / زهور موسمية – غير شامل التوصيل</t>
+          <t>زهور ماري جولد فرنسى</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات قبل الفترة</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>66000</v>
+        <v>250</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>هيبوستس</t>
+          <t>موسميه</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>زهور هيبوستس / زهور هيبوستس مركن9 سم / هيبوستس</t>
+          <t>زهور موسمية (SEASONAL FLOWERS) / زهور موسمية – غير شامل التوصيل</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.55 / 0.7 / 2.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
@@ -1452,14 +1452,16 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات قبل الفترة</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4575</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0.7</v>
+        <v>66000</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1468,37 +1470,37 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>اشجار تيسبيسيا 2- 3 متر</t>
+          <t>هيبوستس</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>أشجار تيسبيسيا 2-3 متر</t>
+          <t>زهور هيبوستس / زهور هيبوستس مركن9 سم / هيبوستس</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0.55 / 0.7 / 2.5</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>معتمد (قرارك)</t>
+          <t>موحد 0.50 (قرارك)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4</v>
+        <v>4575</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>60</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -1507,21 +1509,21 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقي مركن 12</t>
+          <t>اشجار تيسبيسيا 2- 3 متر</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقى مركن 12 / زهور اقحوان افريقى مركن12 سم / زهور اقحوان افريقي مركن 12</t>
+          <t>أشجار تيسبيسيا 2-3 متر</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>3.25</v>
+        <v>60</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1530,14 +1532,14 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>7010</v>
+        <v>4</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -1546,21 +1548,21 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقي مركن 9</t>
+          <t>اقحوان افريقي مركن 12</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>زهور اقحوان افريقي مركن 9 / زهور اقحوان افريقي مركن9 سم</t>
+          <t>اقحوان افريقى مركن 12 / زهور اقحوان افريقى مركن12 سم / زهور اقحوان افريقي مركن 12</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>1.5 / 2</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1573,10 +1575,10 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5975</v>
+        <v>7010</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="23">
@@ -1585,21 +1587,21 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>اقحوان افريقي هولندي مركن 12</t>
+          <t>اقحوان افريقي مركن 9</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>زهور اقحوان افريقي هولندي مركن 12</t>
+          <t>زهور اقحوان افريقي مركن 9 / زهور اقحوان افريقي مركن9 سم</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.5 / 2</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1608,16 +1610,14 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1875</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5975</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
@@ -1626,21 +1626,21 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>اكاسيا جلوكا من 1 - 2 متر</t>
+          <t>اقحوان افريقي هولندي مركن 12</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>اكاسيا جلوكا من 1 - 2 متر</t>
+          <t>زهور اقحوان افريقي هولندي مركن 12</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>172</v>
+        <v>1875</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -1667,21 +1667,21 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>اكاليفا</t>
+          <t>اكاسيا جلوكا من 1 - 2 متر</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>اكاليفا / اكاليفيا</t>
+          <t>اكاسيا جلوكا من 1 - 2 متر</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>اليسوم</t>
+          <t>اكاليفا</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>زهور اليسوم / زهور اليسوم مركن9 سم</t>
+          <t>اكاليفا / اكاليفيا</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1731,14 +1731,16 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5275</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0.5</v>
+        <v>120</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1747,21 +1749,21 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>بانستيم اخضر</t>
+          <t>اليسوم</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>بانستيم اخضر</t>
+          <t>زهور اليسوم / زهور اليسوم مركن9 سم</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -1770,16 +1772,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5275</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
@@ -1788,21 +1788,21 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>بوتنج سويل 70 لتر</t>
+          <t>بانستيم اخضر</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>بوتنج سويل 70 لتر</t>
+          <t>بانستيم اخضر</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>بيرلايت 100 لتر</t>
+          <t>بوتنج سويل 70 لتر</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>بيرلايت 100 لتر</t>
+          <t>بوتنج سويل 70 لتر</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1852,11 +1852,11 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>تجيل كروي مركن 9</t>
+          <t>بيرلايت 100 لتر</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>تجيل كروي مركن 9 سم</t>
+          <t>بيرلايت 100 لتر</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.9</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1893,11 +1893,11 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2400</v>
+        <v>225</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>تراديسكانتيا مركن 19 علاقي</t>
+          <t>تجيل كروي مركن 9</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>تراديسكانتيا مركن 19 علاقي</t>
+          <t>تجيل كروي مركن 9 سم</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>515</v>
+        <v>2400</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>تيكوماريا 50</t>
+          <t>تراديسكانتيا مركن 19 علاقي</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>تيكوماريا / تيكوماريا 50 سم / تيكوماريا50 سم</t>
+          <t>تراديسكانتيا مركن 19 علاقي</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2.5 / 4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -1975,14 +1975,16 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3530</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>4</v>
+        <v>515</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1991,21 +1993,21 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>جازانيا</t>
+          <t>تيكوماريا 50</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>زهور جازانيا</t>
+          <t>تيكوماريا / تيكوماريا 50 سم / تيكوماريا50 سم</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.5 / 4</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2014,14 +2016,14 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5525</v>
+        <v>3530</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2030,21 +2032,21 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>جهنميه بلدي 1 متر</t>
+          <t>جازانيا</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>جهنمية بلدي1 متر</t>
+          <t>زهور جازانيا</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2053,16 +2055,14 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5525</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>جهنميه بلدي 50</t>
+          <t>جهنميه بلدي 1 متر</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>جهنمية بلدى واحد عود 50سم / جهنمية بلدي 50 سم</t>
+          <t>جهنمية بلدي1 متر</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2.5 / 5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2094,11 +2094,11 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
@@ -2112,21 +2112,21 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>جهنميه تايلاندي مركن 25</t>
+          <t>جهنميه بلدي 50</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>جهنميه تايلاندى مركن 25</t>
+          <t>جهنمية بلدى واحد عود 50سم / جهنمية بلدي 50 سم</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2.5 / 5</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2135,11 +2135,11 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>جهنميه كرويه تايلندي صغير</t>
+          <t>جهنميه تايلاندي مركن 25</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>جهنمية كروية تايلندي صغير</t>
+          <t>جهنميه تايلاندى مركن 25</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
@@ -2194,21 +2194,21 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>جهنميه كرويه تايلندي كبير</t>
+          <t>جهنميه كرويه تايلندي صغير</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>جهنمية كروية تايلندي كبير</t>
+          <t>جهنمية كروية تايلندي صغير</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم مركن 12</t>
+          <t>جهنميه كرويه تايلندي كبير</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم مركن 12 / زهور جيرانيوم مركن 12 / زهور جيرانيوم مركن12 سم</t>
+          <t>جهنمية كروية تايلندي كبير</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3 / 3.75</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -2258,14 +2258,16 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>20355</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2274,21 +2276,21 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم مركن 9</t>
+          <t>جيرانيوم مركن 12</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>زهور جرانيوم مركن9 سم / زهور جيرانيوم مركن 9</t>
+          <t>جيرانيوم مركن 12 / زهور جيرانيوم مركن 12 / زهور جيرانيوم مركن12 سم</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>1.25 / 1.4 / 1.5</t>
+          <t>3 / 3.75</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -2301,10 +2303,10 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>41825</v>
+        <v>20355</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2313,21 +2315,21 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>جيرانيوم هولندي مركن 12</t>
+          <t>جيرانيوم مركن 9</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>زهور جيرانيوم  هولندي مركن12 / زهور جيرانيوم هولندى مركن12 سم / زهور جيرانيوم هولندي مركن 12</t>
+          <t>زهور جرانيوم مركن9 سم / زهور جيرانيوم مركن 9</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.45 / 3.75</t>
+          <t>1.25 / 1.4 / 1.5</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -2340,10 +2342,10 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1295</v>
+        <v>41825</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="42">
@@ -2352,21 +2354,21 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري ابيض لامع 1: 3</t>
+          <t>جيرانيوم هولندي مركن 12</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ابيض لامع / حجر ديكوري أبيض لامع 1:3 سم (10 كجم)</t>
+          <t>زهور جيرانيوم  هولندي مركن12 / زهور جيرانيوم هولندى مركن12 سم / زهور جيرانيوم هولندي مركن 12</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>18 / 25</t>
+          <t>3.45 / 3.75</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>18</v>
+        <v>3.45</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -2375,14 +2377,14 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>16</v>
+        <v>1295</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>25</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="43">
@@ -2391,21 +2393,21 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري ابيض مطفي 3: 5</t>
+          <t>حجر ديكوري ابيض لامع 1: 3</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكورى ابيض مطفى 3:5سم-10كجم / حجر ديكوري أبيض مطفي 3:5 سم (10 كجم)</t>
+          <t>ابيض لامع / حجر ديكوري أبيض لامع 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>10 / 13</t>
+          <t>18 / 25</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -2418,10 +2420,10 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1123</v>
+        <v>16</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -2430,21 +2432,21 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري احمر لامع 1: 3</t>
+          <t>حجر ديكوري ابيض مطفي 3: 5</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>احمر لامع / حجر ديكوري أحمر لامع 1:3 سم (10 كجم)</t>
+          <t>حجر ديكورى ابيض مطفى 3:5سم-10كجم / حجر ديكوري أبيض مطفي 3:5 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>18 / 25</t>
+          <t>10 / 13</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -2457,10 +2459,10 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>15</v>
+        <v>1123</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -2469,21 +2471,21 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري احمر مطفي</t>
+          <t>حجر ديكوري احمر لامع 1: 3</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>احمر مطفى</t>
+          <t>احمر لامع / حجر ديكوري أحمر لامع 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18 / 25</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2492,16 +2494,14 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -2510,21 +2510,21 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري اسود لامع 1: 3</t>
+          <t>حجر ديكوري احمر مطفي</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>اسود لامع / حجر ديكوري أسود لامع 1:3 سم (10 كجم)</t>
+          <t>احمر مطفى</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>18 / 25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -2533,14 +2533,16 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
+          <t>ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>25</v>
+        <v>70</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -2549,21 +2551,21 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>حجر ديكوري اصفر مطفي 1: 3</t>
+          <t>حجر ديكوري اسود لامع 1: 3</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>اصفر مطفى / حجر اصفر مطفى / حجر ديكوري أصفر مطفي 1:3 سم (10 كجم)</t>
+          <t>اسود لامع / حجر ديكوري أسود لامع 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>10 / 10.5 / 13</t>
+          <t>18 / 25</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -2572,14 +2574,14 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
@@ -2588,21 +2590,21 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>دورانتا اخضر</t>
+          <t>حجر ديكوري اصفر مطفي 1: 3</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>دورانتا أخضر / دورانتا اخضر</t>
+          <t>اصفر مطفى / حجر اصفر مطفى / حجر ديكوري أصفر مطفي 1:3 سم (10 كجم)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10 / 10.5 / 13</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -2611,16 +2613,14 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>202</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="49">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>رويليا</t>
+          <t>دورانتا اخضر</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>رويليا</t>
+          <t>دورانتا أخضر / دورانتا اخضر</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>سكندابسس مركن 19 علاقي</t>
+          <t>رويليا</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>سكندابسس مركن 19 علاقي</t>
+          <t>رويليا</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -2693,11 +2693,11 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>2300</v>
+        <v>600</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>سيسبانيا 1 - 2 متر</t>
+          <t>سكندابسس مركن 19 علاقي</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>سيسلبانيا 1 - 2 متر</t>
+          <t>سكندابسس مركن 19 علاقي</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>240</v>
+        <v>2300</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
@@ -2752,21 +2752,21 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>سينيراريا مركن 12</t>
+          <t>سيسبانيا 1 - 2 متر</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>زهور سينيراريا 12 / زهور سينيراريا مركن12 سم</t>
+          <t>سيسلبانيا 1 - 2 متر</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>2.5 / 5</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -2775,14 +2775,16 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>348</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>5</v>
+        <v>240</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -2791,21 +2793,21 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>فل بلدي</t>
+          <t>سينيراريا مركن 12</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>فل بلدى / فل بلدي</t>
+          <t>زهور سينيراريا 12 / زهور سينيراريا مركن12 سم</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5 / 5</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -2814,16 +2816,14 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>348</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -2832,21 +2832,21 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>فيكس بندا 50</t>
+          <t>فل بلدي</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>فيكس بندا 50 سم</t>
+          <t>فل بلدى / فل بلدي</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -2855,11 +2855,11 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
@@ -2873,21 +2873,21 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>قرنفل امريكي 12</t>
+          <t>فيكس بندا 50</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>زهور قرنفل امريكي 12</t>
+          <t>فيكس بندا 50 سم</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
@@ -2914,21 +2914,21 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>قرنفل صيني</t>
+          <t>قرنفل امريكي 12</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>زهور قرنفل صيني / زهور قرنفل صيني مركن9 سم</t>
+          <t>زهور قرنفل امريكي 12</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -2937,14 +2937,16 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>3550</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>0.5</v>
+        <v>90</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -2953,21 +2955,21 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>كف مريم 1. 5 : 2 م</t>
+          <t>قرنفل صيني</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>كف مريم 1.5 : 2 م</t>
+          <t>زهور قرنفل صيني / زهور قرنفل صيني مركن9 سم</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -2976,16 +2978,14 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3550</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
@@ -2994,21 +2994,21 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>كلانشو هولندي مركن 12</t>
+          <t>كف مريم 1. 5 : 2 م</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>كالنشو هولندى مركن12 سم / كلانشو هولندي مركن 12</t>
+          <t>كف مريم 1.5 : 2 م</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>4 / 5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -3017,14 +3017,16 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3033,21 +3035,21 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>كلانشو هولندي مركن 12</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>كالنشو هولندى مركن12 سم / كلانشو هولندي مركن 12</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 / 5</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -3056,16 +3058,14 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2720</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>كيليوس</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>زهور كيليوس</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -3097,14 +3097,16 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>0.55</v>
+        <v>70</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3113,21 +3115,21 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>لانتانا لبناني صغير</t>
+          <t>كيليوس</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>لانتانا لبناني صغير</t>
+          <t>زهور كيليوس</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -3136,16 +3138,14 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>عقود أبو خالد</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2200</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="62">
@@ -3154,21 +3154,21 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ملفوف مركن 9</t>
+          <t>لانتانا لبناني صغير</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>زهور ملفوف براسيكا مركن9 سم / زهور ملفوف مركن 9</t>
+          <t>لانتانا لبناني صغير</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -3177,14 +3177,16 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>2862</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3193,12 +3195,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>منثور مركن 9</t>
+          <t>ملفوف مركن 9</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>زهور منثور مركن 9</t>
+          <t>زهور ملفوف براسيكا مركن9 سم / زهور ملفوف مركن 9</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -3216,16 +3218,14 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>462</v>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2862</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="64">
@@ -3234,21 +3234,21 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 30</t>
+          <t>منثور مركن 9</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 30 سم</t>
+          <t>زهور منثور مركن 9</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>262.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>300</v>
+        <v>0.5</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>4</v>
+        <v>462</v>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
@@ -3275,21 +3275,21 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 40</t>
+          <t>نخيل سايكس 30</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 40 سم</t>
+          <t>نخيل سايكس 30 سم</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>262.5</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>هيدرا علاقي مركن 19</t>
+          <t>نخيل سايكس 40</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>هيدرا علاقي مركن 19</t>
+          <t>نخيل سايكس 40 سم</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
@@ -3357,21 +3357,21 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>وايتكس 50</t>
+          <t>هيدرا علاقي مركن 19</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>وايتكس 50 سم</t>
+          <t>هيدرا علاقي مركن 19</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -3380,11 +3380,11 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>ياسمين ازرق</t>
+          <t>وايتكس 50</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>ياسمين أزرق / ياسمين ازرق  50 سم</t>
+          <t>وايتكس 50 سم</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3421,11 +3421,11 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>730</v>
+        <v>400</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
@@ -3439,36 +3439,77 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
+          <t>ياسمين ازرق</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>ياسمين أزرق / ياسمين ازرق  50 سم</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>معتمد (قرارك)</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>730</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
           <t>ياسمين هندي كبير</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>ياسمين هندي كبير</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E70" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>معتمد (قرارك)</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3604,7 +3645,7 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G3,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G3)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G3,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G3)</f>
         <v/>
       </c>
       <c r="J3" s="4">
@@ -3653,7 +3694,7 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G4)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G4)</f>
         <v/>
       </c>
       <c r="J4" s="4">
@@ -3699,7 +3740,7 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G5,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G5)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G5,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G5)</f>
         <v/>
       </c>
       <c r="J5" s="4">
@@ -3745,7 +3786,7 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G6,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G6)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G6,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G6)</f>
         <v/>
       </c>
       <c r="J6" s="4">
@@ -3791,7 +3832,7 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G7,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G7)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G7,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G7)</f>
         <v/>
       </c>
       <c r="J7" s="4">
@@ -3837,7 +3878,7 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G8,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G8)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G8,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G8)</f>
         <v/>
       </c>
       <c r="J8" s="4">
@@ -3883,7 +3924,7 @@
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G9,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G9)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G9,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G9)</f>
         <v/>
       </c>
       <c r="J9" s="4">
@@ -3929,7 +3970,7 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G10,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G10)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G10,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G10)</f>
         <v/>
       </c>
       <c r="J10" s="4">
@@ -3975,7 +4016,7 @@
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G11,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G11)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G11,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G11)</f>
         <v/>
       </c>
       <c r="J11" s="4">
@@ -4021,7 +4062,7 @@
         <v/>
       </c>
       <c r="I12" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G12)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G12)</f>
         <v/>
       </c>
       <c r="J12" s="4">
@@ -4067,7 +4108,7 @@
         <v/>
       </c>
       <c r="I13" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G13,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G13)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G13,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G13)</f>
         <v/>
       </c>
       <c r="J13" s="4">
@@ -4113,7 +4154,7 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G14,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G14)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G14,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G14)</f>
         <v/>
       </c>
       <c r="J14" s="4">
@@ -4159,7 +4200,7 @@
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G15,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G15)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G15,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G15)</f>
         <v/>
       </c>
       <c r="J15" s="4">
@@ -4205,7 +4246,7 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G16,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G16)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G16,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G16)</f>
         <v/>
       </c>
       <c r="J16" s="4">
@@ -4251,7 +4292,7 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G17)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G17)</f>
         <v/>
       </c>
       <c r="J17" s="4">
@@ -4297,7 +4338,7 @@
         <v/>
       </c>
       <c r="I18" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G18,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G18)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G18,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G18)</f>
         <v/>
       </c>
       <c r="J18" s="4">
@@ -4343,7 +4384,7 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G19)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G19)</f>
         <v/>
       </c>
       <c r="J19" s="4">
@@ -4389,7 +4430,7 @@
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G20,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G20)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G20,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G20)</f>
         <v/>
       </c>
       <c r="J20" s="4">
@@ -4435,7 +4476,7 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G21,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G21)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G21,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G21)</f>
         <v/>
       </c>
       <c r="J21" s="4">
@@ -4481,7 +4522,7 @@
         <v/>
       </c>
       <c r="I22" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G22,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G22)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G22,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G22)</f>
         <v/>
       </c>
       <c r="J22" s="4">
@@ -4527,7 +4568,7 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G23,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G23)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G23,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G23)</f>
         <v/>
       </c>
       <c r="J23" s="4">
@@ -4573,7 +4614,7 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G24,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G24)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G24,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G24)</f>
         <v/>
       </c>
       <c r="J24" s="4">
@@ -4619,7 +4660,7 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G25,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G25)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G25,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G25)</f>
         <v/>
       </c>
       <c r="J25" s="4">
@@ -4665,7 +4706,7 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G26,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G26)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G26,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G26)</f>
         <v/>
       </c>
       <c r="J26" s="4">
@@ -4711,7 +4752,7 @@
         <v/>
       </c>
       <c r="I27" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G27,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G27)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G27,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G27)</f>
         <v/>
       </c>
       <c r="J27" s="4">
@@ -4757,7 +4798,7 @@
         <v/>
       </c>
       <c r="I28" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G28,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G28)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G28,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G28)</f>
         <v/>
       </c>
       <c r="J28" s="4">
@@ -4803,7 +4844,7 @@
         <v/>
       </c>
       <c r="I29" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G29,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G29)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G29,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G29)</f>
         <v/>
       </c>
       <c r="J29" s="4">
@@ -4849,7 +4890,7 @@
         <v/>
       </c>
       <c r="I30" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G30,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G30)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G30,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G30)</f>
         <v/>
       </c>
       <c r="J30" s="4">
@@ -4895,7 +4936,7 @@
         <v/>
       </c>
       <c r="I31" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G31,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G31)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G31,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G31)</f>
         <v/>
       </c>
       <c r="J31" s="4">
@@ -4941,7 +4982,7 @@
         <v/>
       </c>
       <c r="I32" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G32,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G32)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G32,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G32)</f>
         <v/>
       </c>
       <c r="J32" s="4">
@@ -4987,7 +5028,7 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G33,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G33)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G33,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G33)</f>
         <v/>
       </c>
       <c r="J33" s="4">
@@ -5033,7 +5074,7 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G34,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G34)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G34,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G34)</f>
         <v/>
       </c>
       <c r="J34" s="4">
@@ -5079,7 +5120,7 @@
         <v/>
       </c>
       <c r="I35" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G35,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G35)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G35,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G35)</f>
         <v/>
       </c>
       <c r="J35" s="4">
@@ -5125,7 +5166,7 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G36,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G36)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G36,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G36)</f>
         <v/>
       </c>
       <c r="J36" s="4">
@@ -5171,7 +5212,7 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G37,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G37)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G37,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G37)</f>
         <v/>
       </c>
       <c r="J37" s="4">
@@ -5217,7 +5258,7 @@
         <v/>
       </c>
       <c r="I38" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G38,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G38)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G38,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G38)</f>
         <v/>
       </c>
       <c r="J38" s="4">
@@ -5263,7 +5304,7 @@
         <v/>
       </c>
       <c r="I39" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G39,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G39)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G39,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G39)</f>
         <v/>
       </c>
       <c r="J39" s="4">
@@ -5309,7 +5350,7 @@
         <v/>
       </c>
       <c r="I40" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G40,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G40)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G40,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G40)</f>
         <v/>
       </c>
       <c r="J40" s="4">
@@ -5355,7 +5396,7 @@
         <v/>
       </c>
       <c r="I41" s="8">
-        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G41,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G41)</f>
+        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G41,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G41)</f>
         <v/>
       </c>
       <c r="J41" s="4">
@@ -5401,7 +5442,7 @@
         <v/>
       </c>
       <c r="I42" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G42,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G42)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G42,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G42)</f>
         <v/>
       </c>
       <c r="J42" s="4">
@@ -5447,7 +5488,7 @@
         <v/>
       </c>
       <c r="I43" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G43,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G43)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G43,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G43)</f>
         <v/>
       </c>
       <c r="J43" s="4">
@@ -5493,7 +5534,7 @@
         <v/>
       </c>
       <c r="I44" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G44,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G44)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G44,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G44)</f>
         <v/>
       </c>
       <c r="J44" s="4">
@@ -5539,7 +5580,7 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G45,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G45)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G45,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G45)</f>
         <v/>
       </c>
       <c r="J45" s="4">
@@ -5585,7 +5626,7 @@
         <v/>
       </c>
       <c r="I46" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G46,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G46)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G46,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G46)</f>
         <v/>
       </c>
       <c r="J46" s="4">
@@ -5631,7 +5672,7 @@
         <v/>
       </c>
       <c r="I47" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G47,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G47)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G47,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G47)</f>
         <v/>
       </c>
       <c r="J47" s="4">
@@ -5677,7 +5718,7 @@
         <v/>
       </c>
       <c r="I48" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G48,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G48)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G48,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G48)</f>
         <v/>
       </c>
       <c r="J48" s="4">
@@ -5723,7 +5764,7 @@
         <v/>
       </c>
       <c r="I49" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G49,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G49)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G49,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G49)</f>
         <v/>
       </c>
       <c r="J49" s="4">
@@ -5769,7 +5810,7 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G50,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G50)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G50,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G50)</f>
         <v/>
       </c>
       <c r="J50" s="4">
@@ -5815,7 +5856,7 @@
         <v/>
       </c>
       <c r="I51" s="4">
-        <f>IFERROR(IF(VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G51,VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G51)</f>
+        <f>IFERROR(IF(VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G51,VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G51)</f>
         <v/>
       </c>
       <c r="J51" s="4">
@@ -5861,7 +5902,7 @@
         <v/>
       </c>
       <c r="I52" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G52,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G52)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G52,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G52)</f>
         <v/>
       </c>
       <c r="J52" s="4">
@@ -5907,7 +5948,7 @@
         <v/>
       </c>
       <c r="I53" s="8">
-        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G53,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G53)</f>
+        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G53,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G53)</f>
         <v/>
       </c>
       <c r="J53" s="4">
@@ -5953,7 +5994,7 @@
         <v/>
       </c>
       <c r="I54" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G54,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G54)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G54,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G54)</f>
         <v/>
       </c>
       <c r="J54" s="4">
@@ -5999,7 +6040,7 @@
         <v/>
       </c>
       <c r="I55" s="8">
-        <f>IFERROR(IF(VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G55,VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G55)</f>
+        <f>IFERROR(IF(VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G55,VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G55)</f>
         <v/>
       </c>
       <c r="J55" s="4">
@@ -6045,7 +6086,7 @@
         <v/>
       </c>
       <c r="I56" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G56,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G56)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G56,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G56)</f>
         <v/>
       </c>
       <c r="J56" s="4">
@@ -6091,7 +6132,7 @@
         <v/>
       </c>
       <c r="I57" s="8">
-        <f>IFERROR(IF(VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G57,VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G57)</f>
+        <f>IFERROR(IF(VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G57,VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G57)</f>
         <v/>
       </c>
       <c r="J57" s="4">
@@ -6137,7 +6178,7 @@
         <v/>
       </c>
       <c r="I58" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G58,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G58)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G58,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G58)</f>
         <v/>
       </c>
       <c r="J58" s="4">
@@ -6183,7 +6224,7 @@
         <v/>
       </c>
       <c r="I59" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G59,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G59)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G59,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G59)</f>
         <v/>
       </c>
       <c r="J59" s="4">
@@ -6229,7 +6270,7 @@
         <v/>
       </c>
       <c r="I60" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",G60,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),G60)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G60,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G60)</f>
         <v/>
       </c>
       <c r="J60" s="4">
@@ -6283,7 +6324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6391,7 +6432,7 @@
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F3,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F3)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F3,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F3)</f>
         <v/>
       </c>
       <c r="I3" s="4">
@@ -6432,7 +6473,7 @@
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F4)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F4)</f>
         <v/>
       </c>
       <c r="I4" s="4">
@@ -6473,7 +6514,7 @@
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F5,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F5)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F5,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F5)</f>
         <v/>
       </c>
       <c r="I5" s="4">
@@ -6514,7 +6555,7 @@
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F6,VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F6)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F6,VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F6)</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -6555,7 +6596,7 @@
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F7,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F7)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F7,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F7)</f>
         <v/>
       </c>
       <c r="I7" s="4">
@@ -6596,7 +6637,7 @@
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F8,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F8)</f>
+        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F8,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F8)</f>
         <v/>
       </c>
       <c r="I8" s="4">
@@ -6637,7 +6678,7 @@
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F9,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F9)</f>
+        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F9,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F9)</f>
         <v/>
       </c>
       <c r="I9" s="4">
@@ -6678,7 +6719,7 @@
         <v/>
       </c>
       <c r="H10" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F10,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F10)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F10,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F10)</f>
         <v/>
       </c>
       <c r="I10" s="4">
@@ -6719,7 +6760,7 @@
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F11,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F11)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F11,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F11)</f>
         <v/>
       </c>
       <c r="I11" s="4">
@@ -6760,7 +6801,7 @@
         <v/>
       </c>
       <c r="H12" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F12)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F12)</f>
         <v/>
       </c>
       <c r="I12" s="4">
@@ -6801,7 +6842,7 @@
         <v/>
       </c>
       <c r="H13" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F13,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F13)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F13,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F13)</f>
         <v/>
       </c>
       <c r="I13" s="4">
@@ -6842,7 +6883,7 @@
         <v/>
       </c>
       <c r="H14" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F14,VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F14)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F14,VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F14)</f>
         <v/>
       </c>
       <c r="I14" s="4">
@@ -6883,7 +6924,7 @@
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F15,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F15)</f>
+        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F15,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F15)</f>
         <v/>
       </c>
       <c r="I15" s="4">
@@ -6924,7 +6965,7 @@
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F16,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F16)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F16,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F16)</f>
         <v/>
       </c>
       <c r="I16" s="4">
@@ -6965,7 +7006,7 @@
         <v/>
       </c>
       <c r="H17" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F17)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F17)</f>
         <v/>
       </c>
       <c r="I17" s="4">
@@ -7006,7 +7047,7 @@
         <v/>
       </c>
       <c r="H18" s="8">
-        <f>IFERROR(IF(VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F18,VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F18)</f>
+        <f>IFERROR(IF(VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F18,VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F18)</f>
         <v/>
       </c>
       <c r="I18" s="4">
@@ -7047,7 +7088,7 @@
         <v/>
       </c>
       <c r="H19" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F19)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F19)</f>
         <v/>
       </c>
       <c r="I19" s="4">
@@ -7088,7 +7129,7 @@
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F20,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F20)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F20,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F20)</f>
         <v/>
       </c>
       <c r="I20" s="4">
@@ -7129,7 +7170,7 @@
         <v/>
       </c>
       <c r="H21" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F21,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F21)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F21,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F21)</f>
         <v/>
       </c>
       <c r="I21" s="4">
@@ -7170,7 +7211,7 @@
         <v/>
       </c>
       <c r="H22" s="8">
-        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F22,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F22)</f>
+        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F22,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F22)</f>
         <v/>
       </c>
       <c r="I22" s="4">
@@ -7211,7 +7252,7 @@
         <v/>
       </c>
       <c r="H23" s="8">
-        <f>IFERROR(IF(VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F23,VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F23)</f>
+        <f>IFERROR(IF(VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F23,VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F23)</f>
         <v/>
       </c>
       <c r="I23" s="4">
@@ -7252,7 +7293,7 @@
         <v/>
       </c>
       <c r="H24" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F24,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F24)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F24,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F24)</f>
         <v/>
       </c>
       <c r="I24" s="4">
@@ -7293,7 +7334,7 @@
         <v/>
       </c>
       <c r="H25" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F25,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F25)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F25,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F25)</f>
         <v/>
       </c>
       <c r="I25" s="4">
@@ -7334,7 +7375,7 @@
         <v/>
       </c>
       <c r="H26" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F26,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F26)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F26,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F26)</f>
         <v/>
       </c>
       <c r="I26" s="4">
@@ -7375,7 +7416,7 @@
         <v/>
       </c>
       <c r="H27" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F27,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F27)</f>
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F27,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F27)</f>
         <v/>
       </c>
       <c r="I27" s="4">
@@ -7416,7 +7457,7 @@
         <v/>
       </c>
       <c r="H28" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F28,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F28)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F28,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F28)</f>
         <v/>
       </c>
       <c r="I28" s="4">
@@ -7457,7 +7498,7 @@
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F29,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F29)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F29,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F29)</f>
         <v/>
       </c>
       <c r="I29" s="4">
@@ -7498,7 +7539,7 @@
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F30,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F30)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F30,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F30)</f>
         <v/>
       </c>
       <c r="I30" s="4">
@@ -7539,7 +7580,7 @@
         <v/>
       </c>
       <c r="H31" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F31,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F31)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F31,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F31)</f>
         <v/>
       </c>
       <c r="I31" s="4">
@@ -7580,7 +7621,7 @@
         <v/>
       </c>
       <c r="H32" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F32,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F32)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F32,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F32)</f>
         <v/>
       </c>
       <c r="I32" s="4">
@@ -7621,7 +7662,7 @@
         <v/>
       </c>
       <c r="H33" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F33,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F33)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F33,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F33)</f>
         <v/>
       </c>
       <c r="I33" s="4">
@@ -7662,7 +7703,7 @@
         <v/>
       </c>
       <c r="H34" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F34,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F34)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F34,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F34)</f>
         <v/>
       </c>
       <c r="I34" s="4">
@@ -7703,7 +7744,7 @@
         <v/>
       </c>
       <c r="H35" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F35,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F35)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F35,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F35)</f>
         <v/>
       </c>
       <c r="I35" s="4">
@@ -7744,7 +7785,7 @@
         <v/>
       </c>
       <c r="H36" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F36,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F36)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F36,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F36)</f>
         <v/>
       </c>
       <c r="I36" s="4">
@@ -7785,7 +7826,7 @@
         <v/>
       </c>
       <c r="H37" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F37,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F37)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F37,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F37)</f>
         <v/>
       </c>
       <c r="I37" s="4">
@@ -7826,7 +7867,7 @@
         <v/>
       </c>
       <c r="H38" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F38,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F38)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F38,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F38)</f>
         <v/>
       </c>
       <c r="I38" s="4">
@@ -7867,7 +7908,7 @@
         <v/>
       </c>
       <c r="H39" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F39,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F39)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F39,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F39)</f>
         <v/>
       </c>
       <c r="I39" s="4">
@@ -7908,7 +7949,7 @@
         <v/>
       </c>
       <c r="H40" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F40,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F40)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F40,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F40)</f>
         <v/>
       </c>
       <c r="I40" s="4">
@@ -7949,7 +7990,7 @@
         <v/>
       </c>
       <c r="H41" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F41,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F41)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F41,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F41)</f>
         <v/>
       </c>
       <c r="I41" s="4">
@@ -7990,7 +8031,7 @@
         <v/>
       </c>
       <c r="H42" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F42,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F42)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F42,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F42)</f>
         <v/>
       </c>
       <c r="I42" s="4">
@@ -8031,7 +8072,7 @@
         <v/>
       </c>
       <c r="H43" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F43,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F43)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F43,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F43)</f>
         <v/>
       </c>
       <c r="I43" s="4">
@@ -8072,7 +8113,7 @@
         <v/>
       </c>
       <c r="H44" s="8">
-        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F44,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F44)</f>
+        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F44,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F44)</f>
         <v/>
       </c>
       <c r="I44" s="4">
@@ -8113,7 +8154,7 @@
         <v/>
       </c>
       <c r="H45" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F45,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F45)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F45,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F45)</f>
         <v/>
       </c>
       <c r="I45" s="4">
@@ -8154,7 +8195,7 @@
         <v/>
       </c>
       <c r="H46" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F46,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F46)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F46,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F46)</f>
         <v/>
       </c>
       <c r="I46" s="4">
@@ -8195,7 +8236,7 @@
         <v/>
       </c>
       <c r="H47" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F47,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F47)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F47,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F47)</f>
         <v/>
       </c>
       <c r="I47" s="4">
@@ -8236,7 +8277,7 @@
         <v/>
       </c>
       <c r="H48" s="8">
-        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F48,VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F48)</f>
+        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F48,VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F48)</f>
         <v/>
       </c>
       <c r="I48" s="4">
@@ -8277,7 +8318,7 @@
         <v/>
       </c>
       <c r="H49" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F49,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F49)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F49,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F49)</f>
         <v/>
       </c>
       <c r="I49" s="4">
@@ -8318,7 +8359,7 @@
         <v/>
       </c>
       <c r="H50" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F50,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F50)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F50,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F50)</f>
         <v/>
       </c>
       <c r="I50" s="4">
@@ -8359,7 +8400,7 @@
         <v/>
       </c>
       <c r="H51" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F51,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F51)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F51,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F51)</f>
         <v/>
       </c>
       <c r="I51" s="4">
@@ -8400,7 +8441,7 @@
         <v/>
       </c>
       <c r="H52" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F52,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F52)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F52,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F52)</f>
         <v/>
       </c>
       <c r="I52" s="4">
@@ -8441,7 +8482,7 @@
         <v/>
       </c>
       <c r="H53" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F53,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F53)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F53,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F53)</f>
         <v/>
       </c>
       <c r="I53" s="4">
@@ -8482,7 +8523,7 @@
         <v/>
       </c>
       <c r="H54" s="8">
-        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F54,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F54)</f>
+        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F54,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F54)</f>
         <v/>
       </c>
       <c r="I54" s="4">
@@ -8523,7 +8564,7 @@
         <v/>
       </c>
       <c r="H55" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F55,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F55)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F55,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F55)</f>
         <v/>
       </c>
       <c r="I55" s="4">
@@ -8564,7 +8605,7 @@
         <v/>
       </c>
       <c r="H56" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F56,VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F56)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F56,VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F56)</f>
         <v/>
       </c>
       <c r="I56" s="4">
@@ -8605,7 +8646,7 @@
         <v/>
       </c>
       <c r="H57" s="8">
-        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F57,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F57)</f>
+        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F57,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F57)</f>
         <v/>
       </c>
       <c r="I57" s="4">
@@ -8646,7 +8687,7 @@
         <v/>
       </c>
       <c r="H58" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F58,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F58)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F58,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F58)</f>
         <v/>
       </c>
       <c r="I58" s="4">
@@ -8687,7 +8728,7 @@
         <v/>
       </c>
       <c r="H59" s="8">
-        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F59,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F59)</f>
+        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F59,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F59)</f>
         <v/>
       </c>
       <c r="I59" s="4">
@@ -8728,7 +8769,7 @@
         <v/>
       </c>
       <c r="H60" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F60,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F60)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F60,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F60)</f>
         <v/>
       </c>
       <c r="I60" s="4">
@@ -8769,7 +8810,7 @@
         <v/>
       </c>
       <c r="H61" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F61,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F61)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F61,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F61)</f>
         <v/>
       </c>
       <c r="I61" s="4">
@@ -8810,7 +8851,7 @@
         <v/>
       </c>
       <c r="H62" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F62,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F62)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F62,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F62)</f>
         <v/>
       </c>
       <c r="I62" s="4">
@@ -8851,7 +8892,7 @@
         <v/>
       </c>
       <c r="H63" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F63,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F63)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F63,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F63)</f>
         <v/>
       </c>
       <c r="I63" s="4">
@@ -8892,7 +8933,7 @@
         <v/>
       </c>
       <c r="H64" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F64,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F64)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F64,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F64)</f>
         <v/>
       </c>
       <c r="I64" s="4">
@@ -8933,7 +8974,7 @@
         <v/>
       </c>
       <c r="H65" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F65,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F65)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F65,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F65)</f>
         <v/>
       </c>
       <c r="I65" s="4">
@@ -8974,7 +9015,7 @@
         <v/>
       </c>
       <c r="H66" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F66,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F66)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F66,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F66)</f>
         <v/>
       </c>
       <c r="I66" s="4">
@@ -9015,7 +9056,7 @@
         <v/>
       </c>
       <c r="H67" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F67,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F67)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F67,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F67)</f>
         <v/>
       </c>
       <c r="I67" s="4">
@@ -9056,7 +9097,7 @@
         <v/>
       </c>
       <c r="H68" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F68,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F68)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F68,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F68)</f>
         <v/>
       </c>
       <c r="I68" s="4">
@@ -9097,7 +9138,7 @@
         <v/>
       </c>
       <c r="H69" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F69,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F69)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F69,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F69)</f>
         <v/>
       </c>
       <c r="I69" s="4">
@@ -9138,7 +9179,7 @@
         <v/>
       </c>
       <c r="H70" s="8">
-        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F70,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F70)</f>
+        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F70,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F70)</f>
         <v/>
       </c>
       <c r="I70" s="4">
@@ -9179,7 +9220,7 @@
         <v/>
       </c>
       <c r="H71" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F71,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F71)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F71,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F71)</f>
         <v/>
       </c>
       <c r="I71" s="4">
@@ -9220,7 +9261,7 @@
         <v/>
       </c>
       <c r="H72" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F72,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F72)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F72,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F72)</f>
         <v/>
       </c>
       <c r="I72" s="4">
@@ -9261,7 +9302,7 @@
         <v/>
       </c>
       <c r="H73" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F73,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F73)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F73,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F73)</f>
         <v/>
       </c>
       <c r="I73" s="4">
@@ -9302,7 +9343,7 @@
         <v/>
       </c>
       <c r="H74" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F74,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F74)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F74,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F74)</f>
         <v/>
       </c>
       <c r="I74" s="4">
@@ -9343,7 +9384,7 @@
         <v/>
       </c>
       <c r="H75" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F75,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F75)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F75,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F75)</f>
         <v/>
       </c>
       <c r="I75" s="4">
@@ -9384,7 +9425,7 @@
         <v/>
       </c>
       <c r="H76" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F76,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F76)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F76,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F76)</f>
         <v/>
       </c>
       <c r="I76" s="4">
@@ -9425,7 +9466,7 @@
         <v/>
       </c>
       <c r="H77" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F77,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F77)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F77,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F77)</f>
         <v/>
       </c>
       <c r="I77" s="4">
@@ -9466,7 +9507,7 @@
         <v/>
       </c>
       <c r="H78" s="8">
-        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F78,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F78)</f>
+        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F78,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F78)</f>
         <v/>
       </c>
       <c r="I78" s="4">
@@ -9507,7 +9548,7 @@
         <v/>
       </c>
       <c r="H79" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F79,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F79)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F79,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F79)</f>
         <v/>
       </c>
       <c r="I79" s="4">
@@ -9548,7 +9589,7 @@
         <v/>
       </c>
       <c r="H80" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F80,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F80)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F80,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F80)</f>
         <v/>
       </c>
       <c r="I80" s="4">
@@ -9589,7 +9630,7 @@
         <v/>
       </c>
       <c r="H81" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F81,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F81)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F81,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F81)</f>
         <v/>
       </c>
       <c r="I81" s="4">
@@ -9630,7 +9671,7 @@
         <v/>
       </c>
       <c r="H82" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F82,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F82)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F82,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F82)</f>
         <v/>
       </c>
       <c r="I82" s="4">
@@ -9671,7 +9712,7 @@
         <v/>
       </c>
       <c r="H83" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F83,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F83)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F83,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F83)</f>
         <v/>
       </c>
       <c r="I83" s="4">
@@ -9712,7 +9753,7 @@
         <v/>
       </c>
       <c r="H84" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F84,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F84)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F84,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F84)</f>
         <v/>
       </c>
       <c r="I84" s="4">
@@ -9753,7 +9794,7 @@
         <v/>
       </c>
       <c r="H85" s="4">
-        <f>IFERROR(IF(VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F85,VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F85)</f>
+        <f>IFERROR(IF(VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F85,VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F85)</f>
         <v/>
       </c>
       <c r="I85" s="4">
@@ -9794,7 +9835,7 @@
         <v/>
       </c>
       <c r="H86" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F86,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F86)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F86,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F86)</f>
         <v/>
       </c>
       <c r="I86" s="4">
@@ -9835,7 +9876,7 @@
         <v/>
       </c>
       <c r="H87" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F87,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F87)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F87,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F87)</f>
         <v/>
       </c>
       <c r="I87" s="4">
@@ -9876,7 +9917,7 @@
         <v/>
       </c>
       <c r="H88" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F88,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F88)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F88,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F88)</f>
         <v/>
       </c>
       <c r="I88" s="4">
@@ -9917,7 +9958,7 @@
         <v/>
       </c>
       <c r="H89" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F89,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F89)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F89,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F89)</f>
         <v/>
       </c>
       <c r="I89" s="4">
@@ -9958,7 +9999,7 @@
         <v/>
       </c>
       <c r="H90" s="8">
-        <f>IFERROR(IF(VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F90,VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F90)</f>
+        <f>IFERROR(IF(VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F90,VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F90)</f>
         <v/>
       </c>
       <c r="I90" s="4">
@@ -9999,7 +10040,7 @@
         <v/>
       </c>
       <c r="H91" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F91,VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F91)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F91,VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F91)</f>
         <v/>
       </c>
       <c r="I91" s="4">
@@ -10040,7 +10081,7 @@
         <v/>
       </c>
       <c r="H92" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F92,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F92)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F92,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F92)</f>
         <v/>
       </c>
       <c r="I92" s="4">
@@ -10081,7 +10122,7 @@
         <v/>
       </c>
       <c r="H93" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F93,VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F93)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F93,VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F93)</f>
         <v/>
       </c>
       <c r="I93" s="4">
@@ -10122,7 +10163,7 @@
         <v/>
       </c>
       <c r="H94" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F94,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F94)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F94,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F94)</f>
         <v/>
       </c>
       <c r="I94" s="4">
@@ -10163,7 +10204,7 @@
         <v/>
       </c>
       <c r="H95" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F95,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F95)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F95,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F95)</f>
         <v/>
       </c>
       <c r="I95" s="4">
@@ -10204,7 +10245,7 @@
         <v/>
       </c>
       <c r="H96" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F96,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F96)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F96,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F96)</f>
         <v/>
       </c>
       <c r="I96" s="4">
@@ -10245,7 +10286,7 @@
         <v/>
       </c>
       <c r="H97" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F97,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F97)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F97,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F97)</f>
         <v/>
       </c>
       <c r="I97" s="4">
@@ -10286,7 +10327,7 @@
         <v/>
       </c>
       <c r="H98" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F98,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F98)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F98,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F98)</f>
         <v/>
       </c>
       <c r="I98" s="4">
@@ -10327,7 +10368,7 @@
         <v/>
       </c>
       <c r="H99" s="8">
-        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F99,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F99)</f>
+        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F99,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F99)</f>
         <v/>
       </c>
       <c r="I99" s="4">
@@ -10368,7 +10409,7 @@
         <v/>
       </c>
       <c r="H100" s="8">
-        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F100,VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F100)</f>
+        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F100,VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F100)</f>
         <v/>
       </c>
       <c r="I100" s="4">
@@ -10409,7 +10450,7 @@
         <v/>
       </c>
       <c r="H101" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F101,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F101)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F101,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F101)</f>
         <v/>
       </c>
       <c r="I101" s="4">
@@ -10450,7 +10491,7 @@
         <v/>
       </c>
       <c r="H102" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F102,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F102)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F102,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F102)</f>
         <v/>
       </c>
       <c r="I102" s="4">
@@ -10491,7 +10532,7 @@
         <v/>
       </c>
       <c r="H103" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F103,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F103)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F103,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F103)</f>
         <v/>
       </c>
       <c r="I103" s="4">
@@ -10532,7 +10573,7 @@
         <v/>
       </c>
       <c r="H104" s="8">
-        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F104,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F104)</f>
+        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F104,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F104)</f>
         <v/>
       </c>
       <c r="I104" s="4">
@@ -10573,7 +10614,7 @@
         <v/>
       </c>
       <c r="H105" s="8">
-        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F105,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F105)</f>
+        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F105,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F105)</f>
         <v/>
       </c>
       <c r="I105" s="4">
@@ -10614,7 +10655,7 @@
         <v/>
       </c>
       <c r="H106" s="8">
-        <f>IFERROR(IF(VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F106,VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F106)</f>
+        <f>IFERROR(IF(VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F106,VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F106)</f>
         <v/>
       </c>
       <c r="I106" s="4">
@@ -10655,7 +10696,7 @@
         <v/>
       </c>
       <c r="H107" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F107,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F107)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F107,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F107)</f>
         <v/>
       </c>
       <c r="I107" s="4">
@@ -10696,7 +10737,7 @@
         <v/>
       </c>
       <c r="H108" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F108,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F108)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F108,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F108)</f>
         <v/>
       </c>
       <c r="I108" s="4">
@@ -10737,7 +10778,7 @@
         <v/>
       </c>
       <c r="H109" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F109,VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F109)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F109,VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F109)</f>
         <v/>
       </c>
       <c r="I109" s="4">
@@ -10778,7 +10819,7 @@
         <v/>
       </c>
       <c r="H110" s="8">
-        <f>IFERROR(IF(VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F110,VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F110)</f>
+        <f>IFERROR(IF(VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F110,VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F110)</f>
         <v/>
       </c>
       <c r="I110" s="4">
@@ -10819,7 +10860,7 @@
         <v/>
       </c>
       <c r="H111" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F111,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F111)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F111,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F111)</f>
         <v/>
       </c>
       <c r="I111" s="4">
@@ -10864,7 +10905,7 @@
         <v/>
       </c>
       <c r="H112" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F112,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F112)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F112,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F112)</f>
         <v/>
       </c>
       <c r="I112" s="4">
@@ -10909,7 +10950,7 @@
         <v/>
       </c>
       <c r="H113" s="8">
-        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F113,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F113)</f>
+        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F113,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F113)</f>
         <v/>
       </c>
       <c r="I113" s="4">
@@ -10954,7 +10995,7 @@
         <v/>
       </c>
       <c r="H114" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F114,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F114)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F114,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F114)</f>
         <v/>
       </c>
       <c r="I114" s="4">
@@ -10999,7 +11040,7 @@
         <v/>
       </c>
       <c r="H115" s="8">
-        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F115,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F115)</f>
+        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F115,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F115)</f>
         <v/>
       </c>
       <c r="I115" s="4">
@@ -11044,7 +11085,7 @@
         <v/>
       </c>
       <c r="H116" s="8">
-        <f>IFERROR(IF(VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F116,VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F116)</f>
+        <f>IFERROR(IF(VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F116,VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F116)</f>
         <v/>
       </c>
       <c r="I116" s="4">
@@ -11089,7 +11130,7 @@
         <v/>
       </c>
       <c r="H117" s="8">
-        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F117,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F117)</f>
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F117,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F117)</f>
         <v/>
       </c>
       <c r="I117" s="4">
@@ -11134,7 +11175,7 @@
         <v/>
       </c>
       <c r="H118" s="8">
-        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F118,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F118)</f>
+        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F118,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F118)</f>
         <v/>
       </c>
       <c r="I118" s="4">
@@ -11179,7 +11220,7 @@
         <v/>
       </c>
       <c r="H119" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F119,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F119)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F119,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F119)</f>
         <v/>
       </c>
       <c r="I119" s="4">
@@ -11224,7 +11265,7 @@
         <v/>
       </c>
       <c r="H120" s="8">
-        <f>IFERROR(IF(VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F120,VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F120)</f>
+        <f>IFERROR(IF(VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F120,VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F120)</f>
         <v/>
       </c>
       <c r="I120" s="4">
@@ -11269,7 +11310,7 @@
         <v/>
       </c>
       <c r="H121" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F121,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F121)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F121,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F121)</f>
         <v/>
       </c>
       <c r="I121" s="4">
@@ -11314,7 +11355,7 @@
         <v/>
       </c>
       <c r="H122" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F122,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F122)</f>
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F122,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F122)</f>
         <v/>
       </c>
       <c r="I122" s="4">
@@ -11359,7 +11400,7 @@
         <v/>
       </c>
       <c r="H123" s="8">
-        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F123,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F123)</f>
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F123,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F123)</f>
         <v/>
       </c>
       <c r="I123" s="4">
@@ -11404,7 +11445,7 @@
         <v/>
       </c>
       <c r="H124" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F124,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F124)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F124,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F124)</f>
         <v/>
       </c>
       <c r="I124" s="4">
@@ -11449,7 +11490,7 @@
         <v/>
       </c>
       <c r="H125" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F125,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F125)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F125,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F125)</f>
         <v/>
       </c>
       <c r="I125" s="4">
@@ -11494,7 +11535,7 @@
         <v/>
       </c>
       <c r="H126" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F126,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F126)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F126,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F126)</f>
         <v/>
       </c>
       <c r="I126" s="4">
@@ -11516,30 +11557,30 @@
         <v>125</v>
       </c>
       <c r="B127" s="7" t="n">
-        <v>46163</v>
+        <v>45873</v>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>طلب 58991 (#299/#301)</t>
+          <t>RNP-1787</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>زهور فينكا</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>-17900</v>
+        <v>33000</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G127" s="4">
         <f>IF(F127="","",E127*F127)</f>
         <v/>
       </c>
       <c r="H127" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F127,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F127)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F127,VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F127)</f>
         <v/>
       </c>
       <c r="I127" s="4">
@@ -11552,38 +11593,83 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
+          <t>مسحوبات لنسما (تأكيدك) – 33,000 فينكا، قيمة النظام 18,150 قبل الضريبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>طلب 58991 (#299/#301)</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>-17900</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G128" s="4">
+        <f>IF(F128="","",E128*F128)</f>
+        <v/>
+      </c>
+      <c r="H128" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F128,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F128)</f>
+        <v/>
+      </c>
+      <c r="I128" s="4">
+        <f>IF(H128="","",E128*H128)</f>
+        <v/>
+      </c>
+      <c r="J128" s="4">
+        <f>IF(OR(G128="",I128=""),"",G128-I128)</f>
+        <v/>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
           <t>خصم كمية مرفوضة/مفقودة مع المناديب (حسب قرارك)</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="9" t="n"/>
-      <c r="B128" s="9" t="n"/>
-      <c r="C128" s="9" t="n"/>
-      <c r="D128" s="10" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E128" s="11">
-        <f>SUM(E3:E127)</f>
-        <v/>
-      </c>
-      <c r="F128" s="9" t="n"/>
-      <c r="G128" s="11">
-        <f>SUM(G3:G127)</f>
-        <v/>
-      </c>
-      <c r="H128" s="9" t="n"/>
-      <c r="I128" s="11">
-        <f>SUM(I3:I127)</f>
-        <v/>
-      </c>
-      <c r="J128" s="11">
-        <f>SUM(J3:J127)</f>
-        <v/>
-      </c>
-      <c r="K128" s="9" t="n"/>
+      <c r="E129" s="11">
+        <f>SUM(E3:E128)</f>
+        <v/>
+      </c>
+      <c r="F129" s="9" t="n"/>
+      <c r="G129" s="11">
+        <f>SUM(G3:G128)</f>
+        <v/>
+      </c>
+      <c r="H129" s="9" t="n"/>
+      <c r="I129" s="11">
+        <f>SUM(I3:I128)</f>
+        <v/>
+      </c>
+      <c r="J129" s="11">
+        <f>SUM(J3:J128)</f>
+        <v/>
+      </c>
+      <c r="K129" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11704,7 +11790,7 @@
         <v/>
       </c>
       <c r="H3" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F3,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F3)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F3,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F3)</f>
         <v/>
       </c>
       <c r="I3" s="4">
@@ -11749,7 +11835,7 @@
         <v/>
       </c>
       <c r="H4" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F4,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F4)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F4,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F4)</f>
         <v/>
       </c>
       <c r="I4" s="4">
@@ -11794,7 +11880,7 @@
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F5,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F5)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F5,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F5)</f>
         <v/>
       </c>
       <c r="I5" s="4">
@@ -11839,7 +11925,7 @@
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F6,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F6)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F6,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F6)</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -11884,7 +11970,7 @@
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F7,VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F7)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F7,VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F7)</f>
         <v/>
       </c>
       <c r="I7" s="4">
@@ -11929,7 +12015,7 @@
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F8,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F8)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F8,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F8)</f>
         <v/>
       </c>
       <c r="I8" s="4">
@@ -11974,7 +12060,7 @@
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F9,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F9)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F9,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F9)</f>
         <v/>
       </c>
       <c r="I9" s="4">
@@ -12015,7 +12101,7 @@
         <v/>
       </c>
       <c r="H10" s="8">
-        <f>IFERROR(IF(VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F10,VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F10)</f>
+        <f>IFERROR(IF(VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F10,VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F10)</f>
         <v/>
       </c>
       <c r="I10" s="4">
@@ -12056,7 +12142,7 @@
         <v/>
       </c>
       <c r="H11" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F11,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F11)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F11,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F11)</f>
         <v/>
       </c>
       <c r="I11" s="4">
@@ -12097,7 +12183,7 @@
         <v/>
       </c>
       <c r="H12" s="8">
-        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F12,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F12)</f>
+        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F12,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F12)</f>
         <v/>
       </c>
       <c r="I12" s="4">
@@ -12138,7 +12224,7 @@
         <v/>
       </c>
       <c r="H13" s="8">
-        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F13,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F13)</f>
+        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F13,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F13)</f>
         <v/>
       </c>
       <c r="I13" s="4">
@@ -12179,7 +12265,7 @@
         <v/>
       </c>
       <c r="H14" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F14,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F14)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F14,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F14)</f>
         <v/>
       </c>
       <c r="I14" s="4">
@@ -12220,7 +12306,7 @@
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F15,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F15)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F15,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F15)</f>
         <v/>
       </c>
       <c r="I15" s="4">
@@ -12261,7 +12347,7 @@
         <v/>
       </c>
       <c r="H16" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F16,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F16)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F16,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F16)</f>
         <v/>
       </c>
       <c r="I16" s="4">
@@ -12302,7 +12388,7 @@
         <v/>
       </c>
       <c r="H17" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F17,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F17)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F17,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F17)</f>
         <v/>
       </c>
       <c r="I17" s="4">
@@ -12343,7 +12429,7 @@
         <v/>
       </c>
       <c r="H18" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F18,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F18)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F18,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F18)</f>
         <v/>
       </c>
       <c r="I18" s="4">
@@ -12384,7 +12470,7 @@
         <v/>
       </c>
       <c r="H19" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F19,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F19)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F19,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F19)</f>
         <v/>
       </c>
       <c r="I19" s="4">
@@ -12425,7 +12511,7 @@
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F20,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F20)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F20,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F20)</f>
         <v/>
       </c>
       <c r="I20" s="4">
@@ -12463,7 +12549,7 @@
         <v/>
       </c>
       <c r="H21" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F21,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F21)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F21,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F21)</f>
         <v/>
       </c>
       <c r="I21" s="4">
@@ -12505,7 +12591,7 @@
         <v/>
       </c>
       <c r="H22" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F22,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F22)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F22,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F22)</f>
         <v/>
       </c>
       <c r="I22" s="4">
@@ -12547,7 +12633,7 @@
         <v/>
       </c>
       <c r="H23" s="8">
-        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F23,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F23)</f>
+        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F23,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F23)</f>
         <v/>
       </c>
       <c r="I23" s="4">
@@ -12589,7 +12675,7 @@
         <v/>
       </c>
       <c r="H24" s="8">
-        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F24,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F24)</f>
+        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F24,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F24)</f>
         <v/>
       </c>
       <c r="I24" s="4">
@@ -12631,7 +12717,7 @@
         <v/>
       </c>
       <c r="H25" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F25,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F25)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F25,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F25)</f>
         <v/>
       </c>
       <c r="I25" s="4">
@@ -12673,7 +12759,7 @@
         <v/>
       </c>
       <c r="H26" s="8">
-        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F26,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F26)</f>
+        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F26,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F26)</f>
         <v/>
       </c>
       <c r="I26" s="4">
@@ -12715,7 +12801,7 @@
         <v/>
       </c>
       <c r="H27" s="8">
-        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F27,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F27)</f>
+        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F27,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F27)</f>
         <v/>
       </c>
       <c r="I27" s="4">
@@ -12760,7 +12846,7 @@
         <v/>
       </c>
       <c r="H28" s="8">
-        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F28,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F28)</f>
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F28,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F28)</f>
         <v/>
       </c>
       <c r="I28" s="4">
@@ -12805,7 +12891,7 @@
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F29,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F29)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F29,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F29)</f>
         <v/>
       </c>
       <c r="I29" s="4">
@@ -12967,7 +13053,7 @@
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F3,VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F3)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F3,VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F3)</f>
         <v/>
       </c>
       <c r="I3" s="4">
@@ -13009,7 +13095,7 @@
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F4,VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F4)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F4,VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F4)</f>
         <v/>
       </c>
       <c r="I4" s="4">
@@ -13051,7 +13137,7 @@
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F5,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F5)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F5,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F5)</f>
         <v/>
       </c>
       <c r="I5" s="4">
@@ -13093,7 +13179,7 @@
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F6,VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F6)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F6,VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F6)</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -13135,7 +13221,7 @@
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F7,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F7)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F7,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F7)</f>
         <v/>
       </c>
       <c r="I7" s="4">
@@ -13177,7 +13263,7 @@
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F8,VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F8)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F8,VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F8)</f>
         <v/>
       </c>
       <c r="I8" s="4">
@@ -13219,7 +13305,7 @@
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F9,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F9)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F9,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F9)</f>
         <v/>
       </c>
       <c r="I9" s="4">
@@ -13261,7 +13347,7 @@
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F10,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F10)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F10,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F10)</f>
         <v/>
       </c>
       <c r="I10" s="4">
@@ -13303,7 +13389,7 @@
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F11,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F11)</f>
+        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F11,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F11)</f>
         <v/>
       </c>
       <c r="I11" s="4">
@@ -13345,7 +13431,7 @@
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F12,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F12)</f>
+        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F12,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F12)</f>
         <v/>
       </c>
       <c r="I12" s="4">
@@ -13387,7 +13473,7 @@
         <v/>
       </c>
       <c r="H13" s="4">
-        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)="",F13,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$69,4,FALSE)),F13)</f>
+        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F13,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F13)</f>
         <v/>
       </c>
       <c r="I13" s="4">
@@ -13444,7 +13530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13647,52 +13733,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>RNP-1787</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>WHOLESALE DEPARTMENT RIYADH</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>20872.5</v>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="F7" s="4">
+        <f>SUM(F3:F6)</f>
+        <v/>
       </c>
       <c r="G7" s="4">
-        <f>ROUND(F7/1.15,2)</f>
-        <v/>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="F8" s="4">
-        <f>SUM(F3:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="4">
-        <f>SUM(G3:G7)</f>
+        <f>SUM(G3:G6)</f>
         <v/>
       </c>
     </row>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -560,15 +560,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'مسحوبات نسما من الرياض'!G129</f>
+        <f>'مسحوبات نسما من الرياض'!G131</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'مسحوبات نسما من الرياض'!I129</f>
+        <f>'مسحوبات نسما من الرياض'!I131</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'مسحوبات نسما من الرياض'!J129</f>
+        <f>'مسحوبات نسما من الرياض'!J131</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!F7</f>
+        <f>'سندات بدون تفصيل أصناف'!F6</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!G7</f>
+        <f>'سندات بدون تفصيل أصناف'!G6</f>
         <v/>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ملفوف مركن 9</t>
+          <t>مركن 16</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>زهور ملفوف براسيكا مركن9 سم / زهور ملفوف مركن 9</t>
+          <t>مركن 16 سم</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -3218,14 +3218,16 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>2862</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>0.5</v>
+        <v>15000</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -3234,12 +3236,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>منثور مركن 9</t>
+          <t>ملفوف مركن 9</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>زهور منثور مركن 9</t>
+          <t>زهور ملفوف براسيكا مركن9 سم / زهور ملفوف مركن 9</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -3257,16 +3259,14 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض</t>
+          <t>عقود أبو خالد + مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>462</v>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2862</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="65">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 30</t>
+          <t>منثور مركن 9</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 30 سم</t>
+          <t>زهور منثور مركن 9</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>262.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>300</v>
+        <v>0.5</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>4</v>
+        <v>462</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 40</t>
+          <t>نخيل سايكس 30</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>نخيل سايكس 40 سم</t>
+          <t>نخيل سايكس 30 سم</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>262.5</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
@@ -3357,21 +3357,21 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>هيدرا علاقي مركن 19</t>
+          <t>نخيل سايكس 40</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>هيدرا علاقي مركن 19</t>
+          <t>نخيل سايكس 40 سم</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>وايتكس 50</t>
+          <t>هيدرا علاقي مركن 19</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>وايتكس 50 سم</t>
+          <t>هيدرا علاقي مركن 19</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -3421,11 +3421,11 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>ترحيل تبوك للرياض</t>
+          <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>ياسمين ازرق</t>
+          <t>وايتكس 50</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>ياسمين أزرق / ياسمين ازرق  50 سم</t>
+          <t>وايتكس 50 سم</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -3462,11 +3462,11 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+          <t>ترحيل تبوك للرياض</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>730</v>
+        <v>400</v>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
@@ -3480,36 +3480,77 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
+          <t>ياسمين ازرق</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>ياسمين أزرق / ياسمين ازرق  50 سم</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>معتمد (قرارك)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>مسحوبات تبوك من الرياض + ترحيل تبوك للرياض</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>730</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
           <t>ياسمين هندي كبير</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>ياسمين هندي كبير</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E71" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>معتمد (قرارك)</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>مسحوبات تبوك من الرياض</t>
         </is>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H71" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3645,7 +3686,7 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G3,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G3)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G3,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G3)</f>
         <v/>
       </c>
       <c r="J3" s="4">
@@ -3694,7 +3735,7 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G4)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G4)</f>
         <v/>
       </c>
       <c r="J4" s="4">
@@ -3740,7 +3781,7 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G5,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G5)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G5,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G5)</f>
         <v/>
       </c>
       <c r="J5" s="4">
@@ -3786,7 +3827,7 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G6,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G6)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G6,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G6)</f>
         <v/>
       </c>
       <c r="J6" s="4">
@@ -3832,7 +3873,7 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G7,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G7)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G7,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G7)</f>
         <v/>
       </c>
       <c r="J7" s="4">
@@ -3878,7 +3919,7 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G8,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G8)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G8,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G8)</f>
         <v/>
       </c>
       <c r="J8" s="4">
@@ -3924,7 +3965,7 @@
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G9,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G9)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G9,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G9)</f>
         <v/>
       </c>
       <c r="J9" s="4">
@@ -3970,7 +4011,7 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G10,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G10)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G10,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G10)</f>
         <v/>
       </c>
       <c r="J10" s="4">
@@ -4016,7 +4057,7 @@
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G11,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G11)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G11,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G11)</f>
         <v/>
       </c>
       <c r="J11" s="4">
@@ -4062,7 +4103,7 @@
         <v/>
       </c>
       <c r="I12" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G12)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G12)</f>
         <v/>
       </c>
       <c r="J12" s="4">
@@ -4108,7 +4149,7 @@
         <v/>
       </c>
       <c r="I13" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G13,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G13)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G13,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G13)</f>
         <v/>
       </c>
       <c r="J13" s="4">
@@ -4154,7 +4195,7 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G14,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G14)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G14,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G14)</f>
         <v/>
       </c>
       <c r="J14" s="4">
@@ -4200,7 +4241,7 @@
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G15,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G15)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G15,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G15)</f>
         <v/>
       </c>
       <c r="J15" s="4">
@@ -4246,7 +4287,7 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G16,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G16)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G16,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G16)</f>
         <v/>
       </c>
       <c r="J16" s="4">
@@ -4292,7 +4333,7 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G17)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G17)</f>
         <v/>
       </c>
       <c r="J17" s="4">
@@ -4338,7 +4379,7 @@
         <v/>
       </c>
       <c r="I18" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G18,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G18)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G18,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G18)</f>
         <v/>
       </c>
       <c r="J18" s="4">
@@ -4384,7 +4425,7 @@
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G19)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G19)</f>
         <v/>
       </c>
       <c r="J19" s="4">
@@ -4430,7 +4471,7 @@
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G20,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G20)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G20,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G20)</f>
         <v/>
       </c>
       <c r="J20" s="4">
@@ -4476,7 +4517,7 @@
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G21,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G21)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G21,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G21)</f>
         <v/>
       </c>
       <c r="J21" s="4">
@@ -4522,7 +4563,7 @@
         <v/>
       </c>
       <c r="I22" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G22,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G22)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G22,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G22)</f>
         <v/>
       </c>
       <c r="J22" s="4">
@@ -4568,7 +4609,7 @@
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G23,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G23)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G23,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G23)</f>
         <v/>
       </c>
       <c r="J23" s="4">
@@ -4614,7 +4655,7 @@
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G24,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G24)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G24,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G24)</f>
         <v/>
       </c>
       <c r="J24" s="4">
@@ -4660,7 +4701,7 @@
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G25,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G25)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G25,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G25)</f>
         <v/>
       </c>
       <c r="J25" s="4">
@@ -4706,7 +4747,7 @@
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G26,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G26)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G26,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G26)</f>
         <v/>
       </c>
       <c r="J26" s="4">
@@ -4752,7 +4793,7 @@
         <v/>
       </c>
       <c r="I27" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G27,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G27)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G27,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G27)</f>
         <v/>
       </c>
       <c r="J27" s="4">
@@ -4798,7 +4839,7 @@
         <v/>
       </c>
       <c r="I28" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G28,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G28)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G28,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G28)</f>
         <v/>
       </c>
       <c r="J28" s="4">
@@ -4844,7 +4885,7 @@
         <v/>
       </c>
       <c r="I29" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G29,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G29)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G29,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G29)</f>
         <v/>
       </c>
       <c r="J29" s="4">
@@ -4890,7 +4931,7 @@
         <v/>
       </c>
       <c r="I30" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G30,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G30)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G30,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G30)</f>
         <v/>
       </c>
       <c r="J30" s="4">
@@ -4936,7 +4977,7 @@
         <v/>
       </c>
       <c r="I31" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G31,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G31)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G31,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G31)</f>
         <v/>
       </c>
       <c r="J31" s="4">
@@ -4982,7 +5023,7 @@
         <v/>
       </c>
       <c r="I32" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G32,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G32)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G32,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G32)</f>
         <v/>
       </c>
       <c r="J32" s="4">
@@ -5028,7 +5069,7 @@
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G33,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G33)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G33,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G33)</f>
         <v/>
       </c>
       <c r="J33" s="4">
@@ -5074,7 +5115,7 @@
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G34,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G34)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G34,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G34)</f>
         <v/>
       </c>
       <c r="J34" s="4">
@@ -5120,7 +5161,7 @@
         <v/>
       </c>
       <c r="I35" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G35,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G35)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G35,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G35)</f>
         <v/>
       </c>
       <c r="J35" s="4">
@@ -5166,7 +5207,7 @@
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G36,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G36)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G36,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G36)</f>
         <v/>
       </c>
       <c r="J36" s="4">
@@ -5212,7 +5253,7 @@
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G37,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G37)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G37,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G37)</f>
         <v/>
       </c>
       <c r="J37" s="4">
@@ -5258,7 +5299,7 @@
         <v/>
       </c>
       <c r="I38" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G38,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G38)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G38,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G38)</f>
         <v/>
       </c>
       <c r="J38" s="4">
@@ -5304,7 +5345,7 @@
         <v/>
       </c>
       <c r="I39" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G39,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G39)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G39,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G39)</f>
         <v/>
       </c>
       <c r="J39" s="4">
@@ -5350,7 +5391,7 @@
         <v/>
       </c>
       <c r="I40" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G40,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G40)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G40,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G40)</f>
         <v/>
       </c>
       <c r="J40" s="4">
@@ -5396,7 +5437,7 @@
         <v/>
       </c>
       <c r="I41" s="8">
-        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G41,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G41)</f>
+        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G41,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G41)</f>
         <v/>
       </c>
       <c r="J41" s="4">
@@ -5442,7 +5483,7 @@
         <v/>
       </c>
       <c r="I42" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G42,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G42)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G42,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G42)</f>
         <v/>
       </c>
       <c r="J42" s="4">
@@ -5488,7 +5529,7 @@
         <v/>
       </c>
       <c r="I43" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G43,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G43)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G43,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G43)</f>
         <v/>
       </c>
       <c r="J43" s="4">
@@ -5534,7 +5575,7 @@
         <v/>
       </c>
       <c r="I44" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G44,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G44)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G44,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G44)</f>
         <v/>
       </c>
       <c r="J44" s="4">
@@ -5580,7 +5621,7 @@
         <v/>
       </c>
       <c r="I45" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G45,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G45)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G45,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G45)</f>
         <v/>
       </c>
       <c r="J45" s="4">
@@ -5626,7 +5667,7 @@
         <v/>
       </c>
       <c r="I46" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G46,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G46)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G46,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G46)</f>
         <v/>
       </c>
       <c r="J46" s="4">
@@ -5672,7 +5713,7 @@
         <v/>
       </c>
       <c r="I47" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G47,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G47)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G47,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G47)</f>
         <v/>
       </c>
       <c r="J47" s="4">
@@ -5718,7 +5759,7 @@
         <v/>
       </c>
       <c r="I48" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G48,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G48)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G48,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G48)</f>
         <v/>
       </c>
       <c r="J48" s="4">
@@ -5764,7 +5805,7 @@
         <v/>
       </c>
       <c r="I49" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G49,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G49)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G49,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G49)</f>
         <v/>
       </c>
       <c r="J49" s="4">
@@ -5810,7 +5851,7 @@
         <v/>
       </c>
       <c r="I50" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G50,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G50)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G50,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G50)</f>
         <v/>
       </c>
       <c r="J50" s="4">
@@ -5856,7 +5897,7 @@
         <v/>
       </c>
       <c r="I51" s="4">
-        <f>IFERROR(IF(VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G51,VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G51)</f>
+        <f>IFERROR(IF(VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G51,VLOOKUP("سيلوزيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G51)</f>
         <v/>
       </c>
       <c r="J51" s="4">
@@ -5902,7 +5943,7 @@
         <v/>
       </c>
       <c r="I52" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G52,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G52)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G52,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G52)</f>
         <v/>
       </c>
       <c r="J52" s="4">
@@ -5948,7 +5989,7 @@
         <v/>
       </c>
       <c r="I53" s="8">
-        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G53,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G53)</f>
+        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G53,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G53)</f>
         <v/>
       </c>
       <c r="J53" s="4">
@@ -5994,7 +6035,7 @@
         <v/>
       </c>
       <c r="I54" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G54,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G54)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G54,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G54)</f>
         <v/>
       </c>
       <c r="J54" s="4">
@@ -6040,7 +6081,7 @@
         <v/>
       </c>
       <c r="I55" s="8">
-        <f>IFERROR(IF(VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G55,VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G55)</f>
+        <f>IFERROR(IF(VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G55,VLOOKUP("اشجار تيسبيسيا 2- 3 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G55)</f>
         <v/>
       </c>
       <c r="J55" s="4">
@@ -6086,7 +6127,7 @@
         <v/>
       </c>
       <c r="I56" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G56,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G56)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G56,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G56)</f>
         <v/>
       </c>
       <c r="J56" s="4">
@@ -6132,7 +6173,7 @@
         <v/>
       </c>
       <c r="I57" s="8">
-        <f>IFERROR(IF(VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G57,VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G57)</f>
+        <f>IFERROR(IF(VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G57,VLOOKUP("كيليوس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G57)</f>
         <v/>
       </c>
       <c r="J57" s="4">
@@ -6178,7 +6219,7 @@
         <v/>
       </c>
       <c r="I58" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G58,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G58)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G58,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G58)</f>
         <v/>
       </c>
       <c r="J58" s="4">
@@ -6224,7 +6265,7 @@
         <v/>
       </c>
       <c r="I59" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G59,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G59)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G59,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G59)</f>
         <v/>
       </c>
       <c r="J59" s="4">
@@ -6270,7 +6311,7 @@
         <v/>
       </c>
       <c r="I60" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",G60,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),G60)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",G60,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),G60)</f>
         <v/>
       </c>
       <c r="J60" s="4">
@@ -6324,7 +6365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6432,7 +6473,7 @@
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F3,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F3)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F3,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F3)</f>
         <v/>
       </c>
       <c r="I3" s="4">
@@ -6473,7 +6514,7 @@
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F4)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F4,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F4)</f>
         <v/>
       </c>
       <c r="I4" s="4">
@@ -6514,7 +6555,7 @@
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F5,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F5)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F5,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F5)</f>
         <v/>
       </c>
       <c r="I5" s="4">
@@ -6555,7 +6596,7 @@
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F6,VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F6)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F6,VLOOKUP("ماري جولد فرنسي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F6)</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -6596,7 +6637,7 @@
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F7,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F7)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F7,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F7)</f>
         <v/>
       </c>
       <c r="I7" s="4">
@@ -6637,7 +6678,7 @@
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F8,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F8)</f>
+        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F8,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F8)</f>
         <v/>
       </c>
       <c r="I8" s="4">
@@ -6678,7 +6719,7 @@
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F9,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F9)</f>
+        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F9,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F9)</f>
         <v/>
       </c>
       <c r="I9" s="4">
@@ -6719,7 +6760,7 @@
         <v/>
       </c>
       <c r="H10" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F10,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F10)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F10,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F10)</f>
         <v/>
       </c>
       <c r="I10" s="4">
@@ -6760,7 +6801,7 @@
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F11,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F11)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F11,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F11)</f>
         <v/>
       </c>
       <c r="I11" s="4">
@@ -6801,7 +6842,7 @@
         <v/>
       </c>
       <c r="H12" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F12)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F12,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F12)</f>
         <v/>
       </c>
       <c r="I12" s="4">
@@ -6842,7 +6883,7 @@
         <v/>
       </c>
       <c r="H13" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F13,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F13)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F13,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F13)</f>
         <v/>
       </c>
       <c r="I13" s="4">
@@ -6883,7 +6924,7 @@
         <v/>
       </c>
       <c r="H14" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F14,VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F14)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F14,VLOOKUP("جهنميه تايلاندي مركن 25",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F14)</f>
         <v/>
       </c>
       <c r="I14" s="4">
@@ -6924,7 +6965,7 @@
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F15,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F15)</f>
+        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F15,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F15)</f>
         <v/>
       </c>
       <c r="I15" s="4">
@@ -6965,7 +7006,7 @@
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F16,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F16)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F16,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F16)</f>
         <v/>
       </c>
       <c r="I16" s="4">
@@ -7006,7 +7047,7 @@
         <v/>
       </c>
       <c r="H17" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F17)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F17,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F17)</f>
         <v/>
       </c>
       <c r="I17" s="4">
@@ -7047,7 +7088,7 @@
         <v/>
       </c>
       <c r="H18" s="8">
-        <f>IFERROR(IF(VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F18,VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F18)</f>
+        <f>IFERROR(IF(VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F18,VLOOKUP("بوتنج سويل 70 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F18)</f>
         <v/>
       </c>
       <c r="I18" s="4">
@@ -7088,7 +7129,7 @@
         <v/>
       </c>
       <c r="H19" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F19)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F19,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F19)</f>
         <v/>
       </c>
       <c r="I19" s="4">
@@ -7129,7 +7170,7 @@
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F20,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F20)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F20,VLOOKUP("اقحوان افريقي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F20)</f>
         <v/>
       </c>
       <c r="I20" s="4">
@@ -7170,7 +7211,7 @@
         <v/>
       </c>
       <c r="H21" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F21,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F21)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F21,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F21)</f>
         <v/>
       </c>
       <c r="I21" s="4">
@@ -7211,7 +7252,7 @@
         <v/>
       </c>
       <c r="H22" s="8">
-        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F22,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F22)</f>
+        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F22,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F22)</f>
         <v/>
       </c>
       <c r="I22" s="4">
@@ -7252,7 +7293,7 @@
         <v/>
       </c>
       <c r="H23" s="8">
-        <f>IFERROR(IF(VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F23,VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F23)</f>
+        <f>IFERROR(IF(VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F23,VLOOKUP("بانستيم اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F23)</f>
         <v/>
       </c>
       <c r="I23" s="4">
@@ -7293,7 +7334,7 @@
         <v/>
       </c>
       <c r="H24" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F24,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F24)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F24,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F24)</f>
         <v/>
       </c>
       <c r="I24" s="4">
@@ -7334,7 +7375,7 @@
         <v/>
       </c>
       <c r="H25" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F25,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F25)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F25,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F25)</f>
         <v/>
       </c>
       <c r="I25" s="4">
@@ -7375,7 +7416,7 @@
         <v/>
       </c>
       <c r="H26" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F26,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F26)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F26,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F26)</f>
         <v/>
       </c>
       <c r="I26" s="4">
@@ -7416,7 +7457,7 @@
         <v/>
       </c>
       <c r="H27" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F27,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F27)</f>
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F27,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F27)</f>
         <v/>
       </c>
       <c r="I27" s="4">
@@ -7457,7 +7498,7 @@
         <v/>
       </c>
       <c r="H28" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F28,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F28)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F28,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F28)</f>
         <v/>
       </c>
       <c r="I28" s="4">
@@ -7498,7 +7539,7 @@
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F29,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F29)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F29,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F29)</f>
         <v/>
       </c>
       <c r="I29" s="4">
@@ -7539,7 +7580,7 @@
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F30,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F30)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F30,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F30)</f>
         <v/>
       </c>
       <c r="I30" s="4">
@@ -7580,7 +7621,7 @@
         <v/>
       </c>
       <c r="H31" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F31,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F31)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F31,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F31)</f>
         <v/>
       </c>
       <c r="I31" s="4">
@@ -7621,7 +7662,7 @@
         <v/>
       </c>
       <c r="H32" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F32,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F32)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F32,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F32)</f>
         <v/>
       </c>
       <c r="I32" s="4">
@@ -7662,7 +7703,7 @@
         <v/>
       </c>
       <c r="H33" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F33,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F33)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F33,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F33)</f>
         <v/>
       </c>
       <c r="I33" s="4">
@@ -7703,7 +7744,7 @@
         <v/>
       </c>
       <c r="H34" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F34,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F34)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F34,VLOOKUP("جيرانيوم مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F34)</f>
         <v/>
       </c>
       <c r="I34" s="4">
@@ -7744,7 +7785,7 @@
         <v/>
       </c>
       <c r="H35" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F35,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F35)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F35,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F35)</f>
         <v/>
       </c>
       <c r="I35" s="4">
@@ -7785,7 +7826,7 @@
         <v/>
       </c>
       <c r="H36" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F36,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F36)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F36,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F36)</f>
         <v/>
       </c>
       <c r="I36" s="4">
@@ -7826,7 +7867,7 @@
         <v/>
       </c>
       <c r="H37" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F37,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F37)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F37,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F37)</f>
         <v/>
       </c>
       <c r="I37" s="4">
@@ -7867,7 +7908,7 @@
         <v/>
       </c>
       <c r="H38" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F38,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F38)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F38,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F38)</f>
         <v/>
       </c>
       <c r="I38" s="4">
@@ -7908,7 +7949,7 @@
         <v/>
       </c>
       <c r="H39" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F39,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F39)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F39,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F39)</f>
         <v/>
       </c>
       <c r="I39" s="4">
@@ -7949,7 +7990,7 @@
         <v/>
       </c>
       <c r="H40" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F40,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F40)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F40,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F40)</f>
         <v/>
       </c>
       <c r="I40" s="4">
@@ -7990,7 +8031,7 @@
         <v/>
       </c>
       <c r="H41" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F41,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F41)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F41,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F41)</f>
         <v/>
       </c>
       <c r="I41" s="4">
@@ -8031,7 +8072,7 @@
         <v/>
       </c>
       <c r="H42" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F42,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F42)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F42,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F42)</f>
         <v/>
       </c>
       <c r="I42" s="4">
@@ -8072,7 +8113,7 @@
         <v/>
       </c>
       <c r="H43" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F43,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F43)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F43,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F43)</f>
         <v/>
       </c>
       <c r="I43" s="4">
@@ -8113,7 +8154,7 @@
         <v/>
       </c>
       <c r="H44" s="8">
-        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F44,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F44)</f>
+        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F44,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F44)</f>
         <v/>
       </c>
       <c r="I44" s="4">
@@ -8154,7 +8195,7 @@
         <v/>
       </c>
       <c r="H45" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F45,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F45)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F45,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F45)</f>
         <v/>
       </c>
       <c r="I45" s="4">
@@ -8195,7 +8236,7 @@
         <v/>
       </c>
       <c r="H46" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F46,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F46)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F46,VLOOKUP("قرنفل صيني",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F46)</f>
         <v/>
       </c>
       <c r="I46" s="4">
@@ -8236,7 +8277,7 @@
         <v/>
       </c>
       <c r="H47" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F47,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F47)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F47,VLOOKUP("جيرانيوم مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F47)</f>
         <v/>
       </c>
       <c r="I47" s="4">
@@ -8277,7 +8318,7 @@
         <v/>
       </c>
       <c r="H48" s="8">
-        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F48,VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F48)</f>
+        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F48,VLOOKUP("نخيل سايكس 30",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F48)</f>
         <v/>
       </c>
       <c r="I48" s="4">
@@ -8318,7 +8359,7 @@
         <v/>
       </c>
       <c r="H49" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F49,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F49)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F49,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F49)</f>
         <v/>
       </c>
       <c r="I49" s="4">
@@ -8359,7 +8400,7 @@
         <v/>
       </c>
       <c r="H50" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F50,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F50)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F50,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F50)</f>
         <v/>
       </c>
       <c r="I50" s="4">
@@ -8400,7 +8441,7 @@
         <v/>
       </c>
       <c r="H51" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F51,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F51)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F51,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F51)</f>
         <v/>
       </c>
       <c r="I51" s="4">
@@ -8441,7 +8482,7 @@
         <v/>
       </c>
       <c r="H52" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F52,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F52)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F52,VLOOKUP("اقحوان افريقي هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F52)</f>
         <v/>
       </c>
       <c r="I52" s="4">
@@ -8482,7 +8523,7 @@
         <v/>
       </c>
       <c r="H53" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F53,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F53)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F53,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F53)</f>
         <v/>
       </c>
       <c r="I53" s="4">
@@ -8523,7 +8564,7 @@
         <v/>
       </c>
       <c r="H54" s="8">
-        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F54,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F54)</f>
+        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F54,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F54)</f>
         <v/>
       </c>
       <c r="I54" s="4">
@@ -8564,7 +8605,7 @@
         <v/>
       </c>
       <c r="H55" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F55,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F55)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F55,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F55)</f>
         <v/>
       </c>
       <c r="I55" s="4">
@@ -8605,7 +8646,7 @@
         <v/>
       </c>
       <c r="H56" s="8">
-        <f>IFERROR(IF(VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F56,VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F56)</f>
+        <f>IFERROR(IF(VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F56,VLOOKUP("قرنفل امريكي 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F56)</f>
         <v/>
       </c>
       <c r="I56" s="4">
@@ -8646,7 +8687,7 @@
         <v/>
       </c>
       <c r="H57" s="8">
-        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F57,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F57)</f>
+        <f>IFERROR(IF(VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F57,VLOOKUP("سينيراريا مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F57)</f>
         <v/>
       </c>
       <c r="I57" s="4">
@@ -8687,7 +8728,7 @@
         <v/>
       </c>
       <c r="H58" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F58,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F58)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F58,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F58)</f>
         <v/>
       </c>
       <c r="I58" s="4">
@@ -8728,7 +8769,7 @@
         <v/>
       </c>
       <c r="H59" s="8">
-        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F59,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F59)</f>
+        <f>IFERROR(IF(VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F59,VLOOKUP("منثور مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F59)</f>
         <v/>
       </c>
       <c r="I59" s="4">
@@ -8769,7 +8810,7 @@
         <v/>
       </c>
       <c r="H60" s="4">
-        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F60,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F60)</f>
+        <f>IFERROR(IF(VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F60,VLOOKUP("سالفيا مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F60)</f>
         <v/>
       </c>
       <c r="I60" s="4">
@@ -8810,7 +8851,7 @@
         <v/>
       </c>
       <c r="H61" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F61,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F61)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F61,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F61)</f>
         <v/>
       </c>
       <c r="I61" s="4">
@@ -8851,7 +8892,7 @@
         <v/>
       </c>
       <c r="H62" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F62,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F62)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F62,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F62)</f>
         <v/>
       </c>
       <c r="I62" s="4">
@@ -8892,7 +8933,7 @@
         <v/>
       </c>
       <c r="H63" s="4">
-        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F63,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F63)</f>
+        <f>IFERROR(IF(VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F63,VLOOKUP("هيبوستس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F63)</f>
         <v/>
       </c>
       <c r="I63" s="4">
@@ -8933,7 +8974,7 @@
         <v/>
       </c>
       <c r="H64" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F64,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F64)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F64,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F64)</f>
         <v/>
       </c>
       <c r="I64" s="4">
@@ -8974,7 +9015,7 @@
         <v/>
       </c>
       <c r="H65" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F65,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F65)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F65,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F65)</f>
         <v/>
       </c>
       <c r="I65" s="4">
@@ -9015,7 +9056,7 @@
         <v/>
       </c>
       <c r="H66" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F66,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F66)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F66,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F66)</f>
         <v/>
       </c>
       <c r="I66" s="4">
@@ -9056,7 +9097,7 @@
         <v/>
       </c>
       <c r="H67" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F67,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F67)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F67,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F67)</f>
         <v/>
       </c>
       <c r="I67" s="4">
@@ -9097,7 +9138,7 @@
         <v/>
       </c>
       <c r="H68" s="8">
-        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F68,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F68)</f>
+        <f>IFERROR(IF(VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F68,VLOOKUP("اقحوان افريقي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F68)</f>
         <v/>
       </c>
       <c r="I68" s="4">
@@ -9138,7 +9179,7 @@
         <v/>
       </c>
       <c r="H69" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F69,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F69)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F69,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F69)</f>
         <v/>
       </c>
       <c r="I69" s="4">
@@ -9179,7 +9220,7 @@
         <v/>
       </c>
       <c r="H70" s="8">
-        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F70,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F70)</f>
+        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F70,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F70)</f>
         <v/>
       </c>
       <c r="I70" s="4">
@@ -9220,7 +9261,7 @@
         <v/>
       </c>
       <c r="H71" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F71,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F71)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F71,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F71)</f>
         <v/>
       </c>
       <c r="I71" s="4">
@@ -9261,7 +9302,7 @@
         <v/>
       </c>
       <c r="H72" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F72,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F72)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F72,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F72)</f>
         <v/>
       </c>
       <c r="I72" s="4">
@@ -9302,7 +9343,7 @@
         <v/>
       </c>
       <c r="H73" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F73,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F73)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F73,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F73)</f>
         <v/>
       </c>
       <c r="I73" s="4">
@@ -9343,7 +9384,7 @@
         <v/>
       </c>
       <c r="H74" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F74,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F74)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F74,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F74)</f>
         <v/>
       </c>
       <c r="I74" s="4">
@@ -9384,7 +9425,7 @@
         <v/>
       </c>
       <c r="H75" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F75,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F75)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F75,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F75)</f>
         <v/>
       </c>
       <c r="I75" s="4">
@@ -9425,7 +9466,7 @@
         <v/>
       </c>
       <c r="H76" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F76,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F76)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F76,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F76)</f>
         <v/>
       </c>
       <c r="I76" s="4">
@@ -9466,7 +9507,7 @@
         <v/>
       </c>
       <c r="H77" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F77,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F77)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F77,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F77)</f>
         <v/>
       </c>
       <c r="I77" s="4">
@@ -9507,7 +9548,7 @@
         <v/>
       </c>
       <c r="H78" s="8">
-        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F78,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F78)</f>
+        <f>IFERROR(IF(VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F78,VLOOKUP("جازانيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F78)</f>
         <v/>
       </c>
       <c r="I78" s="4">
@@ -9548,7 +9589,7 @@
         <v/>
       </c>
       <c r="H79" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F79,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F79)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F79,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F79)</f>
         <v/>
       </c>
       <c r="I79" s="4">
@@ -9589,7 +9630,7 @@
         <v/>
       </c>
       <c r="H80" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F80,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F80)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F80,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F80)</f>
         <v/>
       </c>
       <c r="I80" s="4">
@@ -9630,7 +9671,7 @@
         <v/>
       </c>
       <c r="H81" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F81,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F81)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F81,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F81)</f>
         <v/>
       </c>
       <c r="I81" s="4">
@@ -9671,7 +9712,7 @@
         <v/>
       </c>
       <c r="H82" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F82,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F82)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F82,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F82)</f>
         <v/>
       </c>
       <c r="I82" s="4">
@@ -9712,7 +9753,7 @@
         <v/>
       </c>
       <c r="H83" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F83,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F83)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F83,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F83)</f>
         <v/>
       </c>
       <c r="I83" s="4">
@@ -9753,7 +9794,7 @@
         <v/>
       </c>
       <c r="H84" s="4">
-        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F84,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F84)</f>
+        <f>IFERROR(IF(VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F84,VLOOKUP("امرانتس",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F84)</f>
         <v/>
       </c>
       <c r="I84" s="4">
@@ -9794,7 +9835,7 @@
         <v/>
       </c>
       <c r="H85" s="4">
-        <f>IFERROR(IF(VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F85,VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F85)</f>
+        <f>IFERROR(IF(VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F85,VLOOKUP("فضيه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F85)</f>
         <v/>
       </c>
       <c r="I85" s="4">
@@ -9835,7 +9876,7 @@
         <v/>
       </c>
       <c r="H86" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F86,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F86)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F86,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F86)</f>
         <v/>
       </c>
       <c r="I86" s="4">
@@ -9876,7 +9917,7 @@
         <v/>
       </c>
       <c r="H87" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F87,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F87)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F87,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F87)</f>
         <v/>
       </c>
       <c r="I87" s="4">
@@ -9917,7 +9958,7 @@
         <v/>
       </c>
       <c r="H88" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F88,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F88)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F88,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F88)</f>
         <v/>
       </c>
       <c r="I88" s="4">
@@ -9958,7 +9999,7 @@
         <v/>
       </c>
       <c r="H89" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F89,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F89)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F89,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F89)</f>
         <v/>
       </c>
       <c r="I89" s="4">
@@ -9999,7 +10040,7 @@
         <v/>
       </c>
       <c r="H90" s="8">
-        <f>IFERROR(IF(VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F90,VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F90)</f>
+        <f>IFERROR(IF(VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F90,VLOOKUP("كف مريم 1. 5 : 2 م",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F90)</f>
         <v/>
       </c>
       <c r="I90" s="4">
@@ -10040,7 +10081,7 @@
         <v/>
       </c>
       <c r="H91" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F91,VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F91)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F91,VLOOKUP("جهنميه كرويه تايلندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F91)</f>
         <v/>
       </c>
       <c r="I91" s="4">
@@ -10081,7 +10122,7 @@
         <v/>
       </c>
       <c r="H92" s="4">
-        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F92,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F92)</f>
+        <f>IFERROR(IF(VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F92,VLOOKUP("زينيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F92)</f>
         <v/>
       </c>
       <c r="I92" s="4">
@@ -10122,7 +10163,7 @@
         <v/>
       </c>
       <c r="H93" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F93,VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F93)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F93,VLOOKUP("جهنميه كرويه تايلندي صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F93)</f>
         <v/>
       </c>
       <c r="I93" s="4">
@@ -10163,7 +10204,7 @@
         <v/>
       </c>
       <c r="H94" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F94,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F94)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F94,VLOOKUP("اكاسيا جلوكا من 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F94)</f>
         <v/>
       </c>
       <c r="I94" s="4">
@@ -10204,7 +10245,7 @@
         <v/>
       </c>
       <c r="H95" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F95,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F95)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F95,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F95)</f>
         <v/>
       </c>
       <c r="I95" s="4">
@@ -10245,7 +10286,7 @@
         <v/>
       </c>
       <c r="H96" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F96,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F96)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F96,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F96)</f>
         <v/>
       </c>
       <c r="I96" s="4">
@@ -10286,7 +10327,7 @@
         <v/>
       </c>
       <c r="H97" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F97,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F97)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F97,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F97)</f>
         <v/>
       </c>
       <c r="I97" s="4">
@@ -10327,7 +10368,7 @@
         <v/>
       </c>
       <c r="H98" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F98,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F98)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F98,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F98)</f>
         <v/>
       </c>
       <c r="I98" s="4">
@@ -10368,7 +10409,7 @@
         <v/>
       </c>
       <c r="H99" s="8">
-        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F99,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F99)</f>
+        <f>IFERROR(IF(VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F99,VLOOKUP("تراديسكانتيا مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F99)</f>
         <v/>
       </c>
       <c r="I99" s="4">
@@ -10409,7 +10450,7 @@
         <v/>
       </c>
       <c r="H100" s="8">
-        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F100,VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F100)</f>
+        <f>IFERROR(IF(VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F100,VLOOKUP("نخيل سايكس 40",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F100)</f>
         <v/>
       </c>
       <c r="I100" s="4">
@@ -10450,7 +10491,7 @@
         <v/>
       </c>
       <c r="H101" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F101,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F101)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F101,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F101)</f>
         <v/>
       </c>
       <c r="I101" s="4">
@@ -10491,7 +10532,7 @@
         <v/>
       </c>
       <c r="H102" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F102,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F102)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F102,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F102)</f>
         <v/>
       </c>
       <c r="I102" s="4">
@@ -10532,7 +10573,7 @@
         <v/>
       </c>
       <c r="H103" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F103,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F103)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F103,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F103)</f>
         <v/>
       </c>
       <c r="I103" s="4">
@@ -10573,7 +10614,7 @@
         <v/>
       </c>
       <c r="H104" s="8">
-        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F104,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F104)</f>
+        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F104,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F104)</f>
         <v/>
       </c>
       <c r="I104" s="4">
@@ -10614,7 +10655,7 @@
         <v/>
       </c>
       <c r="H105" s="8">
-        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F105,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F105)</f>
+        <f>IFERROR(IF(VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F105,VLOOKUP("هيدرا علاقي مركن 19",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F105)</f>
         <v/>
       </c>
       <c r="I105" s="4">
@@ -10655,7 +10696,7 @@
         <v/>
       </c>
       <c r="H106" s="8">
-        <f>IFERROR(IF(VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F106,VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F106)</f>
+        <f>IFERROR(IF(VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F106,VLOOKUP("سيسبانيا 1 - 2 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F106)</f>
         <v/>
       </c>
       <c r="I106" s="4">
@@ -10696,7 +10737,7 @@
         <v/>
       </c>
       <c r="H107" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F107,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F107)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F107,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F107)</f>
         <v/>
       </c>
       <c r="I107" s="4">
@@ -10737,7 +10778,7 @@
         <v/>
       </c>
       <c r="H108" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F108,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F108)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F108,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F108)</f>
         <v/>
       </c>
       <c r="I108" s="4">
@@ -10778,7 +10819,7 @@
         <v/>
       </c>
       <c r="H109" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F109,VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F109)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F109,VLOOKUP("جهنميه بلدي 1 متر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F109)</f>
         <v/>
       </c>
       <c r="I109" s="4">
@@ -10819,7 +10860,7 @@
         <v/>
       </c>
       <c r="H110" s="8">
-        <f>IFERROR(IF(VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F110,VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F110)</f>
+        <f>IFERROR(IF(VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F110,VLOOKUP("فيكس بندا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F110)</f>
         <v/>
       </c>
       <c r="I110" s="4">
@@ -10860,7 +10901,7 @@
         <v/>
       </c>
       <c r="H111" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F111,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F111)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F111,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F111)</f>
         <v/>
       </c>
       <c r="I111" s="4">
@@ -10905,7 +10946,7 @@
         <v/>
       </c>
       <c r="H112" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F112,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F112)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F112,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F112)</f>
         <v/>
       </c>
       <c r="I112" s="4">
@@ -10950,7 +10991,7 @@
         <v/>
       </c>
       <c r="H113" s="8">
-        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F113,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F113)</f>
+        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F113,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F113)</f>
         <v/>
       </c>
       <c r="I113" s="4">
@@ -10995,7 +11036,7 @@
         <v/>
       </c>
       <c r="H114" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F114,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F114)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F114,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F114)</f>
         <v/>
       </c>
       <c r="I114" s="4">
@@ -11040,7 +11081,7 @@
         <v/>
       </c>
       <c r="H115" s="8">
-        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F115,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F115)</f>
+        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F115,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F115)</f>
         <v/>
       </c>
       <c r="I115" s="4">
@@ -11085,7 +11126,7 @@
         <v/>
       </c>
       <c r="H116" s="8">
-        <f>IFERROR(IF(VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F116,VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F116)</f>
+        <f>IFERROR(IF(VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F116,VLOOKUP("تجيل كروي مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F116)</f>
         <v/>
       </c>
       <c r="I116" s="4">
@@ -11130,7 +11171,7 @@
         <v/>
       </c>
       <c r="H117" s="8">
-        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F117,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F117)</f>
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F117,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F117)</f>
         <v/>
       </c>
       <c r="I117" s="4">
@@ -11175,7 +11216,7 @@
         <v/>
       </c>
       <c r="H118" s="8">
-        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F118,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F118)</f>
+        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F118,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F118)</f>
         <v/>
       </c>
       <c r="I118" s="4">
@@ -11220,7 +11261,7 @@
         <v/>
       </c>
       <c r="H119" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F119,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F119)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F119,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F119)</f>
         <v/>
       </c>
       <c r="I119" s="4">
@@ -11265,7 +11306,7 @@
         <v/>
       </c>
       <c r="H120" s="8">
-        <f>IFERROR(IF(VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F120,VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F120)</f>
+        <f>IFERROR(IF(VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F120,VLOOKUP("ياسمين هندي كبير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F120)</f>
         <v/>
       </c>
       <c r="I120" s="4">
@@ -11310,7 +11351,7 @@
         <v/>
       </c>
       <c r="H121" s="8">
-        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F121,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F121)</f>
+        <f>IFERROR(IF(VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F121,VLOOKUP("جيرانيوم هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F121)</f>
         <v/>
       </c>
       <c r="I121" s="4">
@@ -11355,7 +11396,7 @@
         <v/>
       </c>
       <c r="H122" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F122,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F122)</f>
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F122,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F122)</f>
         <v/>
       </c>
       <c r="I122" s="4">
@@ -11400,7 +11441,7 @@
         <v/>
       </c>
       <c r="H123" s="8">
-        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F123,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F123)</f>
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F123,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F123)</f>
         <v/>
       </c>
       <c r="I123" s="4">
@@ -11445,7 +11486,7 @@
         <v/>
       </c>
       <c r="H124" s="4">
-        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F124,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F124)</f>
+        <f>IFERROR(IF(VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F124,VLOOKUP("ماري جولد",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F124)</f>
         <v/>
       </c>
       <c r="I124" s="4">
@@ -11490,7 +11531,7 @@
         <v/>
       </c>
       <c r="H125" s="8">
-        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F125,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F125)</f>
+        <f>IFERROR(IF(VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F125,VLOOKUP("كلانشو هولندي مركن 12",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F125)</f>
         <v/>
       </c>
       <c r="I125" s="4">
@@ -11535,7 +11576,7 @@
         <v/>
       </c>
       <c r="H126" s="8">
-        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F126,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F126)</f>
+        <f>IFERROR(IF(VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F126,VLOOKUP("ملفوف مركن 9",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F126)</f>
         <v/>
       </c>
       <c r="I126" s="4">
@@ -11580,7 +11621,7 @@
         <v/>
       </c>
       <c r="H127" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F127,VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F127)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F127,VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F127)</f>
         <v/>
       </c>
       <c r="I127" s="4">
@@ -11602,20 +11643,20 @@
         <v>126</v>
       </c>
       <c r="B128" s="7" t="n">
-        <v>46163</v>
+        <v>45909</v>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>طلب 58991 (#299/#301)</t>
+          <t>RNT-2141</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>مركن 16 سم</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-17900</v>
+        <v>15000</v>
       </c>
       <c r="F128" s="4" t="n">
         <v>0.5</v>
@@ -11624,8 +11665,8 @@
         <f>IF(F128="","",E128*F128)</f>
         <v/>
       </c>
-      <c r="H128" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F128,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F128)</f>
+      <c r="H128" s="8">
+        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F128,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F128)</f>
         <v/>
       </c>
       <c r="I128" s="4">
@@ -11638,38 +11679,128 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
+          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>45909</v>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>RNT-2141</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>كمبوست 10 ك</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="4">
+        <f>IF(F129="","",E129*F129)</f>
+        <v/>
+      </c>
+      <c r="H129" s="8">
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F129,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F129)</f>
+        <v/>
+      </c>
+      <c r="I129" s="4">
+        <f>IF(H129="","",E129*H129)</f>
+        <v/>
+      </c>
+      <c r="J129" s="4">
+        <f>IF(OR(G129="",I129=""),"",G129-I129)</f>
+        <v/>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>طلب 58991 (#299/#301)</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>-17900</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G130" s="4">
+        <f>IF(F130="","",E130*F130)</f>
+        <v/>
+      </c>
+      <c r="H130" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
+        <v/>
+      </c>
+      <c r="I130" s="4">
+        <f>IF(H130="","",E130*H130)</f>
+        <v/>
+      </c>
+      <c r="J130" s="4">
+        <f>IF(OR(G130="",I130=""),"",G130-I130)</f>
+        <v/>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
           <t>خصم كمية مرفوضة/مفقودة مع المناديب (حسب قرارك)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="9" t="n"/>
-      <c r="B129" s="9" t="n"/>
-      <c r="C129" s="9" t="n"/>
-      <c r="D129" s="10" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E129" s="11">
-        <f>SUM(E3:E128)</f>
-        <v/>
-      </c>
-      <c r="F129" s="9" t="n"/>
-      <c r="G129" s="11">
-        <f>SUM(G3:G128)</f>
-        <v/>
-      </c>
-      <c r="H129" s="9" t="n"/>
-      <c r="I129" s="11">
-        <f>SUM(I3:I128)</f>
-        <v/>
-      </c>
-      <c r="J129" s="11">
-        <f>SUM(J3:J128)</f>
-        <v/>
-      </c>
-      <c r="K129" s="9" t="n"/>
+      <c r="E131" s="11">
+        <f>SUM(E3:E130)</f>
+        <v/>
+      </c>
+      <c r="F131" s="9" t="n"/>
+      <c r="G131" s="11">
+        <f>SUM(G3:G130)</f>
+        <v/>
+      </c>
+      <c r="H131" s="9" t="n"/>
+      <c r="I131" s="11">
+        <f>SUM(I3:I130)</f>
+        <v/>
+      </c>
+      <c r="J131" s="11">
+        <f>SUM(J3:J130)</f>
+        <v/>
+      </c>
+      <c r="K131" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11790,7 +11921,7 @@
         <v/>
       </c>
       <c r="H3" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F3,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F3)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F3,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F3)</f>
         <v/>
       </c>
       <c r="I3" s="4">
@@ -11835,7 +11966,7 @@
         <v/>
       </c>
       <c r="H4" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F4,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F4)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F4,VLOOKUP("حجر ديكوري ابيض لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F4)</f>
         <v/>
       </c>
       <c r="I4" s="4">
@@ -11880,7 +12011,7 @@
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F5,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F5)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F5,VLOOKUP("حجر ديكوري اسود لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F5)</f>
         <v/>
       </c>
       <c r="I5" s="4">
@@ -11925,7 +12056,7 @@
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F6,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F6)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F6,VLOOKUP("حجر ديكوري احمر لامع 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F6)</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -11970,7 +12101,7 @@
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F7,VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F7)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F7,VLOOKUP("حجر ديكوري احمر مطفي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F7)</f>
         <v/>
       </c>
       <c r="I7" s="4">
@@ -12015,7 +12146,7 @@
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F8,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F8)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F8,VLOOKUP("حجر ديكوري اصفر مطفي 1: 3",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F8)</f>
         <v/>
       </c>
       <c r="I8" s="4">
@@ -12060,7 +12191,7 @@
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F9,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F9)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F9,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F9)</f>
         <v/>
       </c>
       <c r="I9" s="4">
@@ -12101,7 +12232,7 @@
         <v/>
       </c>
       <c r="H10" s="8">
-        <f>IFERROR(IF(VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F10,VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F10)</f>
+        <f>IFERROR(IF(VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F10,VLOOKUP("وايتكس 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F10)</f>
         <v/>
       </c>
       <c r="I10" s="4">
@@ -12142,7 +12273,7 @@
         <v/>
       </c>
       <c r="H11" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F11,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F11)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F11,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F11)</f>
         <v/>
       </c>
       <c r="I11" s="4">
@@ -12183,7 +12314,7 @@
         <v/>
       </c>
       <c r="H12" s="8">
-        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F12,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F12)</f>
+        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F12,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F12)</f>
         <v/>
       </c>
       <c r="I12" s="4">
@@ -12224,7 +12355,7 @@
         <v/>
       </c>
       <c r="H13" s="8">
-        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F13,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F13)</f>
+        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F13,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F13)</f>
         <v/>
       </c>
       <c r="I13" s="4">
@@ -12265,7 +12396,7 @@
         <v/>
       </c>
       <c r="H14" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F14,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F14)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F14,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F14)</f>
         <v/>
       </c>
       <c r="I14" s="4">
@@ -12306,7 +12437,7 @@
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F15,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F15)</f>
+        <f>IFERROR(IF(VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F15,VLOOKUP("اليسوم",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F15)</f>
         <v/>
       </c>
       <c r="I15" s="4">
@@ -12347,7 +12478,7 @@
         <v/>
       </c>
       <c r="H16" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F16,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F16)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F16,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F16)</f>
         <v/>
       </c>
       <c r="I16" s="4">
@@ -12388,7 +12519,7 @@
         <v/>
       </c>
       <c r="H17" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F17,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F17)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F17,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F17)</f>
         <v/>
       </c>
       <c r="I17" s="4">
@@ -12429,7 +12560,7 @@
         <v/>
       </c>
       <c r="H18" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F18,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F18)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F18,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F18)</f>
         <v/>
       </c>
       <c r="I18" s="4">
@@ -12470,7 +12601,7 @@
         <v/>
       </c>
       <c r="H19" s="8">
-        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F19,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F19)</f>
+        <f>IFERROR(IF(VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F19,VLOOKUP("اكاليفا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F19)</f>
         <v/>
       </c>
       <c r="I19" s="4">
@@ -12511,7 +12642,7 @@
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F20,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F20)</f>
+        <f>IFERROR(IF(VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F20,VLOOKUP("حجر ديكوري ابيض مطفي 3: 5",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F20)</f>
         <v/>
       </c>
       <c r="I20" s="4">
@@ -12549,7 +12680,7 @@
         <v/>
       </c>
       <c r="H21" s="8">
-        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F21,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F21)</f>
+        <f>IFERROR(IF(VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F21,VLOOKUP("جهنميه بلدي 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F21)</f>
         <v/>
       </c>
       <c r="I21" s="4">
@@ -12591,7 +12722,7 @@
         <v/>
       </c>
       <c r="H22" s="8">
-        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F22,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F22)</f>
+        <f>IFERROR(IF(VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F22,VLOOKUP("دورانتا اخضر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F22)</f>
         <v/>
       </c>
       <c r="I22" s="4">
@@ -12633,7 +12764,7 @@
         <v/>
       </c>
       <c r="H23" s="8">
-        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F23,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F23)</f>
+        <f>IFERROR(IF(VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F23,VLOOKUP("لانتانا لبناني صغير",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F23)</f>
         <v/>
       </c>
       <c r="I23" s="4">
@@ -12675,7 +12806,7 @@
         <v/>
       </c>
       <c r="H24" s="8">
-        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F24,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F24)</f>
+        <f>IFERROR(IF(VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F24,VLOOKUP("رويليا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F24)</f>
         <v/>
       </c>
       <c r="I24" s="4">
@@ -12717,7 +12848,7 @@
         <v/>
       </c>
       <c r="H25" s="8">
-        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F25,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F25)</f>
+        <f>IFERROR(IF(VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F25,VLOOKUP("تيكوماريا 50",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F25)</f>
         <v/>
       </c>
       <c r="I25" s="4">
@@ -12759,7 +12890,7 @@
         <v/>
       </c>
       <c r="H26" s="8">
-        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F26,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F26)</f>
+        <f>IFERROR(IF(VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F26,VLOOKUP("فل بلدي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F26)</f>
         <v/>
       </c>
       <c r="I26" s="4">
@@ -12801,7 +12932,7 @@
         <v/>
       </c>
       <c r="H27" s="8">
-        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F27,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F27)</f>
+        <f>IFERROR(IF(VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F27,VLOOKUP("ياسمين ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F27)</f>
         <v/>
       </c>
       <c r="I27" s="4">
@@ -12846,7 +12977,7 @@
         <v/>
       </c>
       <c r="H28" s="8">
-        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F28,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F28)</f>
+        <f>IFERROR(IF(VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F28,VLOOKUP("بيرلايت 100 لتر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F28)</f>
         <v/>
       </c>
       <c r="I28" s="4">
@@ -12891,7 +13022,7 @@
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F29,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F29)</f>
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F29,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F29)</f>
         <v/>
       </c>
       <c r="I29" s="4">
@@ -13053,7 +13184,7 @@
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F3,VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F3)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F3,VLOOKUP("فينكا ابيض نقطه حمراء",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F3)</f>
         <v/>
       </c>
       <c r="I3" s="4">
@@ -13095,7 +13226,7 @@
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F4,VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F4)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F4,VLOOKUP("فينكا احمر بنقطه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F4)</f>
         <v/>
       </c>
       <c r="I4" s="4">
@@ -13137,7 +13268,7 @@
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F5,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F5)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F5,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F5)</f>
         <v/>
       </c>
       <c r="I5" s="4">
@@ -13179,7 +13310,7 @@
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F6,VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F6)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F6,VLOOKUP("فينكا ازرق",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F6)</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -13221,7 +13352,7 @@
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F7,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F7)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F7,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F7)</f>
         <v/>
       </c>
       <c r="I7" s="4">
@@ -13263,7 +13394,7 @@
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F8,VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F8)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F8,VLOOKUP("فينكا مشمشي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F8)</f>
         <v/>
       </c>
       <c r="I8" s="4">
@@ -13305,7 +13436,7 @@
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F9,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F9)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F9,VLOOKUP("فينكا احمر",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F9)</f>
         <v/>
       </c>
       <c r="I9" s="4">
@@ -13347,7 +13478,7 @@
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F10,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F10)</f>
+        <f>IFERROR(IF(VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F10,VLOOKUP("فينكا ابيض",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F10)</f>
         <v/>
       </c>
       <c r="I10" s="4">
@@ -13389,7 +13520,7 @@
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F11,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F11)</f>
+        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F11,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F11)</f>
         <v/>
       </c>
       <c r="I11" s="4">
@@ -13431,7 +13562,7 @@
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F12,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F12)</f>
+        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F12,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F12)</f>
         <v/>
       </c>
       <c r="I12" s="4">
@@ -13473,7 +13604,7 @@
         <v/>
       </c>
       <c r="H13" s="4">
-        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)="",F13,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$70,4,FALSE)),F13)</f>
+        <f>IFERROR(IF(VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F13,VLOOKUP("موسميه",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F13)</f>
         <v/>
       </c>
       <c r="I13" s="4">
@@ -13530,7 +13661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13638,19 +13769,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>RNT-2141</t>
+          <t>RNP-2297</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>45909</v>
+        <v>45926</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>TRANSACTIONS BETWEEN RIYADH-TABUK</t>
+          <t>NESMA ELSHARQ-PROJECTS</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8855</v>
+        <v>5433.75</v>
       </c>
       <c r="G4" s="4">
         <f>ROUND(F4/1.15,2)</f>
@@ -13673,11 +13804,11 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>RNP-2297</t>
+          <t>RNP-2427</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -13685,7 +13816,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5433.75</v>
+        <v>7078.25</v>
       </c>
       <c r="G5" s="4">
         <f>ROUND(F5/1.15,2)</f>
@@ -13698,52 +13829,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>RNP-2427</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>45938</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>NESMA ELSHARQ-PROJECTS</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>7078.25</v>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="F6" s="4">
+        <f>SUM(F3:F5)</f>
+        <v/>
       </c>
       <c r="G6" s="4">
-        <f>ROUND(F6/1.15,2)</f>
-        <v/>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="F7" s="4">
-        <f>SUM(F3:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="4">
-        <f>SUM(G3:G6)</f>
+        <f>SUM(G3:G5)</f>
         <v/>
       </c>
     </row>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -560,15 +560,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'مسحوبات نسما من الرياض'!G131</f>
+        <f>'مسحوبات نسما من الرياض'!G132</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'مسحوبات نسما من الرياض'!I131</f>
+        <f>'مسحوبات نسما من الرياض'!I132</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'مسحوبات نسما من الرياض'!J131</f>
+        <f>'مسحوبات نسما من الرياض'!J132</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!F6</f>
+        <f>'سندات بدون تفصيل أصناف'!F5</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!G6</f>
+        <f>'سندات بدون تفصيل أصناف'!G5</f>
         <v/>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>33000</v>
+        <v>73000</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>RNP-2293</t>
+          <t>RNP-2297</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -6525,7 +6525,11 @@
         <f>IF(OR(G4="",I4=""),"",G4-I4)</f>
         <v/>
       </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>رقم السند مصحح: المحاسب كتبه RNP-2293 والصحيح RNP-2297 (قيمة النظام 4,725)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -6536,7 +6540,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>RNP-2293</t>
+          <t>RNP-2297</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -6566,7 +6570,11 @@
         <f>IF(OR(G5="",I5=""),"",G5-I5)</f>
         <v/>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>رقم السند مصحح: المحاسب كتبه RNP-2293 والصحيح RNP-2297 (قيمة النظام 4,725)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -6577,7 +6585,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>RNP-2293</t>
+          <t>RNP-2297</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -6607,7 +6615,11 @@
         <f>IF(OR(G6="",I6=""),"",G6-I6)</f>
         <v/>
       </c>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>رقم السند مصحح: المحاسب كتبه RNP-2293 والصحيح RNP-2297 (قيمة النظام 4,725)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -11643,30 +11655,30 @@
         <v>126</v>
       </c>
       <c r="B128" s="7" t="n">
-        <v>45909</v>
+        <v>45926</v>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>RNT-2141</t>
+          <t>RNP-2293</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>مركن 16 سم</t>
+          <t>زهور فينكا</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G128" s="4">
         <f>IF(F128="","",E128*F128)</f>
         <v/>
       </c>
-      <c r="H128" s="8">
-        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F128,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F128)</f>
+      <c r="H128" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F128,VLOOKUP("فينكا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F128)</f>
         <v/>
       </c>
       <c r="I128" s="4">
@@ -11679,7 +11691,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+          <t>حسب إفادتك – 40,000 فينكا، مطابق لقيمة النظام 22,000 قبل الضريبة</t>
         </is>
       </c>
     </row>
@@ -11697,21 +11709,21 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>مركن 16 سم</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>100</v>
+        <v>15000</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G129" s="4">
         <f>IF(F129="","",E129*F129)</f>
         <v/>
       </c>
       <c r="H129" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F129,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F129)</f>
+        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F129,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F129)</f>
         <v/>
       </c>
       <c r="I129" s="4">
@@ -11733,30 +11745,30 @@
         <v>128</v>
       </c>
       <c r="B130" s="7" t="n">
-        <v>46163</v>
+        <v>45909</v>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>طلب 58991 (#299/#301)</t>
+          <t>RNT-2141</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-17900</v>
+        <v>100</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G130" s="4">
         <f>IF(F130="","",E130*F130)</f>
         <v/>
       </c>
-      <c r="H130" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
+      <c r="H130" s="8">
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
         <v/>
       </c>
       <c r="I130" s="4">
@@ -11769,38 +11781,83 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
+          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>طلب 58991 (#299/#301)</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>-17900</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G131" s="4">
+        <f>IF(F131="","",E131*F131)</f>
+        <v/>
+      </c>
+      <c r="H131" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F131,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F131)</f>
+        <v/>
+      </c>
+      <c r="I131" s="4">
+        <f>IF(H131="","",E131*H131)</f>
+        <v/>
+      </c>
+      <c r="J131" s="4">
+        <f>IF(OR(G131="",I131=""),"",G131-I131)</f>
+        <v/>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
           <t>خصم كمية مرفوضة/مفقودة مع المناديب (حسب قرارك)</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="9" t="n"/>
-      <c r="B131" s="9" t="n"/>
-      <c r="C131" s="9" t="n"/>
-      <c r="D131" s="10" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E131" s="11">
-        <f>SUM(E3:E130)</f>
-        <v/>
-      </c>
-      <c r="F131" s="9" t="n"/>
-      <c r="G131" s="11">
-        <f>SUM(G3:G130)</f>
-        <v/>
-      </c>
-      <c r="H131" s="9" t="n"/>
-      <c r="I131" s="11">
-        <f>SUM(I3:I130)</f>
-        <v/>
-      </c>
-      <c r="J131" s="11">
-        <f>SUM(J3:J130)</f>
-        <v/>
-      </c>
-      <c r="K131" s="9" t="n"/>
+      <c r="E132" s="11">
+        <f>SUM(E3:E131)</f>
+        <v/>
+      </c>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="11">
+        <f>SUM(G3:G131)</f>
+        <v/>
+      </c>
+      <c r="H132" s="9" t="n"/>
+      <c r="I132" s="11">
+        <f>SUM(I3:I131)</f>
+        <v/>
+      </c>
+      <c r="J132" s="11">
+        <f>SUM(J3:J131)</f>
+        <v/>
+      </c>
+      <c r="K132" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13661,7 +13718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13769,11 +13826,11 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>RNP-2297</t>
+          <t>RNP-2427</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -13781,7 +13838,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5433.75</v>
+        <v>7078.25</v>
       </c>
       <c r="G4" s="4">
         <f>ROUND(F4/1.15,2)</f>
@@ -13794,52 +13851,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>RNP-2427</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>45938</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>NESMA ELSHARQ-PROJECTS</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>7078.25</v>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="F5" s="4">
+        <f>SUM(F3:F4)</f>
+        <v/>
       </c>
       <c r="G5" s="4">
-        <f>ROUND(F5/1.15,2)</f>
-        <v/>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="F6" s="4">
-        <f>SUM(F3:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="4">
-        <f>SUM(G3:G5)</f>
+        <f>SUM(G3:G4)</f>
         <v/>
       </c>
     </row>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -560,15 +560,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'مسحوبات نسما من الرياض'!G132</f>
+        <f>'مسحوبات نسما من الرياض'!G133</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'مسحوبات نسما من الرياض'!I132</f>
+        <f>'مسحوبات نسما من الرياض'!I133</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'مسحوبات نسما من الرياض'!J132</f>
+        <f>'مسحوبات نسما من الرياض'!J133</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!F5</f>
+        <f>'سندات بدون تفصيل أصناف'!F4</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!G5</f>
+        <f>'سندات بدون تفصيل أصناف'!G4</f>
         <v/>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.5 / 0.7 / 0.75</t>
+          <t>0.5 / 0.55 / 0.7 / 0.75</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>259147</v>
+        <v>270147</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>0.5</v>
@@ -6365,7 +6365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11700,30 +11700,30 @@
         <v>127</v>
       </c>
       <c r="B129" s="7" t="n">
-        <v>45909</v>
+        <v>45938</v>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>RNT-2141</t>
+          <t>RNP-2427</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>مركن 16 سم</t>
+          <t>زهور بيتونيا</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G129" s="4">
         <f>IF(F129="","",E129*F129)</f>
         <v/>
       </c>
-      <c r="H129" s="8">
-        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F129,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F129)</f>
+      <c r="H129" s="4">
+        <f>IFERROR(IF(VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F129,VLOOKUP("بيتونيا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F129)</f>
         <v/>
       </c>
       <c r="I129" s="4">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+          <t>حسب إفادتك – 11,000 بيتونيا (قيمة النظام 6,155 قبل الضريبة – فرق 105 عن 0.55)</t>
         </is>
       </c>
     </row>
@@ -11754,21 +11754,21 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>مركن 16 سم</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>100</v>
+        <v>15000</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G130" s="4">
         <f>IF(F130="","",E130*F130)</f>
         <v/>
       </c>
       <c r="H130" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
+        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
         <v/>
       </c>
       <c r="I130" s="4">
@@ -11790,30 +11790,30 @@
         <v>129</v>
       </c>
       <c r="B131" s="7" t="n">
-        <v>46163</v>
+        <v>45909</v>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>طلب 58991 (#299/#301)</t>
+          <t>RNT-2141</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>-17900</v>
+        <v>100</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G131" s="4">
         <f>IF(F131="","",E131*F131)</f>
         <v/>
       </c>
-      <c r="H131" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F131,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F131)</f>
+      <c r="H131" s="8">
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F131,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F131)</f>
         <v/>
       </c>
       <c r="I131" s="4">
@@ -11826,38 +11826,83 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
+          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>طلب 58991 (#299/#301)</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>-17900</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G132" s="4">
+        <f>IF(F132="","",E132*F132)</f>
+        <v/>
+      </c>
+      <c r="H132" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F132,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F132)</f>
+        <v/>
+      </c>
+      <c r="I132" s="4">
+        <f>IF(H132="","",E132*H132)</f>
+        <v/>
+      </c>
+      <c r="J132" s="4">
+        <f>IF(OR(G132="",I132=""),"",G132-I132)</f>
+        <v/>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
           <t>خصم كمية مرفوضة/مفقودة مع المناديب (حسب قرارك)</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="9" t="n"/>
-      <c r="B132" s="9" t="n"/>
-      <c r="C132" s="9" t="n"/>
-      <c r="D132" s="10" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="9" t="n"/>
+      <c r="B133" s="9" t="n"/>
+      <c r="C133" s="9" t="n"/>
+      <c r="D133" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E132" s="11">
-        <f>SUM(E3:E131)</f>
-        <v/>
-      </c>
-      <c r="F132" s="9" t="n"/>
-      <c r="G132" s="11">
-        <f>SUM(G3:G131)</f>
-        <v/>
-      </c>
-      <c r="H132" s="9" t="n"/>
-      <c r="I132" s="11">
-        <f>SUM(I3:I131)</f>
-        <v/>
-      </c>
-      <c r="J132" s="11">
-        <f>SUM(J3:J131)</f>
-        <v/>
-      </c>
-      <c r="K132" s="9" t="n"/>
+      <c r="E133" s="11">
+        <f>SUM(E3:E132)</f>
+        <v/>
+      </c>
+      <c r="F133" s="9" t="n"/>
+      <c r="G133" s="11">
+        <f>SUM(G3:G132)</f>
+        <v/>
+      </c>
+      <c r="H133" s="9" t="n"/>
+      <c r="I133" s="11">
+        <f>SUM(I3:I132)</f>
+        <v/>
+      </c>
+      <c r="J133" s="11">
+        <f>SUM(J3:J132)</f>
+        <v/>
+      </c>
+      <c r="K133" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13718,7 +13763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13816,52 +13861,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RNP-2427</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>45938</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NESMA ELSHARQ-PROJECTS</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>7078.25</v>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="F4" s="4">
+        <f>SUM(F3:F3)</f>
+        <v/>
       </c>
       <c r="G4" s="4">
-        <f>ROUND(F4/1.15,2)</f>
-        <v/>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="F5" s="4">
-        <f>SUM(F3:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="4">
-        <f>SUM(G3:G4)</f>
+        <f>SUM(G3:G3)</f>
         <v/>
       </c>
     </row>

--- a/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
+++ b/التسعير_الموحد_للمسحوبات_والترحيل.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,7 +119,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -560,15 +559,15 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'مسحوبات نسما من الرياض'!G133</f>
+        <f>'مسحوبات نسما من الرياض'!G134</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'مسحوبات نسما من الرياض'!I133</f>
+        <f>'مسحوبات نسما من الرياض'!I134</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'مسحوبات نسما من الرياض'!J133</f>
+        <f>'مسحوبات نسما من الرياض'!J134</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -625,78 +624,58 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>سندات بدون تفصيل أصناف (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="B7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!F4</f>
-        <v/>
-      </c>
-      <c r="C7" s="4">
-        <f>'سندات بدون تفصيل أصناف'!G4</f>
-        <v/>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>تحتاج أصناف أو اعتماد القيمة</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ملاحظات:</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ملاحظات:</t>
+          <t>1) الأصناف (فينكا – زينيا – امرانتس – بيتونيا – سيلوزيا – فضية – ماري جولد – سالفيا – هيبوستس – الزهور الموسمية) موحدة 0.50 للطرفين في كل العقود والمسحوبات.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1) الأصناف (فينكا – زينيا – امرانتس – بيتونيا – سيلوزيا – فضية – ماري جولد – سالفيا – هيبوستس – الزهور الموسمية) موحدة 0.50 للطرفين في كل العقود والمسحوبات.</t>
+          <t>2) باقي الأصناف: السعر الموحد يُدخل في "قائمة الأسعار الموحدة" (الخانة الصفراء) – وإذا تُركت فارغة يُستخدم السعر المسجل بالسند.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2) باقي الأصناف: السعر الموحد يُدخل في "قائمة الأسعار الموحدة" (الخانة الصفراء) – وإذا تُركت فارغة يُستخدم السعر المسجل بالسند.</t>
+          <t>3) عقود أبو خالد قبل 1-11-2025 مشمولة بتسوية 62,937 فلا يُحتسب لها فرق. عقد عرعر WHK-2364 مسعّر أصلاً 0.50.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3) عقود أبو خالد قبل 1-11-2025 مشمولة بتسوية 62,937 فلا يُحتسب لها فرق. عقد عرعر WHK-2364 مسعّر أصلاً 0.50.</t>
+          <t>7) لا تُطبق الضريبة على أي تحويل بين المزرعتين أو مسحوبات لأي من الشريكين – كل القيم قبل الضريبة (معاملات داخلية بدون فاتورة).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>7) لا تُطبق الضريبة على أي تحويل بين المزرعتين أو مسحوبات لأي من الشريكين – كل القيم قبل الضريبة (معاملات داخلية بدون فاتورة).</t>
+          <t>4) الترحيل من الرياض إلى تبوك = مديونية على أبو مازن، ومن تبوك إلى الرياض = دعم تشغيلي من أبو مازن.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>4) الترحيل من الرياض إلى تبوك = مديونية على أبو مازن، ومن تبوك إلى الرياض = دعم تشغيلي من أبو مازن.</t>
+          <t>5) أُلغي PO-213 (بيتونيا 6,000) وخُصمت 17,900 فينكا مفقودة من الطلب 58991، وسلفة رائد الخير (ISV-0075) مستبعدة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>5) أُلغي PO-213 (بيتونيا 6,000) وخُصمت 17,900 فينكا مفقودة من الطلب 58991، وسلفة رائد الخير (ISV-0075) مستبعدة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>6) تكاليف الشحن الخارجي لأوامر ما قبل الفترة تحمّلتها نسما (11,300) ولا تُحمّل على أي طرف.</t>
         </is>
@@ -2721,7 +2700,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9 / 10</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
@@ -2738,7 +2717,7 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>2300</v>
+        <v>2896</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
@@ -6365,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11745,30 +11724,30 @@
         <v>128</v>
       </c>
       <c r="B130" s="7" t="n">
-        <v>45909</v>
+        <v>45887</v>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>RNT-2141</t>
+          <t>RNT-2166</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>مركن 16 سم</t>
+          <t>سكندابسس مركن 19 علاقي</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>15000</v>
+        <v>596</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="G130" s="4">
         <f>IF(F130="","",E130*F130)</f>
         <v/>
       </c>
       <c r="H130" s="8">
-        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
+        <f>IFERROR(IF(VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F130,VLOOKUP("سكندابسس مركن 19 علاقي",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F130)</f>
         <v/>
       </c>
       <c r="I130" s="4">
@@ -11781,7 +11760,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+          <t>حسب إفادتك – 596 سكندابسس × 9 (قيمة النظام 6,500 قبل الضريبة)</t>
         </is>
       </c>
     </row>
@@ -11799,21 +11778,21 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>كمبوست 10 ك</t>
+          <t>مركن 16 سم</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>100</v>
+        <v>15000</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G131" s="4">
         <f>IF(F131="","",E131*F131)</f>
         <v/>
       </c>
       <c r="H131" s="8">
-        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F131,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F131)</f>
+        <f>IFERROR(IF(VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F131,VLOOKUP("مركن 16",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F131)</f>
         <v/>
       </c>
       <c r="I131" s="4">
@@ -11835,30 +11814,30 @@
         <v>130</v>
       </c>
       <c r="B132" s="7" t="n">
-        <v>46163</v>
+        <v>45909</v>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>طلب 58991 (#299/#301)</t>
+          <t>RNT-2141</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>زهور فينكا روزا</t>
+          <t>كمبوست 10 ك</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-17900</v>
+        <v>100</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G132" s="4">
         <f>IF(F132="","",E132*F132)</f>
         <v/>
       </c>
-      <c r="H132" s="4">
-        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F132,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F132)</f>
+      <c r="H132" s="8">
+        <f>IFERROR(IF(VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F132,VLOOKUP("كمبوست 10 ك",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F132)</f>
         <v/>
       </c>
       <c r="I132" s="4">
@@ -11871,38 +11850,83 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
+          <t>أصناف حسب إفادتك – مطابق لقيمة النظام 7,700 قبل الضريبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>طلب 58991 (#299/#301)</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>-17900</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G133" s="4">
+        <f>IF(F133="","",E133*F133)</f>
+        <v/>
+      </c>
+      <c r="H133" s="4">
+        <f>IFERROR(IF(VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)="",F133,VLOOKUP("فينكا روزا",'قائمة الأسعار الموحدة'!$B$3:$E$71,4,FALSE)),F133)</f>
+        <v/>
+      </c>
+      <c r="I133" s="4">
+        <f>IF(H133="","",E133*H133)</f>
+        <v/>
+      </c>
+      <c r="J133" s="4">
+        <f>IF(OR(G133="",I133=""),"",G133-I133)</f>
+        <v/>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
           <t>خصم كمية مرفوضة/مفقودة مع المناديب (حسب قرارك)</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="9" t="n"/>
-      <c r="B133" s="9" t="n"/>
-      <c r="C133" s="9" t="n"/>
-      <c r="D133" s="10" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="10" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="E133" s="11">
-        <f>SUM(E3:E132)</f>
-        <v/>
-      </c>
-      <c r="F133" s="9" t="n"/>
-      <c r="G133" s="11">
-        <f>SUM(G3:G132)</f>
-        <v/>
-      </c>
-      <c r="H133" s="9" t="n"/>
-      <c r="I133" s="11">
-        <f>SUM(I3:I132)</f>
-        <v/>
-      </c>
-      <c r="J133" s="11">
-        <f>SUM(J3:J132)</f>
-        <v/>
-      </c>
-      <c r="K133" s="9" t="n"/>
+      <c r="E134" s="11">
+        <f>SUM(E3:E133)</f>
+        <v/>
+      </c>
+      <c r="F134" s="9" t="n"/>
+      <c r="G134" s="11">
+        <f>SUM(G3:G133)</f>
+        <v/>
+      </c>
+      <c r="H134" s="9" t="n"/>
+      <c r="I134" s="11">
+        <f>SUM(I3:I133)</f>
+        <v/>
+      </c>
+      <c r="J134" s="11">
+        <f>SUM(J3:J133)</f>
+        <v/>
+      </c>
+      <c r="K134" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13763,7 +13787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13826,53 +13850,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>الرياض ← تبوك (على أبو مازن)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>RNT-2166</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>45887</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>TRANSACTIONS BETWEEN RIYADH-TABUK</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>7475</v>
-      </c>
-      <c r="G3" s="4">
-        <f>ROUND(F3/1.15,2)</f>
-        <v/>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>غير مدرج بشيت المحاسب – أرسل الأصناف للتسعير الموحد</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="F4" s="4">
-        <f>SUM(F3:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="4">
-        <f>SUM(G3:G3)</f>
-        <v/>
+          <t>✓ تم تفصيل كل السندات وإدراجها بشيت مسحوبات نسما من الرياض</t>
+        </is>
       </c>
     </row>
   </sheetData>
